--- a/Versão5/BIM/Ontologia_Kml_2x2.xlsx
+++ b/Versão5/BIM/Ontologia_Kml_2x2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3860E2BD-209F-41E1-A4EB-430AA0CCDC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E07971-A7FE-4D46-BB61-371AA2082D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="4" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
@@ -588,9 +588,6 @@
     <t>Elemento de KML. Define um modo de visibilidade &lt;gx:labelVisibility&gt;  &lt;/gx:labelVisibility&gt;</t>
   </si>
   <si>
-    <t>Elemento de KML. Define um modo de tesselagem &lt;tessellate&gt;1&lt;/tessellate&gt;</t>
-  </si>
-  <si>
     <t>Elemento de KML. Define um valor de extrusão &lt;extrude&gt;1&lt;/extrude&gt;.</t>
   </si>
   <si>
@@ -603,18 +600,12 @@
     <t>Elemento de KML. Define a latitude &lt;latitude&gt;-22.45&lt;/latitude&gt;</t>
   </si>
   <si>
-    <t>Kml.Abertura</t>
-  </si>
-  <si>
     <t>Kml.Extrusão</t>
   </si>
   <si>
     <t>Kml.Nome</t>
   </si>
   <si>
-    <t>Kml.Alcance</t>
-  </si>
-  <si>
     <t>Elemento de KML. Define a direction de azimute no sentido horário e em graus decimais (Norte = 0,  Leste = 90, Sul = 180, Oeste = 270). &lt;heading&gt;0&lt;/heading&gt;</t>
   </si>
   <si>
@@ -798,12 +789,6 @@
     <t>Elemento agrupador de pasta KML que ordena elementos em hierarquia de pastas (como a barra lateral do Google Earth), permite ativar ou desativar visibilidades em bloco.</t>
   </si>
   <si>
-    <t>Elemento de KMLque define um estado &lt;open&gt;1&lt;/open&gt;</t>
-  </si>
-  <si>
-    <t>Elemento de KML que define o alcance &lt;range&gt;1000&lt;/range&gt;</t>
-  </si>
-  <si>
     <t>Kml.Camara.Azimut</t>
   </si>
   <si>
@@ -813,15 +798,6 @@
     <t>Elemento agrupador KML de conteúdos geográficos, estilos e schemas associados. É fundamental quando o arquivo contém múltiplos objetos ou estilos reutilizáveis.</t>
   </si>
   <si>
-    <t>Kml.A0.Arquivo</t>
-  </si>
-  <si>
-    <t>Kml.A1.Documento</t>
-  </si>
-  <si>
-    <t>Kml.A2.Pasta</t>
-  </si>
-  <si>
     <t>Kml.Estilo.Cor</t>
   </si>
   <si>
@@ -918,9 +894,6 @@
     <t>&lt;Schema&gt;</t>
   </si>
   <si>
-    <t>Kml.Lugar.Geometria.Tecelagem</t>
-  </si>
-  <si>
     <t>Kml.Modelo.3D</t>
   </si>
   <si>
@@ -963,9 +936,6 @@
     <t>Marca.Arq</t>
   </si>
   <si>
-    <t>é.dentro.de</t>
-  </si>
-  <si>
     <t>é.marcado.com</t>
   </si>
   <si>
@@ -1072,6 +1042,36 @@
   </si>
   <si>
     <t>"&lt;coordinates&gt; &lt;/coordinates&gt;"</t>
+  </si>
+  <si>
+    <t>Kml.Arquivo</t>
+  </si>
+  <si>
+    <t>Kml.Documento</t>
+  </si>
+  <si>
+    <t>Kml.Pasta</t>
+  </si>
+  <si>
+    <t>Especifica se um item da árvore de lugares no Google Earth ou Google Maps é exibido aberto ou fechado por padrão &lt;open&gt;1&lt;/open&gt;</t>
+  </si>
+  <si>
+    <t>Especifica a distância focal da câmera até o ponto de interesse em metros. &lt;range&gt;1000&lt;/range&gt;</t>
+  </si>
+  <si>
+    <t>Kml.Camara.Alcance</t>
+  </si>
+  <si>
+    <t>Kml.Pasta.Aberta</t>
+  </si>
+  <si>
+    <t>Controla se uma linha ou polígono acompanha a curvatura da terra, os relevos do terreno ou se é desenhada como uma linha reta direta no espaço tridimensional. &lt;tessellate&gt;1&lt;/tessellate&gt; Funciona somente se o modo de altitude (&lt;altitudeMode&gt;) está definido como clampToGround (preso ao solo, que é o padrão). Se a altitude for absoluta ou relativa ao solo, o efeito do tessellate é ignorado.</t>
+  </si>
+  <si>
+    <t>Kml.Lugar.Segmento.Projeção</t>
+  </si>
+  <si>
+    <t>é.marcador.interno.de</t>
   </si>
 </sst>
 </file>
@@ -1577,7 +1577,115 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1777,414 +1885,6 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2596,7 +2296,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>11</v>
@@ -2764,7 +2464,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46255.553711111112</v>
+        <v>46255.588563194447</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
@@ -2808,7 +2508,7 @@
         <v>35</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>11</v>
@@ -2986,7 +2686,7 @@
         <v>96</v>
       </c>
       <c r="F2" s="36" t="s">
-        <v>245</v>
+        <v>322</v>
       </c>
       <c r="G2" s="32" t="s">
         <v>2</v>
@@ -3004,46 +2704,46 @@
         <v>2</v>
       </c>
       <c r="L2" s="13" t="str">
-        <f t="shared" ref="L2:O33" si="0">CONCATENATE("", C2)</f>
+        <f>CONCATENATE("", C2)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M2" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D2)</f>
         <v>Esquemas</v>
       </c>
       <c r="N2" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E2)</f>
         <v>KML</v>
       </c>
       <c r="O2" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.A0.Arquivo</v>
+        <f>CONCATENATE("", F2)</f>
+        <v>Kml.Arquivo</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Q2" s="14" t="str">
         <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
         <v>El elemento raíz de agrupación del archivo KML que contiene la declaración de los espacios de nombres y envuelve todo el contenido geográfico.</v>
       </c>
       <c r="R2" s="14" t="str">
-        <f t="shared" ref="R2:R62" si="1">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>The root grouping element of the KML file that contains the declaration of the namespaces and wraps all geographic content.</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T2" s="14" t="str">
-        <f t="shared" ref="T2:U33" si="2">SUBSTITUTE(C2, "_", " ")</f>
+        <f>SUBSTITUTE(C2, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U2" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D2, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V2" s="14" t="str">
-        <f t="shared" ref="V2:V62" si="3">SUBSTITUTE(F2, "_", " ")</f>
-        <v>Kml.A0.Arquivo</v>
+        <f>SUBSTITUTE(F2, "_", " ")</f>
+        <v>Kml.Arquivo</v>
       </c>
       <c r="W2" s="14" t="s">
         <v>64</v>
@@ -3088,7 +2788,7 @@
         <v>96</v>
       </c>
       <c r="F3" s="36" t="s">
-        <v>246</v>
+        <v>140</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>2</v>
@@ -3106,52 +2806,51 @@
         <v>2</v>
       </c>
       <c r="L3" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C3)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M3" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D3)</f>
         <v>Esquemas</v>
       </c>
       <c r="N3" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E3)</f>
         <v>KML</v>
       </c>
       <c r="O3" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.A1.Documento</v>
+        <f>CONCATENATE("", F3)</f>
+        <v>Kml.Atributo</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q3" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P3,"pt","es")</f>
-        <v>KML que agrupa contenido geográfico, estilos y esquemas asociados. Es fundamental cuando el archivo contiene múltiples objetos o estilos reutilizables.</v>
+        <v>141</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>142</v>
       </c>
       <c r="R3" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML bundler of geographic content, styles, and associated schemas. It is critical when the file contains multiple reusable objects or styles.</v>
+        <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <v>Attribute to qualify a KML element.</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T3" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C3, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U3" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D3, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V3" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.A1.Documento</v>
+        <f>SUBSTITUTE(F3, "_", " ")</f>
+        <v>Kml.Atributo</v>
       </c>
       <c r="W3" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X3" s="30" t="str">
-        <f t="shared" ref="X3:X62" si="4">CONCATENATE("Key-Kml-",A3)</f>
+        <f>CONCATENATE("Key-Kml-",A3)</f>
         <v>Key-Kml-3</v>
       </c>
       <c r="Y3" s="14" t="s">
@@ -3170,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="AD3" s="37" t="s">
-        <v>117</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3190,7 +2889,7 @@
         <v>96</v>
       </c>
       <c r="F4" s="36" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="G4" s="32" t="s">
         <v>2</v>
@@ -3208,52 +2907,52 @@
         <v>2</v>
       </c>
       <c r="L4" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C4)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M4" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D4)</f>
         <v>Esquemas</v>
       </c>
       <c r="N4" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E4)</f>
         <v>KML</v>
       </c>
       <c r="O4" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.A2.Pasta</v>
+        <f>CONCATENATE("", F4)</f>
+        <v>Kml.Box</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="Q4" s="14" t="str">
         <f>_xlfn.TRANSLATE(P4,"pt","es")</f>
-        <v>KML folder grouper element que ordena elementos en la jerarquía de carpetas (como la barra lateral de Google Earth), permite habilitar o desactivar la visibilidad de bloques.</v>
+        <v>Elemento KML. Define una región con 4 límites &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
       </c>
       <c r="R4" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML folder grouper element that sorts elements in folder hierarchy (such as the Google Earth sidebar), allows you to enable or disable block visibility.</v>
+        <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
+        <v>KML element. Defines a region with 4 boundaries &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C4, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U4" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D4, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V4" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.A2.Pasta</v>
+        <f>SUBSTITUTE(F4, "_", " ")</f>
+        <v>Kml.Box</v>
       </c>
       <c r="W4" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X4" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A4)</f>
         <v>Key-Kml-4</v>
       </c>
       <c r="Y4" s="14" t="s">
@@ -3272,7 +2971,7 @@
         <v>2</v>
       </c>
       <c r="AD4" s="37" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3292,7 +2991,7 @@
         <v>96</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>175</v>
+        <v>231</v>
       </c>
       <c r="G5" s="32" t="s">
         <v>2</v>
@@ -3310,52 +3009,52 @@
         <v>2</v>
       </c>
       <c r="L5" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C5)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M5" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D5)</f>
         <v>Esquemas</v>
       </c>
       <c r="N5" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E5)</f>
         <v>KML</v>
       </c>
       <c r="O5" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Abertura</v>
+        <f>CONCATENATE("", F5)</f>
+        <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="Q5" s="14" t="str">
         <f>_xlfn.TRANSLATE(P5,"pt","es")</f>
-        <v>Elemento KML que define un estado &lt;open&gt;1&lt;/open&gt;</v>
+        <v>Elemento KML. Fija la longitud del límite oriental de una región &lt;east&gt;120.373033&lt;/east&gt;</v>
       </c>
       <c r="R5" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element that defines a state &lt;open&gt;1&lt;/open&gt;</v>
+        <f>_xlfn.TRANSLATE(P5,"pt","en")</f>
+        <v>KML element. Sets the longitude of the eastern boundary of a region &lt;east&gt;120.373033&lt;/east&gt;</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T5" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C5, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U5" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D5, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V5" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Abertura</v>
+        <f>SUBSTITUTE(F5, "_", " ")</f>
+        <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="W5" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X5" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A5)</f>
         <v>Key-Kml-5</v>
       </c>
       <c r="Y5" s="14" t="s">
@@ -3374,7 +3073,7 @@
         <v>2</v>
       </c>
       <c r="AD5" s="37" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3394,70 +3093,70 @@
         <v>96</v>
       </c>
       <c r="F6" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="13" t="str">
+        <f>CONCATENATE("", C6)</f>
+        <v>Interoperabilidade</v>
+      </c>
+      <c r="M6" s="13" t="str">
+        <f>CONCATENATE("", D6)</f>
+        <v>Esquemas</v>
+      </c>
+      <c r="N6" s="13" t="str">
+        <f>CONCATENATE("", E6)</f>
+        <v>KML</v>
+      </c>
+      <c r="O6" s="13" t="str">
+        <f>CONCATENATE("", F6)</f>
+        <v>Kml.Box.Cardinal.Norte</v>
+      </c>
+      <c r="P6" s="37" t="s">
         <v>178</v>
-      </c>
-      <c r="G6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L6" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Interoperabilidade</v>
-      </c>
-      <c r="M6" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Esquemas</v>
-      </c>
-      <c r="N6" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>KML</v>
-      </c>
-      <c r="O6" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Alcance</v>
-      </c>
-      <c r="P6" s="37" t="s">
-        <v>241</v>
       </c>
       <c r="Q6" s="14" t="str">
         <f>_xlfn.TRANSLATE(P6,"pt","es")</f>
-        <v>Elemento KML que define el rango &lt;range&gt;de 1000&lt;/range&gt;</v>
+        <v>Elemento KML. Fija la latitud del límite norte de una región &lt;north&gt;37.80005&lt;/north&gt;</v>
       </c>
       <c r="R6" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element defining &lt;range&gt;1000&lt;/range&gt; range</v>
+        <f>_xlfn.TRANSLATE(P6,"pt","en")</f>
+        <v>KML element. Sets the latitude of the northern boundary of a region &lt;north&gt;37.80005&lt;/north&gt;</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T6" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C6, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U6" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D6, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V6" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Alcance</v>
+        <f>SUBSTITUTE(F6, "_", " ")</f>
+        <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="W6" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X6" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A6)</f>
         <v>Key-Kml-6</v>
       </c>
       <c r="Y6" s="14" t="s">
@@ -3476,7 +3175,7 @@
         <v>2</v>
       </c>
       <c r="AD6" s="37" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3496,7 +3195,7 @@
         <v>96</v>
       </c>
       <c r="F7" s="36" t="s">
-        <v>140</v>
+        <v>233</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>2</v>
@@ -3514,51 +3213,52 @@
         <v>2</v>
       </c>
       <c r="L7" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C7)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M7" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D7)</f>
         <v>Esquemas</v>
       </c>
       <c r="N7" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E7)</f>
         <v>KML</v>
       </c>
       <c r="O7" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Atributo</v>
+        <f>CONCATENATE("", F7)</f>
+        <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="P7" s="37" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q7" s="14" t="s">
-        <v>142</v>
+        <v>181</v>
+      </c>
+      <c r="Q7" s="14" t="str">
+        <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <v>Elemento KML. Define la longitud del límite occidental de una región &lt;west&gt;120.376033&lt;/west&gt;</v>
       </c>
       <c r="R7" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Attribute to qualify a KML element.</v>
+        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <v>KML element. Defines the longitude of the western boundary of a region &lt;west&gt;120.376033&lt;/west&gt;</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T7" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C7, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U7" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D7, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V7" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Atributo</v>
+        <f>SUBSTITUTE(F7, "_", " ")</f>
+        <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="W7" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X7" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A7)</f>
         <v>Key-Kml-7</v>
       </c>
       <c r="Y7" s="14" t="s">
@@ -3577,7 +3277,7 @@
         <v>2</v>
       </c>
       <c r="AD7" s="37" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3597,7 +3297,7 @@
         <v>96</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>2</v>
@@ -3615,52 +3315,52 @@
         <v>2</v>
       </c>
       <c r="L8" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C8)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M8" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D8)</f>
         <v>Esquemas</v>
       </c>
       <c r="N8" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E8)</f>
         <v>KML</v>
       </c>
       <c r="O8" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box</v>
+        <f>CONCATENATE("", F8)</f>
+        <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="P8" s="37" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="Q8" s="14" t="str">
-        <f t="shared" ref="Q8:Q21" si="5">_xlfn.TRANSLATE(P8,"pt","es")</f>
-        <v>Elemento KML. Define una región con 4 límites &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
+        <f>_xlfn.TRANSLATE(P8,"pt","es")</f>
+        <v>Elemento KML. Establece la latitud del límite sur de una región &lt;south&gt;37.50005&lt;/south&gt;</v>
       </c>
       <c r="R8" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines a region with 4 boundaries &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
+        <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
+        <v>KML element. Sets the latitude of the southern boundary of a region &lt;south&gt;37.50005&lt;/south&gt;</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T8" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C8, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U8" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D8, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V8" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box</v>
+        <f>SUBSTITUTE(F8, "_", " ")</f>
+        <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="W8" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X8" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A8)</f>
         <v>Key-Kml-8</v>
       </c>
       <c r="Y8" s="14" t="s">
@@ -3679,7 +3379,7 @@
         <v>2</v>
       </c>
       <c r="AD8" s="37" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3699,7 +3399,7 @@
         <v>96</v>
       </c>
       <c r="F9" s="36" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>2</v>
@@ -3717,52 +3417,52 @@
         <v>2</v>
       </c>
       <c r="L9" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C9)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M9" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D9)</f>
         <v>Esquemas</v>
       </c>
       <c r="N9" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E9)</f>
         <v>KML</v>
       </c>
       <c r="O9" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box.Cardinal.Leste</v>
+        <f>CONCATENATE("", F9)</f>
+        <v>Kml.Box.Rotado</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>183</v>
       </c>
       <c r="Q9" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Fija la longitud del límite oriental de una región &lt;east&gt;120.373033&lt;/east&gt;</v>
+        <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
+        <v>Elemento KML. Establece una &lt;rotation&gt;rotación 45&lt;/rotation&gt;</v>
       </c>
       <c r="R9" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the longitude of the eastern boundary of a region &lt;east&gt;120.373033&lt;/east&gt;</v>
+        <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
+        <v>KML element. Sets a &lt;rotation&gt;rotation 45&lt;/rotation&gt;</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T9" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C9, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U9" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D9, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V9" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box.Cardinal.Leste</v>
+        <f>SUBSTITUTE(F9, "_", " ")</f>
+        <v>Kml.Box.Rotado</v>
       </c>
       <c r="W9" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X9" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A9)</f>
         <v>Key-Kml-9</v>
       </c>
       <c r="Y9" s="14" t="s">
@@ -3781,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="AD9" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3801,7 +3501,7 @@
         <v>96</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>235</v>
+        <v>145</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>2</v>
@@ -3819,52 +3519,52 @@
         <v>2</v>
       </c>
       <c r="L10" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C10)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M10" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D10)</f>
         <v>Esquemas</v>
       </c>
       <c r="N10" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E10)</f>
         <v>KML</v>
       </c>
       <c r="O10" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box.Cardinal.Norte</v>
+        <f>CONCATENATE("", F10)</f>
+        <v>Kml.Camara</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>181</v>
+        <v>103</v>
       </c>
       <c r="Q10" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Fija la latitud del límite norte de una región &lt;north&gt;37.80005&lt;/north&gt;</v>
+        <f>_xlfn.TRANSLATE(P10,"pt","es")</f>
+        <v>Elemento de visualización en KML. Establece la posición y orientación exactas de la propia cámara en el espacio tridimensional (latitud, longitud, altitud, rotación e inclinación).</v>
       </c>
       <c r="R10" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the latitude of the northern boundary of a region &lt;north&gt;37.80005&lt;/north&gt;</v>
+        <f>_xlfn.TRANSLATE(P10,"pt","en")</f>
+        <v>Visualization element in KML. Sets the exact position and orientation of the camera itself in three-dimensional space (latitude, longitude, altitude, rotation, and tilt).</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T10" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C10, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U10" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D10, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V10" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box.Cardinal.Norte</v>
+        <f>SUBSTITUTE(F10, "_", " ")</f>
+        <v>Kml.Camara</v>
       </c>
       <c r="W10" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X10" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A10)</f>
         <v>Key-Kml-10</v>
       </c>
       <c r="Y10" s="14" t="s">
@@ -3883,7 +3583,7 @@
         <v>2</v>
       </c>
       <c r="AD10" s="37" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3903,7 +3603,7 @@
         <v>96</v>
       </c>
       <c r="F11" s="36" t="s">
-        <v>236</v>
+        <v>327</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>2</v>
@@ -3921,52 +3621,52 @@
         <v>2</v>
       </c>
       <c r="L11" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C11)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M11" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D11)</f>
         <v>Esquemas</v>
       </c>
       <c r="N11" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E11)</f>
         <v>KML</v>
       </c>
       <c r="O11" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box.Cardinal.Oeste</v>
+        <f>CONCATENATE("", F11)</f>
+        <v>Kml.Camara.Alcance</v>
       </c>
       <c r="P11" s="37" t="s">
-        <v>184</v>
+        <v>326</v>
       </c>
       <c r="Q11" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define la longitud del límite occidental de una región &lt;west&gt;120.376033&lt;/west&gt;</v>
+        <f>_xlfn.TRANSLATE(P11,"pt","es")</f>
+        <v>Especifica la distancia focal de la cámara hasta el punto de interés en metros. &lt;range&gt;1000&lt;/range&gt;</v>
       </c>
       <c r="R11" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines the longitude of the western boundary of a region &lt;west&gt;120.376033&lt;/west&gt;</v>
+        <f>_xlfn.TRANSLATE(P11,"pt","en")</f>
+        <v>Specifies the focal length of the camera to the point of interest in meters. &lt;range&gt;1000&lt;/range&gt;</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T11" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C11, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U11" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D11, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V11" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box.Cardinal.Oeste</v>
+        <f>SUBSTITUTE(F11, "_", " ")</f>
+        <v>Kml.Camara.Alcance</v>
       </c>
       <c r="W11" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X11" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A11)</f>
         <v>Key-Kml-11</v>
       </c>
       <c r="Y11" s="14" t="s">
@@ -3985,7 +3685,7 @@
         <v>2</v>
       </c>
       <c r="AD11" s="37" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4005,7 +3705,7 @@
         <v>96</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>2</v>
@@ -4023,52 +3723,52 @@
         <v>2</v>
       </c>
       <c r="L12" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C12)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M12" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D12)</f>
         <v>Esquemas</v>
       </c>
       <c r="N12" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E12)</f>
         <v>KML</v>
       </c>
       <c r="O12" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box.Cardinal.Sul</v>
+        <f>CONCATENATE("", F12)</f>
+        <v>Kml.Camara.Alvo</v>
       </c>
       <c r="P12" s="37" t="s">
-        <v>182</v>
+        <v>104</v>
       </c>
       <c r="Q12" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Establece la latitud del límite sur de una región &lt;south&gt;37.50005&lt;/south&gt;</v>
+        <f>_xlfn.TRANSLATE(P12,"pt","es")</f>
+        <v>Elemento de visualización en KML. Establece la vista posicionando la cámara respecto a un punto geográfico objetivo (incluyendo distancia, inclinación y rumbo).</v>
       </c>
       <c r="R12" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the latitude of the southern boundary of a region &lt;south&gt;37.50005&lt;/south&gt;</v>
+        <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
+        <v>Visualization element in KML. Sets the view by positioning the camera relative to a target geographic point (including distance, tilt, and heading).</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C12, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U12" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D12, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V12" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box.Cardinal.Sul</v>
+        <f>SUBSTITUTE(F12, "_", " ")</f>
+        <v>Kml.Camara.Alvo</v>
       </c>
       <c r="W12" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X12" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A12)</f>
         <v>Key-Kml-12</v>
       </c>
       <c r="Y12" s="14" t="s">
@@ -4087,7 +3787,7 @@
         <v>2</v>
       </c>
       <c r="AD12" s="37" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4107,7 +3807,7 @@
         <v>96</v>
       </c>
       <c r="F13" s="36" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>2</v>
@@ -4125,52 +3825,52 @@
         <v>2</v>
       </c>
       <c r="L13" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C13)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M13" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D13)</f>
         <v>Esquemas</v>
       </c>
       <c r="N13" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E13)</f>
         <v>KML</v>
       </c>
       <c r="O13" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Box.Rotado</v>
+        <f>CONCATENATE("", F13)</f>
+        <v>Kml.Camara.Azimut</v>
       </c>
       <c r="P13" s="37" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="Q13" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Establece una &lt;rotation&gt;rotación 45&lt;/rotation&gt;</v>
+        <f>_xlfn.TRANSLATE(P13,"pt","es")</f>
+        <v>Elemento KML. Establece la dirección del acimut en sentido horario y en grados decimales (Norte = 0, Este = 90, Sur = 180, Oeste = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
       </c>
       <c r="R13" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets a &lt;rotation&gt;rotation 45&lt;/rotation&gt;</v>
+        <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
+        <v>KML element. Sets the azimuth direction clockwise and in decimal degrees (North = 0, East = 90, South = 180, West = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T13" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C13, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U13" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D13, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V13" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Box.Rotado</v>
+        <f>SUBSTITUTE(F13, "_", " ")</f>
+        <v>Kml.Camara.Azimut</v>
       </c>
       <c r="W13" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X13" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A13)</f>
         <v>Key-Kml-13</v>
       </c>
       <c r="Y13" s="14" t="s">
@@ -4189,7 +3889,7 @@
         <v>2</v>
       </c>
       <c r="AD13" s="37" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4209,7 +3909,7 @@
         <v>96</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>145</v>
+        <v>253</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>2</v>
@@ -4227,52 +3927,52 @@
         <v>2</v>
       </c>
       <c r="L14" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C14)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M14" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D14)</f>
         <v>Esquemas</v>
       </c>
       <c r="N14" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E14)</f>
         <v>KML</v>
       </c>
       <c r="O14" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Camara</v>
+        <f>CONCATENATE("", F14)</f>
+        <v>Kml.Dado.Estendido</v>
       </c>
       <c r="P14" s="37" t="s">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c r="Q14" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento de visualización en KML. Establece la posición y orientación exactas de la propia cámara en el espacio tridimensional (latitud, longitud, altitud, rotación e inclinación).</v>
+        <f>_xlfn.TRANSLATE(P14,"pt","es")</f>
+        <v>Elemento KML. Define un conjunto de datos extendido (personalizado). &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
       </c>
       <c r="R14" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Visualization element in KML. Sets the exact position and orientation of the camera itself in three-dimensional space (latitude, longitude, altitude, rotation, and tilt).</v>
+        <f>_xlfn.TRANSLATE(P14,"pt","en")</f>
+        <v>KML element. Defines an extended (custom) dataset. &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T14" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C14, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U14" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D14, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V14" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Camara</v>
+        <f>SUBSTITUTE(F14, "_", " ")</f>
+        <v>Kml.Dado.Estendido</v>
       </c>
       <c r="W14" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X14" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A14)</f>
         <v>Key-Kml-14</v>
       </c>
       <c r="Y14" s="14" t="s">
@@ -4291,7 +3991,7 @@
         <v>2</v>
       </c>
       <c r="AD14" s="37" t="s">
-        <v>137</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4311,7 +4011,7 @@
         <v>96</v>
       </c>
       <c r="F15" s="36" t="s">
-        <v>243</v>
+        <v>269</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>2</v>
@@ -4329,52 +4029,52 @@
         <v>2</v>
       </c>
       <c r="L15" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C15)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M15" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D15)</f>
         <v>Esquemas</v>
       </c>
       <c r="N15" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E15)</f>
         <v>KML</v>
       </c>
       <c r="O15" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Camara.Alvo</v>
+        <f>CONCATENATE("", F15)</f>
+        <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="P15" s="37" t="s">
-        <v>104</v>
+        <v>218</v>
       </c>
       <c r="Q15" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento de visualización en KML. Establece la vista posicionando la cámara respecto a un punto geográfico objetivo (incluyendo distancia, inclinación y rumbo).</v>
+        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
+        <v>Elemento KML. Define un dato personalizado dentro de ExtendenData &lt;Nombre de datos='doname'&lt;value&gt;&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
       </c>
       <c r="R15" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Visualization element in KML. Sets the view by positioning the camera relative to a target geographic point (including distance, tilt, and heading).</v>
+        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
+        <v>KML element. Define a custom data within ExtendenData &lt;Data name='doname'&gt;&lt;value&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T15" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C15, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U15" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D15, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V15" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Camara.Alvo</v>
+        <f>SUBSTITUTE(F15, "_", " ")</f>
+        <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="W15" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X15" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A15)</f>
         <v>Key-Kml-15</v>
       </c>
       <c r="Y15" s="14" t="s">
@@ -4393,7 +4093,7 @@
         <v>2</v>
       </c>
       <c r="AD15" s="37" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4413,7 +4113,7 @@
         <v>96</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>242</v>
+        <v>270</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>2</v>
@@ -4431,52 +4131,52 @@
         <v>2</v>
       </c>
       <c r="L16" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C16)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M16" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D16)</f>
         <v>Esquemas</v>
       </c>
       <c r="N16" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E16)</f>
         <v>KML</v>
       </c>
       <c r="O16" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Camara.Azimut</v>
+        <f>CONCATENATE("", F16)</f>
+        <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="Q16" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Establece la dirección del acimut en sentido horario y en grados decimales (Norte = 0, Este = 90, Sur = 180, Oeste = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
+        <f>_xlfn.TRANSLATE(P16,"pt","es")</f>
+        <v>Elemento KML. Define un dato plano personalizado dentro de ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
       </c>
       <c r="R16" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the azimuth direction clockwise and in decimal degrees (North = 0, East = 90, South = 180, West = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
+        <f>_xlfn.TRANSLATE(P16,"pt","en")</f>
+        <v>KML element. Define a custom flat data inside ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T16" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C16, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U16" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D16, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V16" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Camara.Azimut</v>
+        <f>SUBSTITUTE(F16, "_", " ")</f>
+        <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="W16" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X16" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A16)</f>
         <v>Key-Kml-16</v>
       </c>
       <c r="Y16" s="14" t="s">
@@ -4495,7 +4195,7 @@
         <v>2</v>
       </c>
       <c r="AD16" s="37" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4515,7 +4215,7 @@
         <v>96</v>
       </c>
       <c r="F17" s="36" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>2</v>
@@ -4533,52 +4233,52 @@
         <v>2</v>
       </c>
       <c r="L17" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C17)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M17" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D17)</f>
         <v>Esquemas</v>
       </c>
       <c r="N17" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E17)</f>
         <v>KML</v>
       </c>
       <c r="O17" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Dado.Estendido</v>
+        <f>CONCATENATE("", F17)</f>
+        <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="P17" s="37" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="Q17" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define un conjunto de datos extendido (personalizado). &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
+        <f>_xlfn.TRANSLATE(P17,"pt","es")</f>
+        <v>Elemento KML. Define un diseño &lt;Schema&gt; personalizado ..... &lt;/Schema&gt;</v>
       </c>
       <c r="R17" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines an extended (custom) dataset. &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
+        <f>_xlfn.TRANSLATE(P17,"pt","en")</f>
+        <v>KML element. Define a custom layout &lt;Schema&gt; ..... &lt;/Schema&gt;</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T17" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C17, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U17" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D17, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V17" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Dado.Estendido</v>
+        <f>SUBSTITUTE(F17, "_", " ")</f>
+        <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="W17" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X17" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A17)</f>
         <v>Key-Kml-17</v>
       </c>
       <c r="Y17" s="14" t="s">
@@ -4597,7 +4297,7 @@
         <v>2</v>
       </c>
       <c r="AD17" s="37" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4617,7 +4317,7 @@
         <v>96</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="G18" s="32" t="s">
         <v>2</v>
@@ -4635,52 +4335,52 @@
         <v>2</v>
       </c>
       <c r="L18" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C18)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M18" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D18)</f>
         <v>Esquemas</v>
       </c>
       <c r="N18" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E18)</f>
         <v>KML</v>
       </c>
       <c r="O18" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Dado.Estendido.Dado</v>
+        <f>CONCATENATE("", F18)</f>
+        <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="P18" s="37" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q18" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define un dato personalizado dentro de ExtendenData &lt;Nombre de datos='doname'&lt;value&gt;&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
+        <f>_xlfn.TRANSLATE(P18,"pt","es")</f>
+        <v>Elemento KML. Define un dato &lt;Schema&gt; asociado a uno para añadir datos personalizados tipados a un elemento KML.</v>
       </c>
       <c r="R18" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Define a custom data within ExtendenData &lt;Data name='doname'&gt;&lt;value&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
+        <f>_xlfn.TRANSLATE(P18,"pt","en")</f>
+        <v>KML element. Defines a piece of data associated &lt;Schema&gt; with one to add typed custom data to a KML element.</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T18" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C18, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U18" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D18, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V18" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Dado.Estendido.Dado</v>
+        <f>SUBSTITUTE(F18, "_", " ")</f>
+        <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="W18" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X18" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A18)</f>
         <v>Key-Kml-18</v>
       </c>
       <c r="Y18" s="14" t="s">
@@ -4719,7 +4419,7 @@
         <v>96</v>
       </c>
       <c r="F19" s="36" t="s">
-        <v>278</v>
+        <v>323</v>
       </c>
       <c r="G19" s="32" t="s">
         <v>2</v>
@@ -4737,52 +4437,52 @@
         <v>2</v>
       </c>
       <c r="L19" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C19)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M19" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D19)</f>
         <v>Esquemas</v>
       </c>
       <c r="N19" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E19)</f>
         <v>KML</v>
       </c>
       <c r="O19" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Dado.Estendido.Dado.Simples</v>
+        <f>CONCATENATE("", F19)</f>
+        <v>Kml.Documento</v>
       </c>
       <c r="P19" s="37" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="Q19" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define un dato plano personalizado dentro de ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
+        <f>_xlfn.TRANSLATE(P19,"pt","es")</f>
+        <v>KML que agrupa contenido geográfico, estilos y esquemas asociados. Es fundamental cuando el archivo contiene múltiples objetos o estilos reutilizables.</v>
       </c>
       <c r="R19" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Define a custom flat data inside ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
+        <f>_xlfn.TRANSLATE(P19,"pt","en")</f>
+        <v>KML bundler of geographic content, styles, and associated schemas. It is critical when the file contains multiple reusable objects or styles.</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T19" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C19, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U19" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D19, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V19" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Dado.Estendido.Dado.Simples</v>
+        <f>SUBSTITUTE(F19, "_", " ")</f>
+        <v>Kml.Documento</v>
       </c>
       <c r="W19" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X19" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A19)</f>
         <v>Key-Kml-19</v>
       </c>
       <c r="Y19" s="14" t="s">
@@ -4801,7 +4501,7 @@
         <v>2</v>
       </c>
       <c r="AD19" s="37" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4821,7 +4521,7 @@
         <v>96</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>276</v>
+        <v>155</v>
       </c>
       <c r="G20" s="32" t="s">
         <v>2</v>
@@ -4839,52 +4539,51 @@
         <v>2</v>
       </c>
       <c r="L20" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C20)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M20" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D20)</f>
         <v>Esquemas</v>
       </c>
       <c r="N20" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E20)</f>
         <v>KML</v>
       </c>
       <c r="O20" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Dado.Estendido.Esquema</v>
+        <f>CONCATENATE("", F20)</f>
+        <v>Kml.Elemento.N0</v>
       </c>
       <c r="P20" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q20" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define un diseño &lt;Schema&gt; personalizado ..... &lt;/Schema&gt;</v>
+        <v>151</v>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>146</v>
       </c>
       <c r="R20" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Define a custom layout &lt;Schema&gt; ..... &lt;/Schema&gt;</v>
+        <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
+        <v>A KML element of level 0 Root (&lt;KML&gt;).</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T20" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C20, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U20" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D20, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V20" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Dado.Estendido.Esquema</v>
+        <f>SUBSTITUTE(F20, "_", " ")</f>
+        <v>Kml.Elemento.N0</v>
       </c>
       <c r="W20" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X20" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A20)</f>
         <v>Key-Kml-20</v>
       </c>
       <c r="Y20" s="14" t="s">
@@ -4903,7 +4602,7 @@
         <v>2</v>
       </c>
       <c r="AD20" s="37" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4923,7 +4622,7 @@
         <v>96</v>
       </c>
       <c r="F21" s="36" t="s">
-        <v>275</v>
+        <v>156</v>
       </c>
       <c r="G21" s="32" t="s">
         <v>2</v>
@@ -4941,52 +4640,51 @@
         <v>2</v>
       </c>
       <c r="L21" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C21)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M21" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D21)</f>
         <v>Esquemas</v>
       </c>
       <c r="N21" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E21)</f>
         <v>KML</v>
       </c>
       <c r="O21" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Dado.Estendido.Esquema.Dado</v>
+        <f>CONCATENATE("", F21)</f>
+        <v>Kml.Elemento.N1</v>
       </c>
       <c r="P21" s="37" t="s">
-        <v>226</v>
-      </c>
-      <c r="Q21" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v>Elemento KML. Define un dato &lt;Schema&gt; asociado a uno para añadir datos personalizados tipados a un elemento KML.</v>
+        <v>152</v>
+      </c>
+      <c r="Q21" s="37" t="s">
+        <v>147</v>
       </c>
       <c r="R21" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines a piece of data associated &lt;Schema&gt; with one to add typed custom data to a KML element.</v>
+        <f>_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <v>A level 1 KML element (&lt;Document&gt; and &lt;Folder&gt;).</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T21" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C21, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U21" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D21, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V21" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Dado.Estendido.Esquema.Dado</v>
+        <f>SUBSTITUTE(F21, "_", " ")</f>
+        <v>Kml.Elemento.N1</v>
       </c>
       <c r="W21" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X21" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A21)</f>
         <v>Key-Kml-21</v>
       </c>
       <c r="Y21" s="14" t="s">
@@ -5005,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="AD21" s="37" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5025,7 +4723,7 @@
         <v>96</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>2</v>
@@ -5043,51 +4741,51 @@
         <v>2</v>
       </c>
       <c r="L22" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C22)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M22" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D22)</f>
         <v>Esquemas</v>
       </c>
       <c r="N22" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E22)</f>
         <v>KML</v>
       </c>
       <c r="O22" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N0</v>
+        <f>CONCATENATE("", F22)</f>
+        <v>Kml.Elemento.N2</v>
       </c>
       <c r="P22" s="37" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Q22" s="37" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R22" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A KML element of level 0 Root (&lt;KML&gt;).</v>
+        <f>_xlfn.TRANSLATE(P22,"pt","en")</f>
+        <v>A level 2 KML element (&lt;Placemark&gt;, &lt;GroundOverlay&gt;...).</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T22" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C22, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U22" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D22, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V22" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N0</v>
+        <f>SUBSTITUTE(F22, "_", " ")</f>
+        <v>Kml.Elemento.N2</v>
       </c>
       <c r="W22" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X22" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A22)</f>
         <v>Key-Kml-22</v>
       </c>
       <c r="Y22" s="14" t="s">
@@ -5106,7 +4804,7 @@
         <v>2</v>
       </c>
       <c r="AD22" s="37" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5126,7 +4824,7 @@
         <v>96</v>
       </c>
       <c r="F23" s="36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G23" s="32" t="s">
         <v>2</v>
@@ -5144,51 +4842,51 @@
         <v>2</v>
       </c>
       <c r="L23" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C23)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M23" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D23)</f>
         <v>Esquemas</v>
       </c>
       <c r="N23" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E23)</f>
         <v>KML</v>
       </c>
       <c r="O23" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N1</v>
+        <f>CONCATENATE("", F23)</f>
+        <v>Kml.Elemento.N3</v>
       </c>
       <c r="P23" s="37" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q23" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="R23" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A level 1 KML element (&lt;Document&gt; and &lt;Folder&gt;).</v>
+        <f>_xlfn.TRANSLATE(P23,"pt","en")</f>
+        <v>A level 3 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T23" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C23, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U23" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D23, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V23" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N1</v>
+        <f>SUBSTITUTE(F23, "_", " ")</f>
+        <v>Kml.Elemento.N3</v>
       </c>
       <c r="W23" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X23" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A23)</f>
         <v>Key-Kml-23</v>
       </c>
       <c r="Y23" s="14" t="s">
@@ -5207,7 +4905,7 @@
         <v>2</v>
       </c>
       <c r="AD23" s="37" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5227,7 +4925,7 @@
         <v>96</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>2</v>
@@ -5245,51 +4943,51 @@
         <v>2</v>
       </c>
       <c r="L24" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C24)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M24" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D24)</f>
         <v>Esquemas</v>
       </c>
       <c r="N24" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E24)</f>
         <v>KML</v>
       </c>
       <c r="O24" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N2</v>
+        <f>CONCATENATE("", F24)</f>
+        <v>Kml.Elemento.N4</v>
       </c>
       <c r="P24" s="37" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q24" s="37" t="s">
         <v>148</v>
       </c>
       <c r="R24" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A level 2 KML element (&lt;Placemark&gt;, &lt;GroundOverlay&gt;...).</v>
+        <f>_xlfn.TRANSLATE(P24,"pt","en")</f>
+        <v>A level 4 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T24" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C24, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U24" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D24, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V24" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N2</v>
+        <f>SUBSTITUTE(F24, "_", " ")</f>
+        <v>Kml.Elemento.N4</v>
       </c>
       <c r="W24" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X24" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A24)</f>
         <v>Key-Kml-24</v>
       </c>
       <c r="Y24" s="14" t="s">
@@ -5308,7 +5006,7 @@
         <v>2</v>
       </c>
       <c r="AD24" s="37" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5328,7 +5026,7 @@
         <v>96</v>
       </c>
       <c r="F25" s="36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G25" s="32" t="s">
         <v>2</v>
@@ -5346,51 +5044,51 @@
         <v>2</v>
       </c>
       <c r="L25" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C25)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M25" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D25)</f>
         <v>Esquemas</v>
       </c>
       <c r="N25" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E25)</f>
         <v>KML</v>
       </c>
       <c r="O25" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N3</v>
+        <f>CONCATENATE("", F25)</f>
+        <v>Kml.Elemento.N5</v>
       </c>
       <c r="P25" s="37" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="Q25" s="37" t="s">
         <v>148</v>
       </c>
       <c r="R25" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A level 3 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
+        <f>_xlfn.TRANSLATE(P25,"pt","en")</f>
+        <v>A level 5 KML element (&lt;outerBoundaryIs&gt;, &lt;LinearRing&gt;, &lt;coordinates&gt;).</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T25" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C25, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U25" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D25, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V25" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N3</v>
+        <f>SUBSTITUTE(F25, "_", " ")</f>
+        <v>Kml.Elemento.N5</v>
       </c>
       <c r="W25" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X25" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A25)</f>
         <v>Key-Kml-25</v>
       </c>
       <c r="Y25" s="14" t="s">
@@ -5409,7 +5107,7 @@
         <v>2</v>
       </c>
       <c r="AD25" s="37" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5429,7 +5127,7 @@
         <v>96</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G26" s="32" t="s">
         <v>2</v>
@@ -5447,51 +5145,52 @@
         <v>2</v>
       </c>
       <c r="L26" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C26)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M26" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D26)</f>
         <v>Esquemas</v>
       </c>
       <c r="N26" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E26)</f>
         <v>KML</v>
       </c>
       <c r="O26" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N4</v>
+        <f>CONCATENATE("", F26)</f>
+        <v>Kml.Estilo</v>
       </c>
       <c r="P26" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q26" s="37" t="s">
-        <v>148</v>
+        <v>97</v>
+      </c>
+      <c r="Q26" s="14" t="str">
+        <f>_xlfn.TRANSLATE(P26,"pt","es")</f>
+        <v>Elemento de estilo en KML. Agrupa propiedades gráficas de personalización como colores, transparencias, tamaños e iconos.</v>
       </c>
       <c r="R26" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A level 4 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
+        <f>_xlfn.TRANSLATE(P26,"pt","en")</f>
+        <v>Styling element in KML. Groups graphical customization properties such as colors, transparencies, sizes, and icons.</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T26" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C26, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U26" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D26, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V26" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N4</v>
+        <f>SUBSTITUTE(F26, "_", " ")</f>
+        <v>Kml.Estilo</v>
       </c>
       <c r="W26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X26" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A26)</f>
         <v>Key-Kml-26</v>
       </c>
       <c r="Y26" s="14" t="s">
@@ -5510,7 +5209,7 @@
         <v>2</v>
       </c>
       <c r="AD26" s="37" t="s">
-        <v>290</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5530,7 +5229,7 @@
         <v>96</v>
       </c>
       <c r="F27" s="36" t="s">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="G27" s="32" t="s">
         <v>2</v>
@@ -5548,51 +5247,52 @@
         <v>2</v>
       </c>
       <c r="L27" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C27)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M27" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D27)</f>
         <v>Esquemas</v>
       </c>
       <c r="N27" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E27)</f>
         <v>KML</v>
       </c>
       <c r="O27" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Elemento.N5</v>
+        <f>CONCATENATE("", F27)</f>
+        <v>Kml.Estilo.Balão</v>
       </c>
       <c r="P27" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q27" s="37" t="s">
-        <v>148</v>
+        <v>100</v>
+      </c>
+      <c r="Q27" s="14" t="str">
+        <f>_xlfn.TRANSLATE(P27,"pt","es")</f>
+        <v>Elemento de estilo en KML. Personaliza la burbuja de información/ventana emergente que se abre al hacer clic en un elemento (soporta etiquetas HTML).</v>
       </c>
       <c r="R27" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>A level 5 KML element (&lt;outerBoundaryIs&gt;, &lt;LinearRing&gt;, &lt;coordinates&gt;).</v>
+        <f>_xlfn.TRANSLATE(P27,"pt","en")</f>
+        <v>Styling element in KML. Customizes the info/pop-up bubble that opens when you click on an element (supports HTML tags).</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T27" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C27, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U27" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D27, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V27" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Elemento.N5</v>
+        <f>SUBSTITUTE(F27, "_", " ")</f>
+        <v>Kml.Estilo.Balão</v>
       </c>
       <c r="W27" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X27" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A27)</f>
         <v>Key-Kml-27</v>
       </c>
       <c r="Y27" s="14" t="s">
@@ -5611,7 +5311,7 @@
         <v>2</v>
       </c>
       <c r="AD27" s="37" t="s">
-        <v>290</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5631,7 +5331,7 @@
         <v>96</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>144</v>
+        <v>240</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>2</v>
@@ -5649,52 +5349,52 @@
         <v>2</v>
       </c>
       <c r="L28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C28)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D28)</f>
         <v>Esquemas</v>
       </c>
       <c r="N28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E28)</f>
         <v>KML</v>
       </c>
       <c r="O28" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo</v>
+        <f>CONCATENATE("", F28)</f>
+        <v>Kml.Estilo.Cor</v>
       </c>
       <c r="P28" s="37" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
       <c r="Q28" s="14" t="str">
-        <f t="shared" ref="Q28:Q62" si="6">_xlfn.TRANSLATE(P28,"pt","es")</f>
-        <v>Elemento de estilo en KML. Agrupa propiedades gráficas de personalización como colores, transparencias, tamaños e iconos.</v>
+        <f>_xlfn.TRANSLATE(P28,"pt","es")</f>
+        <v>Elemento KML. Establece un &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
       </c>
       <c r="R28" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Styling element in KML. Groups graphical customization properties such as colors, transparencies, sizes, and icons.</v>
+        <f>_xlfn.TRANSLATE(P28,"pt","en")</f>
+        <v>KML element. Sets a &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T28" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C28, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U28" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D28, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V28" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo</v>
+        <f>SUBSTITUTE(F28, "_", " ")</f>
+        <v>Kml.Estilo.Cor</v>
       </c>
       <c r="W28" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X28" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A28)</f>
         <v>Key-Kml-28</v>
       </c>
       <c r="Y28" s="14" t="s">
@@ -5713,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="AD28" s="37" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5733,7 +5433,7 @@
         <v>96</v>
       </c>
       <c r="F29" s="36" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="G29" s="32" t="s">
         <v>2</v>
@@ -5751,52 +5451,52 @@
         <v>2</v>
       </c>
       <c r="L29" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C29)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M29" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D29)</f>
         <v>Esquemas</v>
       </c>
       <c r="N29" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E29)</f>
         <v>KML</v>
       </c>
       <c r="O29" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo.Balão</v>
+        <f>CONCATENATE("", F29)</f>
+        <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="P29" s="37" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="Q29" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de estilo en KML. Personaliza la burbuja de información/ventana emergente que se abre al hacer clic en un elemento (soporta etiquetas HTML).</v>
+        <f>_xlfn.TRANSLATE(P29,"pt","es")</f>
+        <v>Elemento KML. Establece un espesor &lt;width&gt;de 1&lt;/width&gt;</v>
       </c>
       <c r="R29" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Styling element in KML. Customizes the info/pop-up bubble that opens when you click on an element (supports HTML tags).</v>
+        <f>_xlfn.TRANSLATE(P29,"pt","en")</f>
+        <v>KML element. Sets a thickness &lt;width&gt;of 1&lt;/width&gt;</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T29" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C29, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U29" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D29, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V29" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Balão</v>
+        <f>SUBSTITUTE(F29, "_", " ")</f>
+        <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="W29" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X29" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A29)</f>
         <v>Key-Kml-29</v>
       </c>
       <c r="Y29" s="14" t="s">
@@ -5815,7 +5515,7 @@
         <v>2</v>
       </c>
       <c r="AD29" s="37" t="s">
-        <v>132</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5835,7 +5535,7 @@
         <v>96</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G30" s="32" t="s">
         <v>2</v>
@@ -5853,52 +5553,52 @@
         <v>2</v>
       </c>
       <c r="L30" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C30)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M30" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D30)</f>
         <v>Esquemas</v>
       </c>
       <c r="N30" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E30)</f>
         <v>KML</v>
       </c>
       <c r="O30" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo.Cor</v>
+        <f>CONCATENATE("", F30)</f>
+        <v>Kml.Estilo.Linha</v>
       </c>
       <c r="P30" s="37" t="s">
-        <v>167</v>
+        <v>98</v>
       </c>
       <c r="Q30" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece un &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
+        <f>_xlfn.TRANSLATE(P30,"pt","es")</f>
+        <v>Elemento de estilo en KML. Establece el color, la opacidad y el grosor de las líneas.</v>
       </c>
       <c r="R30" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets a &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
+        <f>_xlfn.TRANSLATE(P30,"pt","en")</f>
+        <v>Styling element in KML. Sets the color, opacity, and thickness of the lines.</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T30" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C30, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U30" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D30, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V30" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Cor</v>
+        <f>SUBSTITUTE(F30, "_", " ")</f>
+        <v>Kml.Estilo.Linha</v>
       </c>
       <c r="W30" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X30" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A30)</f>
         <v>Key-Kml-30</v>
       </c>
       <c r="Y30" s="14" t="s">
@@ -5917,7 +5617,7 @@
         <v>2</v>
       </c>
       <c r="AD30" s="37" t="s">
-        <v>200</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5937,7 +5637,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G31" s="32" t="s">
         <v>2</v>
@@ -5955,52 +5655,52 @@
         <v>2</v>
       </c>
       <c r="L31" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C31)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M31" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D31)</f>
         <v>Esquemas</v>
       </c>
       <c r="N31" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E31)</f>
         <v>KML</v>
       </c>
       <c r="O31" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo.Espessura</v>
+        <f>CONCATENATE("", F31)</f>
+        <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="P31" s="37" t="s">
-        <v>168</v>
+        <v>101</v>
       </c>
       <c r="Q31" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece un espesor &lt;width&gt;de 1&lt;/width&gt;</v>
+        <f>_xlfn.TRANSLATE(P31,"pt","es")</f>
+        <v>Elemento de estilo en KML. Permite cambiar la apariencia de un elemento según la acción del usuario (por ejemplo, cambiar el icono cuando el cursor flota).</v>
       </c>
       <c r="R31" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets a thickness &lt;width&gt;of 1&lt;/width&gt;</v>
+        <f>_xlfn.TRANSLATE(P31,"pt","en")</f>
+        <v>Styling element in KML. Allows you to toggle the appearance of an element based on the user's action (e.g., change the icon when the cursor hovers).</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T31" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C31, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U31" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D31, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V31" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Espessura</v>
+        <f>SUBSTITUTE(F31, "_", " ")</f>
+        <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="W31" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X31" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A31)</f>
         <v>Key-Kml-31</v>
       </c>
       <c r="Y31" s="14" t="s">
@@ -6019,7 +5719,7 @@
         <v>2</v>
       </c>
       <c r="AD31" s="37" t="s">
-        <v>201</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6039,7 +5739,7 @@
         <v>96</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="G32" s="32" t="s">
         <v>2</v>
@@ -6057,52 +5757,52 @@
         <v>2</v>
       </c>
       <c r="L32" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C32)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M32" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D32)</f>
         <v>Esquemas</v>
       </c>
       <c r="N32" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E32)</f>
         <v>KML</v>
       </c>
       <c r="O32" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo.Linha</v>
+        <f>CONCATENATE("", F32)</f>
+        <v>Kml.Estilo.Texto</v>
       </c>
       <c r="P32" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q32" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de estilo en KML. Establece el color, la opacidad y el grosor de las líneas.</v>
+        <f>_xlfn.TRANSLATE(P32,"pt","es")</f>
+        <v>Elemento de estilo en KML. Establece el color y la escala del texto de la etiqueta en viñetas.</v>
       </c>
       <c r="R32" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Styling element in KML. Sets the color, opacity, and thickness of the lines.</v>
+        <f>_xlfn.TRANSLATE(P32,"pt","en")</f>
+        <v>Styling element in KML. Sets the color and scale of the bullet label text.</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T32" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C32, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U32" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D32, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V32" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Linha</v>
+        <f>SUBSTITUTE(F32, "_", " ")</f>
+        <v>Kml.Estilo.Texto</v>
       </c>
       <c r="W32" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X32" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A32)</f>
         <v>Key-Kml-32</v>
       </c>
       <c r="Y32" s="14" t="s">
@@ -6121,7 +5821,7 @@
         <v>2</v>
       </c>
       <c r="AD32" s="37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6141,7 +5841,7 @@
         <v>96</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="G33" s="32" t="s">
         <v>2</v>
@@ -6159,52 +5859,52 @@
         <v>2</v>
       </c>
       <c r="L33" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", C33)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M33" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", D33)</f>
         <v>Esquemas</v>
       </c>
       <c r="N33" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f>CONCATENATE("", E33)</f>
         <v>KML</v>
       </c>
       <c r="O33" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>Kml.Estilo.Mapa</v>
+        <f>CONCATENATE("", F33)</f>
+        <v>Kml.Estilo.Usado</v>
       </c>
       <c r="P33" s="37" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="Q33" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de estilo en KML. Permite cambiar la apariencia de un elemento según la acción del usuario (por ejemplo, cambiar el icono cuando el cursor flota).</v>
+        <f>_xlfn.TRANSLATE(P33,"pt","es")</f>
+        <v>Elemento KML. Establece la referencia a un estilo &lt;styleUrl&gt;ya definido #EstilodeLinha&lt;/styleUrl&gt;</v>
       </c>
       <c r="R33" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Styling element in KML. Allows you to toggle the appearance of an element based on the user's action (e.g., change the icon when the cursor hovers).</v>
+        <f>_xlfn.TRANSLATE(P33,"pt","en")</f>
+        <v>KML element. Sets the reference to a style already defined &lt;styleUrl&gt;#EstilodeLinha&lt;/styleUrl&gt;</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T33" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(C33, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U33" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f>SUBSTITUTE(D33, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V33" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Mapa</v>
+        <f>SUBSTITUTE(F33, "_", " ")</f>
+        <v>Kml.Estilo.Usado</v>
       </c>
       <c r="W33" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X33" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A33)</f>
         <v>Key-Kml-33</v>
       </c>
       <c r="Y33" s="14" t="s">
@@ -6223,7 +5923,7 @@
         <v>2</v>
       </c>
       <c r="AD33" s="37" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6243,7 +5943,7 @@
         <v>96</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G34" s="32" t="s">
         <v>2</v>
@@ -6261,52 +5961,52 @@
         <v>2</v>
       </c>
       <c r="L34" s="13" t="str">
-        <f t="shared" ref="L34:O62" si="7">CONCATENATE("", C34)</f>
+        <f>CONCATENATE("", C34)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M34" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D34)</f>
         <v>Esquemas</v>
       </c>
       <c r="N34" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E34)</f>
         <v>KML</v>
       </c>
       <c r="O34" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Estilo.Texto</v>
+        <f>CONCATENATE("", F34)</f>
+        <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="P34" s="37" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
       <c r="Q34" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de estilo en KML. Establece el color y la escala del texto de la etiqueta en viñetas.</v>
+        <f>_xlfn.TRANSLATE(P34,"pt","es")</f>
+        <v>Elemento KML. Establece un modo de visibilidad &lt;gx:etiquetaVisibilidad&gt; &lt;/gx:etiquetaVisibilidad&gt;</v>
       </c>
       <c r="R34" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Styling element in KML. Sets the color and scale of the bullet label text.</v>
+        <f>_xlfn.TRANSLATE(P34,"pt","en")</f>
+        <v>KML element. Sets a visibility mode &lt;gx:labelVisibility&gt; &lt;/gx:labelVisibility&gt;</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T34" s="14" t="str">
-        <f t="shared" ref="T34:U62" si="8">SUBSTITUTE(C34, "_", " ")</f>
+        <f>SUBSTITUTE(C34, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U34" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D34, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V34" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Texto</v>
+        <f>SUBSTITUTE(F34, "_", " ")</f>
+        <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="W34" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X34" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A34)</f>
         <v>Key-Kml-34</v>
       </c>
       <c r="Y34" s="14" t="s">
@@ -6325,7 +6025,7 @@
         <v>2</v>
       </c>
       <c r="AD34" s="37" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6345,7 +6045,7 @@
         <v>96</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="G35" s="32" t="s">
         <v>2</v>
@@ -6363,52 +6063,52 @@
         <v>2</v>
       </c>
       <c r="L35" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C35)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M35" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D35)</f>
         <v>Esquemas</v>
       </c>
       <c r="N35" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E35)</f>
         <v>KML</v>
       </c>
       <c r="O35" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Estilo.Usado</v>
+        <f>CONCATENATE("", F35)</f>
+        <v>Kml.Extrusão</v>
       </c>
       <c r="P35" s="37" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="Q35" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece la referencia a un estilo &lt;styleUrl&gt;ya definido #EstilodeLinha&lt;/styleUrl&gt;</v>
+        <f>_xlfn.TRANSLATE(P35,"pt","es")</f>
+        <v>Elemento KML. Fija un valor de extrusión &lt;extrude&gt;de 1&lt;/extrude&gt;.</v>
       </c>
       <c r="R35" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the reference to a style already defined &lt;styleUrl&gt;#EstilodeLinha&lt;/styleUrl&gt;</v>
+        <f>_xlfn.TRANSLATE(P35,"pt","en")</f>
+        <v>KML element. Sets an extrusion value &lt;extrude&gt;of 1&lt;/extrude&gt;.</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T35" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C35, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U35" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D35, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V35" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Usado</v>
+        <f>SUBSTITUTE(F35, "_", " ")</f>
+        <v>Kml.Extrusão</v>
       </c>
       <c r="W35" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X35" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A35)</f>
         <v>Key-Kml-35</v>
       </c>
       <c r="Y35" s="14" t="s">
@@ -6427,7 +6127,7 @@
         <v>2</v>
       </c>
       <c r="AD35" s="37" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6447,7 +6147,7 @@
         <v>96</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="G36" s="32" t="s">
         <v>2</v>
@@ -6465,52 +6165,52 @@
         <v>2</v>
       </c>
       <c r="L36" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C36)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M36" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D36)</f>
         <v>Esquemas</v>
       </c>
       <c r="N36" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E36)</f>
         <v>KML</v>
       </c>
       <c r="O36" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Estilo.Visibilidade</v>
+        <f>CONCATENATE("", F36)</f>
+        <v>Kml.Gira.X</v>
       </c>
       <c r="P36" s="37" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="Q36" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece un modo de visibilidad &lt;gx:etiquetaVisibilidad&gt; &lt;/gx:etiquetaVisibilidad&gt;</v>
+        <f>_xlfn.TRANSLATE(P36,"pt","es")</f>
+        <v>Elemento KML. Ajusta la inclinación alrededor del eje &lt;tilt&gt;X 10,5&lt;/tilt&gt; Un valor de 0 está hacia abajo hacia la Tierra. Valor 90, la vista es hacia el horizonte. El valor &gt; 90 indica que la opinión sube. Los valores siempre son positivos.</v>
       </c>
       <c r="R36" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets a visibility mode &lt;gx:labelVisibility&gt; &lt;/gx:labelVisibility&gt;</v>
+        <f>_xlfn.TRANSLATE(P36,"pt","en")</f>
+        <v>KML element. Sets the tilt about the X-axis &lt;tilt&gt;10.5&lt;/tilt&gt; A value of 0 view is downward toward the Earth. Value 90 the view is to the horizon. Value &gt; 90 indicates the view points up. The values are always positive.</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T36" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C36, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U36" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D36, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V36" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Estilo.Visibilidade</v>
+        <f>SUBSTITUTE(F36, "_", " ")</f>
+        <v>Kml.Gira.X</v>
       </c>
       <c r="W36" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X36" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A36)</f>
         <v>Key-Kml-36</v>
       </c>
       <c r="Y36" s="14" t="s">
@@ -6529,7 +6229,7 @@
         <v>2</v>
       </c>
       <c r="AD36" s="37" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6549,7 +6249,7 @@
         <v>96</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>176</v>
+        <v>227</v>
       </c>
       <c r="G37" s="32" t="s">
         <v>2</v>
@@ -6567,52 +6267,52 @@
         <v>2</v>
       </c>
       <c r="L37" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C37)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M37" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D37)</f>
         <v>Esquemas</v>
       </c>
       <c r="N37" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E37)</f>
         <v>KML</v>
       </c>
       <c r="O37" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Extrusão</v>
+        <f>CONCATENATE("", F37)</f>
+        <v>Kml.Gira.Z</v>
       </c>
       <c r="P37" s="37" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="Q37" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Fija un valor de extrusión &lt;extrude&gt;de 1&lt;/extrude&gt;.</v>
+        <f>_xlfn.TRANSLATE(P37,"pt","es")</f>
+        <v>Elemento KML. Define que un giro alrededor del eje &lt;roll&gt;Z 0&lt;/roll&gt; no puede ser valor negativo.</v>
       </c>
       <c r="R37" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets an extrusion value &lt;extrude&gt;of 1&lt;/extrude&gt;.</v>
+        <f>_xlfn.TRANSLATE(P37,"pt","en")</f>
+        <v>KML element. Defines a turn around the Z-axis &lt;roll&gt;0&lt;/roll&gt; cannot be negative value.</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T37" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C37, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U37" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D37, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V37" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Extrusão</v>
+        <f>SUBSTITUTE(F37, "_", " ")</f>
+        <v>Kml.Gira.Z</v>
       </c>
       <c r="W37" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X37" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A37)</f>
         <v>Key-Kml-37</v>
       </c>
       <c r="Y37" s="14" t="s">
@@ -6631,7 +6331,7 @@
         <v>2</v>
       </c>
       <c r="AD37" s="37" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6651,7 +6351,7 @@
         <v>96</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>231</v>
+        <v>143</v>
       </c>
       <c r="G38" s="32" t="s">
         <v>2</v>
@@ -6669,52 +6369,52 @@
         <v>2</v>
       </c>
       <c r="L38" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C38)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M38" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D38)</f>
         <v>Esquemas</v>
       </c>
       <c r="N38" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E38)</f>
         <v>KML</v>
       </c>
       <c r="O38" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Gira.X</v>
+        <f>CONCATENATE("", F38)</f>
+        <v>Kml.Lugar</v>
       </c>
       <c r="P38" s="37" t="s">
-        <v>188</v>
+        <v>115</v>
       </c>
       <c r="Q38" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Ajusta la inclinación alrededor del eje &lt;tilt&gt;X 10,5&lt;/tilt&gt; Un valor de 0 está hacia abajo hacia la Tierra. Valor 90, la vista es hacia el horizonte. El valor &gt; 90 indica que la opinión sube. Los valores siempre son positivos.</v>
+        <f>_xlfn.TRANSLATE(P38,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Define el elemento más común que representa una característica geográfica individual y puede asociar un nombre, descripción, estilo y geometría.</v>
       </c>
       <c r="R38" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets the tilt about the X-axis &lt;tilt&gt;10.5&lt;/tilt&gt; A value of 0 view is downward toward the Earth. Value 90 the view is to the horizon. Value &gt; 90 indicates the view points up. The values are always positive.</v>
+        <f>_xlfn.TRANSLATE(P38,"pt","en")</f>
+        <v>Geographic feature element in KML. Defines the most common element that represents an individual geographic feature and can associate a name, description, style, and geometry.</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T38" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C38, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U38" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D38, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V38" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Gira.X</v>
+        <f>SUBSTITUTE(F38, "_", " ")</f>
+        <v>Kml.Lugar</v>
       </c>
       <c r="W38" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X38" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A38)</f>
         <v>Key-Kml-38</v>
       </c>
       <c r="Y38" s="14" t="s">
@@ -6733,7 +6433,7 @@
         <v>2</v>
       </c>
       <c r="AD38" s="37" t="s">
-        <v>209</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -6753,7 +6453,7 @@
         <v>96</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>230</v>
+        <v>266</v>
       </c>
       <c r="G39" s="32" t="s">
         <v>2</v>
@@ -6771,52 +6471,52 @@
         <v>2</v>
       </c>
       <c r="L39" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C39)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M39" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D39)</f>
         <v>Esquemas</v>
       </c>
       <c r="N39" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E39)</f>
         <v>KML</v>
       </c>
       <c r="O39" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Gira.Z</v>
+        <f>CONCATENATE("", F39)</f>
+        <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="P39" s="37" t="s">
-        <v>187</v>
+        <v>113</v>
       </c>
       <c r="Q39" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Define que un giro alrededor del eje &lt;roll&gt;Z 0&lt;/roll&gt; no puede ser valor negativo.</v>
+        <f>_xlfn.TRANSLATE(P39,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Un contenedor que agrupa varias geometrías bajo un único Placemark (por ejemplo, un país compuesto por varias islas).</v>
       </c>
       <c r="R39" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines a turn around the Z-axis &lt;roll&gt;0&lt;/roll&gt; cannot be negative value.</v>
+        <f>_xlfn.TRANSLATE(P39,"pt","en")</f>
+        <v>Geographic feature element in KML. A container that groups several geometries under a single Placemark (for example, a country composed of several islands).</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T39" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C39, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U39" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D39, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V39" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Gira.Z</v>
+        <f>SUBSTITUTE(F39, "_", " ")</f>
+        <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="W39" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X39" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A39)</f>
         <v>Key-Kml-39</v>
       </c>
       <c r="Y39" s="14" t="s">
@@ -6835,12 +6535,12 @@
         <v>2</v>
       </c>
       <c r="AD39" s="37" t="s">
-        <v>210</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="31">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>91</v>
@@ -6855,7 +6555,7 @@
         <v>96</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="G40" s="32" t="s">
         <v>2</v>
@@ -6873,53 +6573,53 @@
         <v>2</v>
       </c>
       <c r="L40" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C40)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M40" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D40)</f>
         <v>Esquemas</v>
       </c>
       <c r="N40" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E40)</f>
         <v>KML</v>
       </c>
       <c r="O40" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar</v>
+        <f>CONCATENATE("", F40)</f>
+        <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="P40" s="37" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="Q40" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Define el elemento más común que representa una característica geográfica individual y puede asociar un nombre, descripción, estilo y geometría.</v>
+        <f>_xlfn.TRANSLATE(P40,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Establece una ubicación puntual en el mapa usando longitud, latitud y, opcionalmente, coordenadas de altitud.</v>
       </c>
       <c r="R40" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. Defines the most common element that represents an individual geographic feature and can associate a name, description, style, and geometry.</v>
+        <f>_xlfn.TRANSLATE(P40,"pt","en")</f>
+        <v>Geographic feature element in KML. Sets a point location on the map using longitude, latitude, and optionally altitude coordinates.</v>
       </c>
       <c r="S40" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T40" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C40, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U40" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D40, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V40" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar</v>
+        <f>SUBSTITUTE(F40, "_", " ")</f>
+        <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="W40" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X40" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-40</v>
+        <f>CONCATENATE("Key-Kml-",A40)</f>
+        <v>Key-Kml-41</v>
       </c>
       <c r="Y40" s="14" t="s">
         <v>2</v>
@@ -6937,12 +6637,12 @@
         <v>2</v>
       </c>
       <c r="AD40" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="31">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>91</v>
@@ -6957,7 +6657,7 @@
         <v>96</v>
       </c>
       <c r="F41" s="36" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="G41" s="32" t="s">
         <v>2</v>
@@ -6975,53 +6675,53 @@
         <v>2</v>
       </c>
       <c r="L41" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C41)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M41" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D41)</f>
         <v>Esquemas</v>
       </c>
       <c r="N41" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E41)</f>
         <v>KML</v>
       </c>
       <c r="O41" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Geometria</v>
+        <f>CONCATENATE("", F41)</f>
+        <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="P41" s="37" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="Q41" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Un contenedor que agrupa varias geometrías bajo un único Placemark (por ejemplo, un país compuesto por varias islas).</v>
+        <f>_xlfn.TRANSLATE(P41,"pt","es")</f>
+        <v>Elemento KML. Fija una altitud &lt;altitude&gt;de 10,5&lt;/altitude&gt;</v>
       </c>
       <c r="R41" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. A container that groups several geometries under a single Placemark (for example, a country composed of several islands).</v>
+        <f>_xlfn.TRANSLATE(P41,"pt","en")</f>
+        <v>KML element. Set an altitude &lt;altitude&gt;of 10.5&lt;/altitude&gt;</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T41" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C41, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U41" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D41, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V41" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Geometria</v>
+        <f>SUBSTITUTE(F41, "_", " ")</f>
+        <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="W41" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X41" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-41</v>
+        <f>CONCATENATE("Key-Kml-",A41)</f>
+        <v>Key-Kml-42</v>
       </c>
       <c r="Y41" s="14" t="s">
         <v>2</v>
@@ -7039,12 +6739,12 @@
         <v>2</v>
       </c>
       <c r="AD41" s="37" t="s">
-        <v>124</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="31">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>91</v>
@@ -7059,7 +6759,7 @@
         <v>96</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="G42" s="32" t="s">
         <v>2</v>
@@ -7077,53 +6777,53 @@
         <v>2</v>
       </c>
       <c r="L42" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C42)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M42" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D42)</f>
         <v>Esquemas</v>
       </c>
       <c r="N42" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E42)</f>
         <v>KML</v>
       </c>
       <c r="O42" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Geometria.Tecelagem</v>
+        <f>CONCATENATE("", F42)</f>
+        <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="P42" s="37" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="Q42" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece un modo de &lt;tessellate&gt;teselación 1&lt;/tessellate&gt;</v>
+        <f>_xlfn.TRANSLATE(P42,"pt","es")</f>
+        <v>Elemento KML. Establece el modo &lt;altitudeMode&gt;altitud absoluta&lt;/altitudeMode&gt; (Valores posibles: relativeToGround, clampToGround y absoluto)</v>
       </c>
       <c r="R42" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets a tessellation mode &lt;tessellate&gt;1&lt;/tessellate&gt;</v>
+        <f>_xlfn.TRANSLATE(P42,"pt","en")</f>
+        <v>KML element. Sets &lt;altitudeMode&gt;the absolute altitude&lt;/altitudeMode&gt; mode (Possible values: relativeToGround, clampToGround, and absolute)</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T42" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C42, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U42" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D42, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V42" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Geometria.Tecelagem</v>
+        <f>SUBSTITUTE(F42, "_", " ")</f>
+        <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="W42" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X42" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-42</v>
+        <f>CONCATENATE("Key-Kml-",A42)</f>
+        <v>Key-Kml-43</v>
       </c>
       <c r="Y42" s="14" t="s">
         <v>2</v>
@@ -7141,12 +6841,12 @@
         <v>2</v>
       </c>
       <c r="AD42" s="37" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="31">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>91</v>
@@ -7161,7 +6861,7 @@
         <v>96</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="G43" s="32" t="s">
         <v>2</v>
@@ -7179,53 +6879,53 @@
         <v>2</v>
       </c>
       <c r="L43" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C43)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M43" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D43)</f>
         <v>Esquemas</v>
       </c>
       <c r="N43" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E43)</f>
         <v>KML</v>
       </c>
       <c r="O43" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto</v>
+        <f>CONCATENATE("", F43)</f>
+        <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="P43" s="37" t="s">
-        <v>109</v>
+        <v>173</v>
       </c>
       <c r="Q43" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Establece una ubicación puntual en el mapa usando longitud, latitud y, opcionalmente, coordenadas de altitud.</v>
+        <f>_xlfn.TRANSLATE(P43,"pt","es")</f>
+        <v>Elemento KML. Conjuntos latitud &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
       </c>
       <c r="R43" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. Sets a point location on the map using longitude, latitude, and optionally altitude coordinates.</v>
+        <f>_xlfn.TRANSLATE(P43,"pt","en")</f>
+        <v>KML element. Sets latitude &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T43" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C43, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U43" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D43, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V43" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto</v>
+        <f>SUBSTITUTE(F43, "_", " ")</f>
+        <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="W43" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X43" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-43</v>
+        <f>CONCATENATE("Key-Kml-",A43)</f>
+        <v>Key-Kml-44</v>
       </c>
       <c r="Y43" s="14" t="s">
         <v>2</v>
@@ -7243,12 +6943,12 @@
         <v>2</v>
       </c>
       <c r="AD43" s="37" t="s">
-        <v>120</v>
+        <v>201</v>
       </c>
     </row>
     <row r="44" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="31">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>91</v>
@@ -7263,7 +6963,7 @@
         <v>96</v>
       </c>
       <c r="F44" s="36" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G44" s="32" t="s">
         <v>2</v>
@@ -7281,53 +6981,53 @@
         <v>2</v>
       </c>
       <c r="L44" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C44)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M44" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D44)</f>
         <v>Esquemas</v>
       </c>
       <c r="N44" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E44)</f>
         <v>KML</v>
       </c>
       <c r="O44" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto.Altitude</v>
+        <f>CONCATENATE("", F44)</f>
+        <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="P44" s="37" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="Q44" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Fija una altitud &lt;altitude&gt;de 10,5&lt;/altitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P44,"pt","es")</f>
+        <v>Elemento KML. Conjuntos longitud &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
       </c>
       <c r="R44" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Set an altitude &lt;altitude&gt;of 10.5&lt;/altitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P44,"pt","en")</f>
+        <v>KML element. Sets longitude &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T44" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C44, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U44" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D44, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V44" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto.Altitude</v>
+        <f>SUBSTITUTE(F44, "_", " ")</f>
+        <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="W44" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X44" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-44</v>
+        <f>CONCATENATE("Key-Kml-",A44)</f>
+        <v>Key-Kml-45</v>
       </c>
       <c r="Y44" s="14" t="s">
         <v>2</v>
@@ -7345,12 +7045,12 @@
         <v>2</v>
       </c>
       <c r="AD44" s="37" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
     </row>
     <row r="45" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="31">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>91</v>
@@ -7365,7 +7065,7 @@
         <v>96</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>268</v>
+        <v>305</v>
       </c>
       <c r="G45" s="32" t="s">
         <v>2</v>
@@ -7383,53 +7083,53 @@
         <v>2</v>
       </c>
       <c r="L45" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C45)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M45" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D45)</f>
         <v>Esquemas</v>
       </c>
       <c r="N45" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E45)</f>
         <v>KML</v>
       </c>
       <c r="O45" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto.AltitudeModo</v>
+        <f>CONCATENATE("", F45)</f>
+        <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="P45" s="37" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Establece el modo &lt;altitudeMode&gt;altitud absoluta&lt;/altitudeMode&gt; (Valores posibles: relativeToGround, clampToGround y absoluto)</v>
+        <f>_xlfn.TRANSLATE(P45,"pt","es")</f>
+        <v>Elemento de coordenadas en KML. Coordenadas. X, Y, Z separados por comas y coordinados por espacios &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
       </c>
       <c r="R45" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets &lt;altitudeMode&gt;the absolute altitude&lt;/altitudeMode&gt; mode (Possible values: relativeToGround, clampToGround, and absolute)</v>
+        <f>_xlfn.TRANSLATE(P45,"pt","en")</f>
+        <v>Coordinate element in KML. Coordinates. X, Y, Z separated by commas and coordinated by spaces &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
       </c>
       <c r="S45" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T45" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C45, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U45" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D45, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V45" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto.AltitudeModo</v>
+        <f>SUBSTITUTE(F45, "_", " ")</f>
+        <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="W45" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X45" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-45</v>
+        <f>CONCATENATE("Key-Kml-",A45)</f>
+        <v>Key-Kml-46</v>
       </c>
       <c r="Y45" s="14" t="s">
         <v>2</v>
@@ -7447,12 +7147,12 @@
         <v>2</v>
       </c>
       <c r="AD45" s="37" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="31">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>91</v>
@@ -7467,7 +7167,7 @@
         <v>96</v>
       </c>
       <c r="F46" s="36" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="G46" s="32" t="s">
         <v>2</v>
@@ -7485,53 +7185,53 @@
         <v>2</v>
       </c>
       <c r="L46" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C46)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M46" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D46)</f>
         <v>Esquemas</v>
       </c>
       <c r="N46" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E46)</f>
         <v>KML</v>
       </c>
       <c r="O46" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto.XYZ</v>
+        <f>CONCATENATE("", F46)</f>
+        <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="P46" s="37" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="Q46" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de coordenadas en KML. Coordenadas. X, Y, Z separados por comas y coordinados por espacios &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
+        <f>_xlfn.TRANSLATE(P46,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Define una línea continua a través de una secuencia de coordenadas (útil para caminos, rutas y ríos).</v>
       </c>
       <c r="R46" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Coordinate element in KML. Coordinates. X, Y, Z separated by commas and coordinated by spaces &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
+        <f>_xlfn.TRANSLATE(P46,"pt","en")</f>
+        <v>Geographic feature element in KML. Defines a continuous line through a sequence of coordinates (useful for paths, routes, and rivers).</v>
       </c>
       <c r="S46" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T46" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C46, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U46" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D46, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V46" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto.XYZ</v>
+        <f>SUBSTITUTE(F46, "_", " ")</f>
+        <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="W46" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X46" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-46</v>
+        <f>CONCATENATE("Key-Kml-",A46)</f>
+        <v>Key-Kml-47</v>
       </c>
       <c r="Y46" s="14" t="s">
         <v>2</v>
@@ -7549,12 +7249,12 @@
         <v>2</v>
       </c>
       <c r="AD46" s="37" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="31">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>91</v>
@@ -7569,7 +7269,7 @@
         <v>96</v>
       </c>
       <c r="F47" s="36" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G47" s="32" t="s">
         <v>2</v>
@@ -7587,53 +7287,53 @@
         <v>2</v>
       </c>
       <c r="L47" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C47)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M47" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D47)</f>
         <v>Esquemas</v>
       </c>
       <c r="N47" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E47)</f>
         <v>KML</v>
       </c>
       <c r="O47" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto.Latitude</v>
+        <f>CONCATENATE("", F47)</f>
+        <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="P47" s="37" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="Q47" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Conjuntos latitud &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P47,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Una línea cerrada, no auto-intersectante, usada principalmente para definir los límites de un polígono.</v>
       </c>
       <c r="R47" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets latitude &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P47,"pt","en")</f>
+        <v>Geographic feature element in KML. A closed, non-self-intersecting line, used primarily to define the boundaries of a polygon.</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T47" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C47, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U47" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D47, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V47" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto.Latitude</v>
+        <f>SUBSTITUTE(F47, "_", " ")</f>
+        <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="W47" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X47" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-47</v>
+        <f>CONCATENATE("Key-Kml-",A47)</f>
+        <v>Key-Kml-48</v>
       </c>
       <c r="Y47" s="14" t="s">
         <v>2</v>
@@ -7651,12 +7351,12 @@
         <v>2</v>
       </c>
       <c r="AD47" s="37" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="31">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>91</v>
@@ -7671,7 +7371,7 @@
         <v>96</v>
       </c>
       <c r="F48" s="36" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G48" s="32" t="s">
         <v>2</v>
@@ -7689,53 +7389,53 @@
         <v>2</v>
       </c>
       <c r="L48" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C48)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M48" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D48)</f>
         <v>Esquemas</v>
       </c>
       <c r="N48" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E48)</f>
         <v>KML</v>
       </c>
       <c r="O48" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Ponto.Longitude</v>
+        <f>CONCATENATE("", F48)</f>
+        <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="P48" s="37" t="s">
-        <v>173</v>
+        <v>112</v>
       </c>
       <c r="Q48" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Conjuntos longitud &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P48,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Define un área delimitada por un límite exterior (&lt;outerBoundaryIs&gt;) y, opcionalmente, por un límite interior (&lt;innerBoundaryIs&gt;) para crear agujeros.</v>
       </c>
       <c r="R48" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Sets longitude &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
+        <f>_xlfn.TRANSLATE(P48,"pt","en")</f>
+        <v>Geographic feature element in KML. Defines an area bounded by an outer boundary (&lt;outerBoundaryIs&gt;) and, optionally, inner boundary (&lt;innerBoundaryIs&gt;) to create holes.</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T48" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C48, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U48" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D48, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V48" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Ponto.Longitude</v>
+        <f>SUBSTITUTE(F48, "_", " ")</f>
+        <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="W48" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X48" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-48</v>
+        <f>CONCATENATE("Key-Kml-",A48)</f>
+        <v>Key-Kml-49</v>
       </c>
       <c r="Y48" s="14" t="s">
         <v>2</v>
@@ -7753,12 +7453,12 @@
         <v>2</v>
       </c>
       <c r="AD48" s="37" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="31">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>91</v>
@@ -7773,7 +7473,7 @@
         <v>96</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>271</v>
+        <v>330</v>
       </c>
       <c r="G49" s="32" t="s">
         <v>2</v>
@@ -7791,53 +7491,53 @@
         <v>2</v>
       </c>
       <c r="L49" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C49)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M49" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D49)</f>
         <v>Esquemas</v>
       </c>
       <c r="N49" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E49)</f>
         <v>KML</v>
       </c>
       <c r="O49" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Segmento</v>
+        <f>CONCATENATE("", F49)</f>
+        <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="P49" s="37" t="s">
-        <v>110</v>
+        <v>329</v>
       </c>
       <c r="Q49" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Define una línea continua a través de una secuencia de coordenadas (útil para caminos, rutas y ríos).</v>
+        <f>_xlfn.TRANSLATE(P49,"pt","es")</f>
+        <v>Determina si una línea o polígono sigue la curvatura de la tierra, los relieves del terreno o si se dibuja como una línea recta en el espacio tridimensional. &lt;tessellate&gt;1&lt;/tessellate&gt; solo funciona si el modo altitud (&lt;altitudeMode&gt;) está configurado en clampToGround (fijado a tierra, que es el valor predeterminado). Si la altitud es absoluta o relativa al suelo, se ignora el efecto del teselado.</v>
       </c>
       <c r="R49" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. Defines a continuous line through a sequence of coordinates (useful for paths, routes, and rivers).</v>
+        <f>_xlfn.TRANSLATE(P49,"pt","en")</f>
+        <v>Controls whether a line or polygon follows the curvature of the earth, the terrain reliefs, or whether it is drawn as a straight line in three-dimensional space. &lt;tessellate&gt;1&lt;/tessellate&gt; Works only if the altitude mode (&lt;altitudeMode&gt;) is set to clampToGround (secured to ground, which is the default). If the altitude is absolute or relative to the ground, the effect of tessellate is ignored.</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T49" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C49, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U49" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D49, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V49" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Segmento</v>
+        <f>SUBSTITUTE(F49, "_", " ")</f>
+        <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="W49" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X49" s="30" t="str">
-        <f t="shared" si="4"/>
-        <v>Key-Kml-49</v>
+        <f>CONCATENATE("Key-Kml-",A49)</f>
+        <v>Key-Kml-40</v>
       </c>
       <c r="Y49" s="14" t="s">
         <v>2</v>
@@ -7855,7 +7555,7 @@
         <v>2</v>
       </c>
       <c r="AD49" s="37" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7893,52 +7593,52 @@
         <v>2</v>
       </c>
       <c r="L50" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C50)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M50" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D50)</f>
         <v>Esquemas</v>
       </c>
       <c r="N50" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E50)</f>
         <v>KML</v>
       </c>
       <c r="O50" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Segmento.Poligonal</v>
+        <f>CONCATENATE("", F50)</f>
+        <v>Kml.Modelo.3D</v>
       </c>
       <c r="P50" s="37" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Q50" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Una línea cerrada, no auto-intersectante, usada principalmente para definir los límites de un polígono.</v>
+        <f>_xlfn.TRANSLATE(P50,"pt","es")</f>
+        <v>Elemento de características geográficas en KML. Permite insertar modelos 3D complejos (normalmente en formato COLLADA .dae) en el mapa.</v>
       </c>
       <c r="R50" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. A closed, non-self-intersecting line, used primarily to define the boundaries of a polygon.</v>
+        <f>_xlfn.TRANSLATE(P50,"pt","en")</f>
+        <v>Geographic feature element in KML. It allows you to insert complex 3D models (usually in COLLADA .dae format) into the map.</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T50" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C50, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U50" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D50, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V50" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Segmento.Poligonal</v>
+        <f>SUBSTITUTE(F50, "_", " ")</f>
+        <v>Kml.Modelo.3D</v>
       </c>
       <c r="W50" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X50" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A50)</f>
         <v>Key-Kml-50</v>
       </c>
       <c r="Y50" s="14" t="s">
@@ -7957,7 +7657,7 @@
         <v>2</v>
       </c>
       <c r="AD50" s="37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="51" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -7977,7 +7677,7 @@
         <v>96</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>273</v>
+        <v>175</v>
       </c>
       <c r="G51" s="32" t="s">
         <v>2</v>
@@ -7995,52 +7695,52 @@
         <v>2</v>
       </c>
       <c r="L51" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C51)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M51" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D51)</f>
         <v>Esquemas</v>
       </c>
       <c r="N51" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E51)</f>
         <v>KML</v>
       </c>
       <c r="O51" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Lugar.Segmento.Poligono</v>
+        <f>CONCATENATE("", F51)</f>
+        <v>Kml.Nome</v>
       </c>
       <c r="P51" s="37" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="Q51" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Define un área delimitada por un límite exterior (&lt;outerBoundaryIs&gt;) y, opcionalmente, por un límite interior (&lt;innerBoundaryIs&gt;) para crear agujeros.</v>
+        <f>_xlfn.TRANSLATE(P51,"pt","es")</f>
+        <v>Elemento KML. Define un nombre que puede ser archivo, lugar, etc. &lt;name&gt;Nombre del elemento&lt;/name&gt;</v>
       </c>
       <c r="R51" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. Defines an area bounded by an outer boundary (&lt;outerBoundaryIs&gt;) and, optionally, inner boundary (&lt;innerBoundaryIs&gt;) to create holes.</v>
+        <f>_xlfn.TRANSLATE(P51,"pt","en")</f>
+        <v>KML element. Defines a name that can be file, place, etc. &lt;name&gt;Element Name&lt;/name&gt;</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T51" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C51, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U51" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D51, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V51" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Lugar.Segmento.Poligono</v>
+        <f>SUBSTITUTE(F51, "_", " ")</f>
+        <v>Kml.Nome</v>
       </c>
       <c r="W51" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X51" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A51)</f>
         <v>Key-Kml-51</v>
       </c>
       <c r="Y51" s="14" t="s">
@@ -8059,7 +7759,7 @@
         <v>2</v>
       </c>
       <c r="AD51" s="37" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8079,7 +7779,7 @@
         <v>96</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>281</v>
+        <v>324</v>
       </c>
       <c r="G52" s="32" t="s">
         <v>2</v>
@@ -8097,52 +7797,52 @@
         <v>2</v>
       </c>
       <c r="L52" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C52)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M52" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D52)</f>
         <v>Esquemas</v>
       </c>
       <c r="N52" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E52)</f>
         <v>KML</v>
       </c>
       <c r="O52" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Modelo.3D</v>
+        <f>CONCATENATE("", F52)</f>
+        <v>Kml.Pasta</v>
       </c>
       <c r="P52" s="37" t="s">
-        <v>114</v>
+        <v>236</v>
       </c>
       <c r="Q52" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento de características geográficas en KML. Permite insertar modelos 3D complejos (normalmente en formato COLLADA .dae) en el mapa.</v>
+        <f>_xlfn.TRANSLATE(P52,"pt","es")</f>
+        <v>KML folder grouper element que ordena elementos en la jerarquía de carpetas (como la barra lateral de Google Earth), permite habilitar o desactivar la visibilidad de bloques.</v>
       </c>
       <c r="R52" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>Geographic feature element in KML. It allows you to insert complex 3D models (usually in COLLADA .dae format) into the map.</v>
+        <f>_xlfn.TRANSLATE(P52,"pt","en")</f>
+        <v>KML folder grouper element that sorts elements in folder hierarchy (such as the Google Earth sidebar), allows you to enable or disable block visibility.</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T52" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C52, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U52" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D52, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V52" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Modelo.3D</v>
+        <f>SUBSTITUTE(F52, "_", " ")</f>
+        <v>Kml.Pasta</v>
       </c>
       <c r="W52" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X52" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A52)</f>
         <v>Key-Kml-52</v>
       </c>
       <c r="Y52" s="14" t="s">
@@ -8161,7 +7861,7 @@
         <v>2</v>
       </c>
       <c r="AD52" s="37" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8181,7 +7881,7 @@
         <v>96</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>177</v>
+        <v>328</v>
       </c>
       <c r="G53" s="32" t="s">
         <v>2</v>
@@ -8199,52 +7899,52 @@
         <v>2</v>
       </c>
       <c r="L53" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C53)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M53" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D53)</f>
         <v>Esquemas</v>
       </c>
       <c r="N53" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E53)</f>
         <v>KML</v>
       </c>
       <c r="O53" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Kml.Nome</v>
+        <f>CONCATENATE("", F53)</f>
+        <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="P53" s="37" t="s">
-        <v>172</v>
+        <v>325</v>
       </c>
       <c r="Q53" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Define un nombre que puede ser archivo, lugar, etc. &lt;name&gt;Nombre del elemento&lt;/name&gt;</v>
+        <f>_xlfn.TRANSLATE(P53,"pt","es")</f>
+        <v>Especifica si un elemento en el árbol de lugares en Google Earth o Google Maps se muestra abierto o cerrado por &lt;open&gt;defecto 1&lt;/open&gt;</v>
       </c>
       <c r="R53" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines a name that can be file, place, etc. &lt;name&gt;Element Name&lt;/name&gt;</v>
+        <f>_xlfn.TRANSLATE(P53,"pt","en")</f>
+        <v>Specifies whether an item in the place tree in Google Earth or Google Maps is displayed open or closed by default &lt;open&gt;1&lt;/open&gt;</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T53" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C53, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U53" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D53, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V53" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Nome</v>
+        <f>SUBSTITUTE(F53, "_", " ")</f>
+        <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="W53" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X53" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A53)</f>
         <v>Key-Kml-53</v>
       </c>
       <c r="Y53" s="14" t="s">
@@ -8263,7 +7963,7 @@
         <v>2</v>
       </c>
       <c r="AD53" s="37" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
     </row>
     <row r="54" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8283,70 +7983,70 @@
         <v>96</v>
       </c>
       <c r="F54" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="G54" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H54" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I54" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J54" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K54" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L54" s="13" t="str">
+        <f>CONCATENATE("", C54)</f>
+        <v>Interoperabilidade</v>
+      </c>
+      <c r="M54" s="13" t="str">
+        <f>CONCATENATE("", D54)</f>
+        <v>Esquemas</v>
+      </c>
+      <c r="N54" s="13" t="str">
+        <f>CONCATENATE("", E54)</f>
+        <v>KML</v>
+      </c>
+      <c r="O54" s="13" t="str">
+        <f>CONCATENATE("", F54)</f>
+        <v>Kml.Region</v>
+      </c>
+      <c r="P54" s="37" t="s">
         <v>215</v>
       </c>
-      <c r="G54" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="H54" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="I54" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="J54" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="K54" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="L54" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Interoperabilidade</v>
-      </c>
-      <c r="M54" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>Esquemas</v>
-      </c>
-      <c r="N54" s="13" t="str">
-        <f t="shared" si="7"/>
-        <v>KML</v>
-      </c>
-      <c r="O54" s="13" t="str">
-        <f t="shared" si="7"/>
+      <c r="Q54" s="14" t="str">
+        <f>_xlfn.TRANSLATE(P54,"pt","es")</f>
+        <v>Elemento KML. Define una región. &lt;Region&gt; ..... &lt;/Region&gt;</v>
+      </c>
+      <c r="R54" s="14" t="str">
+        <f>_xlfn.TRANSLATE(P54,"pt","en")</f>
+        <v>KML element. Defines a region. &lt;Region&gt; ..... &lt;/Region&gt;</v>
+      </c>
+      <c r="S54" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T54" s="14" t="str">
+        <f>SUBSTITUTE(C54, "_", " ")</f>
+        <v>Interoperabilidade</v>
+      </c>
+      <c r="U54" s="14" t="str">
+        <f>SUBSTITUTE(D54, "_", " ")</f>
+        <v>Esquemas</v>
+      </c>
+      <c r="V54" s="14" t="str">
+        <f>SUBSTITUTE(F54, "_", " ")</f>
         <v>Kml.Region</v>
       </c>
-      <c r="P54" s="37" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q54" s="14" t="str">
-        <f t="shared" si="6"/>
-        <v>Elemento KML. Define una región. &lt;Region&gt; ..... &lt;/Region&gt;</v>
-      </c>
-      <c r="R54" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v>KML element. Defines a region. &lt;Region&gt; ..... &lt;/Region&gt;</v>
-      </c>
-      <c r="S54" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="T54" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v>Interoperabilidade</v>
-      </c>
-      <c r="U54" s="14" t="str">
-        <f t="shared" si="8"/>
-        <v>Esquemas</v>
-      </c>
-      <c r="V54" s="14" t="str">
-        <f t="shared" si="3"/>
-        <v>Kml.Region</v>
-      </c>
       <c r="W54" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X54" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A54)</f>
         <v>Key-Kml-54</v>
       </c>
       <c r="Y54" s="14" t="s">
@@ -8365,7 +8065,7 @@
         <v>2</v>
       </c>
       <c r="AD54" s="37" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="55" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8385,7 +8085,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="G55" s="32" t="s">
         <v>2</v>
@@ -8403,52 +8103,52 @@
         <v>2</v>
       </c>
       <c r="L55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C55)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D55)</f>
         <v>Esquemas</v>
       </c>
       <c r="N55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E55)</f>
         <v>KML</v>
       </c>
       <c r="O55" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F55)</f>
         <v>Kml.Sobrepor</v>
       </c>
       <c r="P55" s="37" t="s">
         <v>106</v>
       </c>
       <c r="Q55" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P55,"pt","es")</f>
         <v>Elemento superpuesto en KML. Muestra una imagen fija en la pantalla de la aplicación (como logotipos, leyendas o brújulas) independientemente de la navegación por el mapa.</v>
       </c>
       <c r="R55" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P55,"pt","en")</f>
         <v>Overlay element in KML. Displays a fixed image on the app screen (such as logos, legends, or compasses) independent of the map navigation.</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T55" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C55, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U55" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D55, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V55" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F55, "_", " ")</f>
         <v>Kml.Sobrepor</v>
       </c>
       <c r="W55" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X55" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A55)</f>
         <v>Key-Kml-55</v>
       </c>
       <c r="Y55" s="14" t="s">
@@ -8487,7 +8187,7 @@
         <v>96</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="G56" s="32" t="s">
         <v>2</v>
@@ -8505,52 +8205,52 @@
         <v>2</v>
       </c>
       <c r="L56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C56)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D56)</f>
         <v>Esquemas</v>
       </c>
       <c r="N56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E56)</f>
         <v>KML</v>
       </c>
       <c r="O56" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F56)</f>
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="P56" s="37" t="s">
         <v>107</v>
       </c>
       <c r="Q56" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P56,"pt","es")</f>
         <v>Elemento superpuesto en KML. Asocia una foto con una ubicación geográfica específica, permitiendo navegación en gigapíxeles o vista panorámica.</v>
       </c>
       <c r="R56" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P56,"pt","en")</f>
         <v>Overlay element in KML. Associates a photo with a specific geographic location, allowing gigapixel navigation or panoramic view.</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T56" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C56, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U56" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D56, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V56" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F56, "_", " ")</f>
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="W56" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X56" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A56)</f>
         <v>Key-Kml-56</v>
       </c>
       <c r="Y56" s="14" t="s">
@@ -8589,7 +8289,7 @@
         <v>96</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G57" s="32" t="s">
         <v>2</v>
@@ -8607,52 +8307,52 @@
         <v>2</v>
       </c>
       <c r="L57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C57)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D57)</f>
         <v>Esquemas</v>
       </c>
       <c r="N57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E57)</f>
         <v>KML</v>
       </c>
       <c r="O57" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F57)</f>
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="P57" s="37" t="s">
         <v>108</v>
       </c>
       <c r="Q57" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P57,"pt","es")</f>
         <v>Elemento superpuesto en KML. Proyecta una imagen bidimensional directamente sobre la superficie terrestre, alineada por coordenadas geográficas de frontera.</v>
       </c>
       <c r="R57" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P57,"pt","en")</f>
         <v>Overlay element in KML. It projects a two-dimensional image directly onto the Earth's surface, aligned by geographic boundary coordinates.</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T57" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C57, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U57" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D57, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V57" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F57, "_", " ")</f>
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="W57" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X57" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A57)</f>
         <v>Key-Kml-57</v>
       </c>
       <c r="Y57" s="14" t="s">
@@ -8691,7 +8391,7 @@
         <v>96</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="G58" s="32" t="s">
         <v>2</v>
@@ -8709,52 +8409,52 @@
         <v>2</v>
       </c>
       <c r="L58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C58)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D58)</f>
         <v>Esquemas</v>
       </c>
       <c r="N58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E58)</f>
         <v>KML</v>
       </c>
       <c r="O58" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F58)</f>
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="P58" s="37" t="s">
         <v>105</v>
       </c>
       <c r="Q58" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P58,"pt","es")</f>
         <v>Elemento de animación en KML. Establece un rango de tiempo con &lt;begin&gt;la fecha/hora de inicio () y fin &lt;end&gt;().</v>
       </c>
       <c r="R58" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P58,"pt","en")</f>
         <v>Animation element in KML. Sets a time range with start (&lt;begin&gt;) and end () date/time&lt;end&gt;.</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T58" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C58, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U58" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D58, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V58" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F58, "_", " ")</f>
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="W58" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X58" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A58)</f>
         <v>Key-Kml-58</v>
       </c>
       <c r="Y58" s="14" t="s">
@@ -8793,7 +8493,7 @@
         <v>96</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="G59" s="32" t="s">
         <v>2</v>
@@ -8811,52 +8511,52 @@
         <v>2</v>
       </c>
       <c r="L59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C59)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D59)</f>
         <v>Esquemas</v>
       </c>
       <c r="N59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E59)</f>
         <v>KML</v>
       </c>
       <c r="O59" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F59)</f>
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="P59" s="37" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="Q59" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P59,"pt","es")</f>
         <v>Elemento KML. Define un momento que puede ser un año, una fecha o una hora. &lt;when&gt;01-08-2024&lt;/when&gt;</v>
       </c>
       <c r="R59" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P59,"pt","en")</f>
         <v>KML element. Defines a moment that can be a year, date, or time. &lt;when&gt;2024-08-01&lt;/when&gt;</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T59" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C59, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U59" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D59, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V59" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F59, "_", " ")</f>
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="W59" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X59" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A59)</f>
         <v>Key-Kml-59</v>
       </c>
       <c r="Y59" s="14" t="s">
@@ -8875,7 +8575,7 @@
         <v>2</v>
       </c>
       <c r="AD59" s="37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8895,7 +8595,7 @@
         <v>96</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G60" s="32" t="s">
         <v>2</v>
@@ -8913,52 +8613,52 @@
         <v>2</v>
       </c>
       <c r="L60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C60)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D60)</f>
         <v>Esquemas</v>
       </c>
       <c r="N60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E60)</f>
         <v>KML</v>
       </c>
       <c r="O60" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F60)</f>
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="P60" s="37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q60" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P60,"pt","es")</f>
         <v>Elemento KML. Establece un momento final en &lt;TimeSpan&gt;un . &lt;end&gt;01-08-2024&lt;/end&gt;</v>
       </c>
       <c r="R60" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P60,"pt","en")</f>
         <v>KML element. Sets an end moment in a &lt;TimeSpan&gt;. &lt;end&gt;2024-08-01&lt;/end&gt;</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T60" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C60, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U60" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D60, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V60" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F60, "_", " ")</f>
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="W60" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X60" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A60)</f>
         <v>Key-Kml-60</v>
       </c>
       <c r="Y60" s="14" t="s">
@@ -8977,7 +8677,7 @@
         <v>2</v>
       </c>
       <c r="AD60" s="37" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -8997,7 +8697,7 @@
         <v>96</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="G61" s="32" t="s">
         <v>2</v>
@@ -9015,52 +8715,52 @@
         <v>2</v>
       </c>
       <c r="L61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C61)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D61)</f>
         <v>Esquemas</v>
       </c>
       <c r="N61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E61)</f>
         <v>KML</v>
       </c>
       <c r="O61" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F61)</f>
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="P61" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q61" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P61,"pt","es")</f>
         <v>Elemento KML. Establece un momento inicial en &lt;TimeSpan&gt;un . &lt;begin&gt;01-01-2024&lt;/begin&gt;</v>
       </c>
       <c r="R61" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P61,"pt","en")</f>
         <v>KML element. Sets a starting moment in a &lt;TimeSpan&gt;. &lt;begin&gt;2024-01-01&lt;/begin&gt;</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T61" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C61, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U61" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D61, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V61" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F61, "_", " ")</f>
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="W61" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X61" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A61)</f>
         <v>Key-Kml-61</v>
       </c>
       <c r="Y61" s="14" t="s">
@@ -9079,7 +8779,7 @@
         <v>2</v>
       </c>
       <c r="AD61" s="37" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9099,7 +8799,7 @@
         <v>96</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="G62" s="32" t="s">
         <v>2</v>
@@ -9117,52 +8817,52 @@
         <v>2</v>
       </c>
       <c r="L62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", C62)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", D62)</f>
         <v>Esquemas</v>
       </c>
       <c r="N62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", E62)</f>
         <v>KML</v>
       </c>
       <c r="O62" s="13" t="str">
-        <f t="shared" si="7"/>
+        <f>CONCATENATE("", F62)</f>
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="P62" s="37" t="s">
         <v>102</v>
       </c>
       <c r="Q62" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f>_xlfn.TRANSLATE(P62,"pt","es")</f>
         <v>Elemento de animación en KML. Asocia un elemento con un punto específico en el tiempo (por ejemplo, un evento puntual).</v>
       </c>
       <c r="R62" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.TRANSLATE(P62,"pt","en")</f>
         <v>Animation element in KML. Associates an element with a specific point in time (e.g., point event).</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T62" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(C62, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U62" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f>SUBSTITUTE(D62, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V62" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f>SUBSTITUTE(F62, "_", " ")</f>
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="W62" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X62" s="30" t="str">
-        <f t="shared" si="4"/>
+        <f>CONCATENATE("Key-Kml-",A62)</f>
         <v>Key-Kml-62</v>
       </c>
       <c r="Y62" s="14" t="s">
@@ -9185,21 +8885,24 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD62">
+    <sortCondition ref="F30:F62"/>
+  </sortState>
   <conditionalFormatting sqref="A2:B62">
-    <cfRule type="cellIs" dxfId="22" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F62">
-    <cfRule type="duplicateValues" dxfId="21" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9351,7 +9054,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9422,22 +9125,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="12" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9453,9 +9156,10 @@
     <col min="1" max="1" width="2.83203125" style="55" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.6640625" style="38" customWidth="1"/>
     <col min="3" max="3" width="11.83203125" style="52" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" style="52" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="52" customWidth="1"/>
     <col min="5" max="5" width="8" style="52" customWidth="1"/>
-    <col min="6" max="7" width="8.6640625" style="52" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" style="52" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" style="52" customWidth="1"/>
     <col min="8" max="8" width="5.6640625" style="52" customWidth="1"/>
     <col min="9" max="9" width="5.33203125" style="52" customWidth="1"/>
     <col min="10" max="10" width="8.5" style="52" customWidth="1"/>
@@ -9546,10 +9250,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="39" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C2" s="56" t="s">
-        <v>245</v>
+        <v>322</v>
       </c>
       <c r="D2" s="46" t="s">
         <v>2</v>
@@ -9585,7 +9289,7 @@
         <v>139</v>
       </c>
       <c r="O2" s="57" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="P2" s="49" t="s">
         <v>2</v>
@@ -9617,16 +9321,16 @@
         <v>3</v>
       </c>
       <c r="B3" s="39" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C3" s="56" t="s">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="54" t="s">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>285</v>
       </c>
       <c r="F3" s="46" t="s">
         <v>2</v>
@@ -9656,7 +9360,7 @@
         <v>139</v>
       </c>
       <c r="O3" s="57" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="P3" s="49" t="s">
         <v>2</v>
@@ -9688,16 +9392,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C4" s="56" t="s">
-        <v>247</v>
+        <v>324</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="54" t="s">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>282</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>2</v>
@@ -9727,7 +9431,7 @@
         <v>139</v>
       </c>
       <c r="O4" s="57" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="P4" s="49" t="s">
         <v>2</v>
@@ -9759,16 +9463,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="39" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C5" s="56" t="s">
         <v>143</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="54" t="s">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>283</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>2</v>
@@ -9798,7 +9502,7 @@
         <v>139</v>
       </c>
       <c r="O5" s="57" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="P5" s="49" t="s">
         <v>2</v>
@@ -9830,16 +9534,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="C6" s="56" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="54" t="s">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>304</v>
       </c>
       <c r="F6" s="46" t="s">
         <v>2</v>
@@ -9869,7 +9573,7 @@
         <v>139</v>
       </c>
       <c r="O6" s="57" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="P6" s="49" t="s">
         <v>2</v>
@@ -9901,10 +9605,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D7" s="46" t="s">
         <v>2</v>
@@ -9940,7 +9644,7 @@
         <v>139</v>
       </c>
       <c r="O7" s="57" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="P7" s="49" t="s">
         <v>2</v>
@@ -9972,16 +9676,16 @@
         <v>8</v>
       </c>
       <c r="B8" s="39" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C8" s="56" t="s">
         <v>155</v>
       </c>
       <c r="D8" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E8" s="39" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>2</v>
@@ -10008,10 +9712,10 @@
         <v>2</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O8" s="48" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="P8" s="49" t="s">
         <v>2</v>
@@ -10043,22 +9747,22 @@
         <v>9</v>
       </c>
       <c r="B9" s="39" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C9" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="D9" s="46" t="s">
-        <v>295</v>
+      <c r="D9" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E9" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="F9" s="51" t="s">
-        <v>296</v>
+        <v>282</v>
+      </c>
+      <c r="F9" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G9" s="39" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="H9" s="46" t="s">
         <v>2</v>
@@ -10079,10 +9783,10 @@
         <v>2</v>
       </c>
       <c r="N9" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O9" s="48" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="P9" s="49" t="s">
         <v>2</v>
@@ -10114,22 +9818,22 @@
         <v>10</v>
       </c>
       <c r="B10" s="39" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="C10" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="46" t="s">
-        <v>295</v>
+      <c r="D10" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E10" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="F10" s="51" t="s">
-        <v>296</v>
+        <v>283</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G10" s="39" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H10" s="46" t="s">
         <v>2</v>
@@ -10150,10 +9854,10 @@
         <v>2</v>
       </c>
       <c r="N10" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O10" s="48" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="P10" s="49" t="s">
         <v>2</v>
@@ -10185,22 +9889,22 @@
         <v>11</v>
       </c>
       <c r="B11" s="39" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C11" s="56" t="s">
         <v>157</v>
       </c>
-      <c r="D11" s="46" t="s">
-        <v>295</v>
+      <c r="D11" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>298</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>296</v>
+        <v>283</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H11" s="46" t="s">
         <v>2</v>
@@ -10221,10 +9925,10 @@
         <v>2</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O11" s="48" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="P11" s="49" t="s">
         <v>2</v>
@@ -10256,22 +9960,22 @@
         <v>12</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C12" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D12" s="46" t="s">
-        <v>295</v>
+      <c r="D12" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E12" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="F12" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F12" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H12" s="46" t="s">
         <v>2</v>
@@ -10280,28 +9984,28 @@
         <v>2</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K12" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L12" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M12" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O12" s="48" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="P12" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q12" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R12" s="49" t="s">
         <v>2</v>
@@ -10327,22 +10031,22 @@
         <v>13</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C13" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D13" s="46" t="s">
-        <v>295</v>
+      <c r="D13" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H13" s="46" t="s">
         <v>2</v>
@@ -10351,28 +10055,28 @@
         <v>2</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K13" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L13" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M13" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O13" s="48" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="P13" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q13" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R13" s="49" t="s">
         <v>2</v>
@@ -10398,22 +10102,22 @@
         <v>14</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C14" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="46" t="s">
-        <v>295</v>
+      <c r="D14" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="F14" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F14" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H14" s="46" t="s">
         <v>2</v>
@@ -10422,28 +10126,28 @@
         <v>2</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L14" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M14" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N14" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O14" s="48" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="P14" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q14" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R14" s="49" t="s">
         <v>2</v>
@@ -10469,22 +10173,22 @@
         <v>15</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C15" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>295</v>
+      <c r="D15" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="F15" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G15" s="39" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H15" s="46" t="s">
         <v>2</v>
@@ -10493,28 +10197,28 @@
         <v>2</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K15" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L15" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M15" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N15" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O15" s="48" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="P15" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q15" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R15" s="49" t="s">
         <v>2</v>
@@ -10540,52 +10244,52 @@
         <v>16</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="C16" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D16" s="46" t="s">
-        <v>295</v>
+      <c r="D16" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E16" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>301</v>
+      </c>
+      <c r="H16" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="J16" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="L16" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="M16" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="O16" s="48" t="s">
         <v>311</v>
-      </c>
-      <c r="F16" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>293</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="K16" s="39" t="s">
-        <v>313</v>
-      </c>
-      <c r="L16" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="N16" s="47" t="s">
-        <v>329</v>
-      </c>
-      <c r="O16" s="48" t="s">
-        <v>321</v>
       </c>
       <c r="P16" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q16" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R16" s="49" t="s">
         <v>2</v>
@@ -10611,22 +10315,22 @@
         <v>17</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="C17" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="46" t="s">
-        <v>295</v>
+      <c r="D17" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>311</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F17" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G17" s="39" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="H17" s="46" t="s">
         <v>2</v>
@@ -10635,28 +10339,28 @@
         <v>2</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K17" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L17" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M17" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O17" s="48" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="P17" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q17" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R17" s="49" t="s">
         <v>2</v>
@@ -10682,22 +10386,22 @@
         <v>18</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="C18" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="46" t="s">
-        <v>295</v>
+      <c r="D18" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E18" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F18" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G18" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H18" s="46" t="s">
         <v>2</v>
@@ -10706,28 +10410,28 @@
         <v>2</v>
       </c>
       <c r="J18" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K18" s="39" t="s">
+        <v>303</v>
+      </c>
+      <c r="L18" s="51" t="s">
+        <v>286</v>
+      </c>
+      <c r="M18" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="N18" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="O18" s="48" t="s">
         <v>313</v>
-      </c>
-      <c r="L18" s="51" t="s">
-        <v>296</v>
-      </c>
-      <c r="M18" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="N18" s="47" t="s">
-        <v>329</v>
-      </c>
-      <c r="O18" s="48" t="s">
-        <v>323</v>
       </c>
       <c r="P18" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q18" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R18" s="49" t="s">
         <v>2</v>
@@ -10753,22 +10457,22 @@
         <v>19</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C19" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="46" t="s">
-        <v>295</v>
+      <c r="D19" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E19" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F19" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F19" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G19" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H19" s="46" t="s">
         <v>2</v>
@@ -10777,28 +10481,28 @@
         <v>2</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K19" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L19" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M19" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="N19" s="47" t="s">
+        <v>319</v>
+      </c>
+      <c r="O19" s="48" t="s">
         <v>314</v>
-      </c>
-      <c r="N19" s="47" t="s">
-        <v>329</v>
-      </c>
-      <c r="O19" s="48" t="s">
-        <v>324</v>
       </c>
       <c r="P19" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q19" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R19" s="49" t="s">
         <v>2</v>
@@ -10824,22 +10528,22 @@
         <v>20</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="C20" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="46" t="s">
-        <v>295</v>
+      <c r="D20" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E20" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F20" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G20" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H20" s="46" t="s">
         <v>2</v>
@@ -10848,28 +10552,28 @@
         <v>2</v>
       </c>
       <c r="J20" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K20" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L20" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M20" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N20" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O20" s="48" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="P20" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q20" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R20" s="49" t="s">
         <v>2</v>
@@ -10895,22 +10599,22 @@
         <v>21</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="C21" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D21" s="46" t="s">
-        <v>295</v>
+      <c r="D21" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E21" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F21" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G21" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H21" s="46" t="s">
         <v>2</v>
@@ -10919,28 +10623,28 @@
         <v>2</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K21" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L21" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M21" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N21" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O21" s="48" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="P21" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q21" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R21" s="49" t="s">
         <v>2</v>
@@ -10966,22 +10670,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C22" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D22" s="46" t="s">
-        <v>295</v>
+      <c r="D22" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E22" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F22" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F22" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G22" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H22" s="46" t="s">
         <v>2</v>
@@ -10990,28 +10694,28 @@
         <v>2</v>
       </c>
       <c r="J22" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K22" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L22" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M22" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N22" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O22" s="48" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="P22" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q22" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R22" s="49" t="s">
         <v>2</v>
@@ -11037,22 +10741,22 @@
         <v>23</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="C23" s="56" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="46" t="s">
-        <v>295</v>
+      <c r="D23" s="51" t="s">
+        <v>286</v>
       </c>
       <c r="E23" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="F23" s="51" t="s">
-        <v>296</v>
+        <v>284</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>331</v>
       </c>
       <c r="G23" s="39" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="H23" s="46" t="s">
         <v>2</v>
@@ -11061,28 +10765,28 @@
         <v>2</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="K23" s="39" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="L23" s="51" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="M23" s="39" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="N23" s="47" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="O23" s="48" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="P23" s="47" t="s">
         <v>139</v>
       </c>
       <c r="Q23" s="50" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="R23" s="49" t="s">
         <v>2</v>
@@ -11106,38 +10810,54 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B10:B1048576 B1:B8">
-    <cfRule type="duplicateValues" dxfId="11" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D1">
+    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="8" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1">
+    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="7" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="duplicateValues" dxfId="6" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="5" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="duplicateValues" dxfId="4" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="duplicateValues" dxfId="3" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L1">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/BIM/Ontologia_Kml_2x2.xlsx
+++ b/Versão5/BIM/Ontologia_Kml_2x2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E07971-A7FE-4D46-BB61-371AA2082D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4785289B-A6E6-4186-8404-DDC52FEBD042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="4" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="340">
   <si>
     <t>Organização</t>
   </si>
@@ -1072,13 +1072,37 @@
   </si>
   <si>
     <t>é.marcador.interno.de</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -1163,8 +1187,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1309,6 +1339,12 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1397,7 +1433,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1572,12 +1608,40 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1587,6 +1651,22 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1667,24 +1747,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2464,7 +2526,7 @@
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46255.588563194447</v>
+        <v>46258.594610069442</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
@@ -2548,8 +2610,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B21B10B-C8BF-4318-B9A8-B9240E89A4C8}">
-  <dimension ref="A1:AD62"/>
-  <sheetFormatPr defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AD63"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.5" customWidth="1"/>
@@ -2577,7 +2639,7 @@
     <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="58">
         <v>1</v>
       </c>
@@ -2669,7 +2731,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -2704,19 +2766,19 @@
         <v>2</v>
       </c>
       <c r="L2" s="13" t="str">
-        <f>CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:L33" si="0">CONCATENATE("", C2)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M2" s="13" t="str">
-        <f>CONCATENATE("", D2)</f>
+        <f t="shared" ref="M2:M33" si="1">CONCATENATE("", D2)</f>
         <v>Esquemas</v>
       </c>
       <c r="N2" s="13" t="str">
-        <f>CONCATENATE("", E2)</f>
+        <f t="shared" ref="N2:N33" si="2">CONCATENATE("", E2)</f>
         <v>KML</v>
       </c>
       <c r="O2" s="13" t="str">
-        <f>CONCATENATE("", F2)</f>
+        <f t="shared" ref="O2:O33" si="3">CONCATENATE("", F2)</f>
         <v>Kml.Arquivo</v>
       </c>
       <c r="P2" s="37" t="s">
@@ -2727,29 +2789,29 @@
         <v>El elemento raíz de agrupación del archivo KML que contiene la declaración de los espacios de nombres y envuelve todo el contenido geográfico.</v>
       </c>
       <c r="R2" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="R2:R33" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>The root grouping element of the KML file that contains the declaration of the namespaces and wraps all geographic content.</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T2" s="14" t="str">
-        <f>SUBSTITUTE(C2, "_", " ")</f>
+        <f t="shared" ref="T2:T33" si="5">SUBSTITUTE(C2, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U2" s="14" t="str">
-        <f>SUBSTITUTE(D2, "_", " ")</f>
+        <f t="shared" ref="U2:U33" si="6">SUBSTITUTE(D2, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V2" s="14" t="str">
-        <f>SUBSTITUTE(F2, "_", " ")</f>
+        <f t="shared" ref="V2:V33" si="7">SUBSTITUTE(F2, "_", " ")</f>
         <v>Kml.Arquivo</v>
       </c>
       <c r="W2" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X2" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A2)</f>
+        <f t="shared" ref="X2:X33" si="8">CONCATENATE("Key-Kml-",A2)</f>
         <v>Key-Kml-2</v>
       </c>
       <c r="Y2" s="14" t="s">
@@ -2771,7 +2833,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -2806,19 +2868,19 @@
         <v>2</v>
       </c>
       <c r="L3" s="13" t="str">
-        <f>CONCATENATE("", C3)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M3" s="13" t="str">
-        <f>CONCATENATE("", D3)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N3" s="13" t="str">
-        <f>CONCATENATE("", E3)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O3" s="13" t="str">
-        <f>CONCATENATE("", F3)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Atributo</v>
       </c>
       <c r="P3" s="37" t="s">
@@ -2828,29 +2890,29 @@
         <v>142</v>
       </c>
       <c r="R3" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P3,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Attribute to qualify a KML element.</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T3" s="14" t="str">
-        <f>SUBSTITUTE(C3, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U3" s="14" t="str">
-        <f>SUBSTITUTE(D3, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V3" s="14" t="str">
-        <f>SUBSTITUTE(F3, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Atributo</v>
       </c>
       <c r="W3" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X3" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A3)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-3</v>
       </c>
       <c r="Y3" s="14" t="s">
@@ -2872,7 +2934,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -2907,52 +2969,52 @@
         <v>2</v>
       </c>
       <c r="L4" s="13" t="str">
-        <f>CONCATENATE("", C4)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M4" s="13" t="str">
-        <f>CONCATENATE("", D4)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N4" s="13" t="str">
-        <f>CONCATENATE("", E4)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O4" s="13" t="str">
-        <f>CONCATENATE("", F4)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box</v>
       </c>
       <c r="P4" s="37" t="s">
         <v>182</v>
       </c>
       <c r="Q4" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","es")</f>
+        <f t="shared" ref="Q4:Q19" si="9">_xlfn.TRANSLATE(P4,"pt","es")</f>
         <v>Elemento KML. Define una región con 4 límites &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
       </c>
       <c r="R4" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Defines a region with 4 boundaries &lt;LatLonBox&gt;&lt;north&gt;37.80005&lt;/north&gt; &lt;south&gt;37.50005&lt;/south&gt; &lt;east&gt;120.373033&lt;/east&gt; &lt;west&gt;120.376033&lt;/west&gt; &lt;rotation&gt;0&lt;/rotation&gt;&lt;/LatLonBox&gt;</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T4" s="14" t="str">
-        <f>SUBSTITUTE(C4, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U4" s="14" t="str">
-        <f>SUBSTITUTE(D4, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V4" s="14" t="str">
-        <f>SUBSTITUTE(F4, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box</v>
       </c>
       <c r="W4" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X4" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A4)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-4</v>
       </c>
       <c r="Y4" s="14" t="s">
@@ -2974,7 +3036,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -3009,52 +3071,52 @@
         <v>2</v>
       </c>
       <c r="L5" s="13" t="str">
-        <f>CONCATENATE("", C5)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M5" s="13" t="str">
-        <f>CONCATENATE("", D5)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N5" s="13" t="str">
-        <f>CONCATENATE("", E5)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O5" s="13" t="str">
-        <f>CONCATENATE("", F5)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="P5" s="37" t="s">
         <v>180</v>
       </c>
       <c r="Q5" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P5,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Fija la longitud del límite oriental de una región &lt;east&gt;120.373033&lt;/east&gt;</v>
       </c>
       <c r="R5" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P5,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets the longitude of the eastern boundary of a region &lt;east&gt;120.373033&lt;/east&gt;</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T5" s="14" t="str">
-        <f>SUBSTITUTE(C5, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U5" s="14" t="str">
-        <f>SUBSTITUTE(D5, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V5" s="14" t="str">
-        <f>SUBSTITUTE(F5, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box.Cardinal.Leste</v>
       </c>
       <c r="W5" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X5" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A5)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-5</v>
       </c>
       <c r="Y5" s="14" t="s">
@@ -3076,7 +3138,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -3111,52 +3173,52 @@
         <v>2</v>
       </c>
       <c r="L6" s="13" t="str">
-        <f>CONCATENATE("", C6)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M6" s="13" t="str">
-        <f>CONCATENATE("", D6)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N6" s="13" t="str">
-        <f>CONCATENATE("", E6)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O6" s="13" t="str">
-        <f>CONCATENATE("", F6)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="P6" s="37" t="s">
         <v>178</v>
       </c>
       <c r="Q6" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P6,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Fija la latitud del límite norte de una región &lt;north&gt;37.80005&lt;/north&gt;</v>
       </c>
       <c r="R6" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P6,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets the latitude of the northern boundary of a region &lt;north&gt;37.80005&lt;/north&gt;</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T6" s="14" t="str">
-        <f>SUBSTITUTE(C6, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U6" s="14" t="str">
-        <f>SUBSTITUTE(D6, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V6" s="14" t="str">
-        <f>SUBSTITUTE(F6, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box.Cardinal.Norte</v>
       </c>
       <c r="W6" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X6" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A6)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-6</v>
       </c>
       <c r="Y6" s="14" t="s">
@@ -3178,7 +3240,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -3213,52 +3275,52 @@
         <v>2</v>
       </c>
       <c r="L7" s="13" t="str">
-        <f>CONCATENATE("", C7)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M7" s="13" t="str">
-        <f>CONCATENATE("", D7)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N7" s="13" t="str">
-        <f>CONCATENATE("", E7)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O7" s="13" t="str">
-        <f>CONCATENATE("", F7)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="P7" s="37" t="s">
         <v>181</v>
       </c>
       <c r="Q7" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define la longitud del límite occidental de una región &lt;west&gt;120.376033&lt;/west&gt;</v>
       </c>
       <c r="R7" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Defines the longitude of the western boundary of a region &lt;west&gt;120.376033&lt;/west&gt;</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T7" s="14" t="str">
-        <f>SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U7" s="14" t="str">
-        <f>SUBSTITUTE(D7, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V7" s="14" t="str">
-        <f>SUBSTITUTE(F7, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box.Cardinal.Oeste</v>
       </c>
       <c r="W7" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X7" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A7)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-7</v>
       </c>
       <c r="Y7" s="14" t="s">
@@ -3280,7 +3342,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -3315,52 +3377,52 @@
         <v>2</v>
       </c>
       <c r="L8" s="13" t="str">
-        <f>CONCATENATE("", C8)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M8" s="13" t="str">
-        <f>CONCATENATE("", D8)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N8" s="13" t="str">
-        <f>CONCATENATE("", E8)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O8" s="13" t="str">
-        <f>CONCATENATE("", F8)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="P8" s="37" t="s">
         <v>179</v>
       </c>
       <c r="Q8" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P8,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Establece la latitud del límite sur de una región &lt;south&gt;37.50005&lt;/south&gt;</v>
       </c>
       <c r="R8" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets the latitude of the southern boundary of a region &lt;south&gt;37.50005&lt;/south&gt;</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T8" s="14" t="str">
-        <f>SUBSTITUTE(C8, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U8" s="14" t="str">
-        <f>SUBSTITUTE(D8, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V8" s="14" t="str">
-        <f>SUBSTITUTE(F8, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box.Cardinal.Sul</v>
       </c>
       <c r="W8" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X8" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A8)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-8</v>
       </c>
       <c r="Y8" s="14" t="s">
@@ -3382,7 +3444,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -3417,52 +3479,52 @@
         <v>2</v>
       </c>
       <c r="L9" s="13" t="str">
-        <f>CONCATENATE("", C9)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M9" s="13" t="str">
-        <f>CONCATENATE("", D9)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N9" s="13" t="str">
-        <f>CONCATENATE("", E9)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O9" s="13" t="str">
-        <f>CONCATENATE("", F9)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Box.Rotado</v>
       </c>
       <c r="P9" s="37" t="s">
         <v>183</v>
       </c>
       <c r="Q9" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P9,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Establece una &lt;rotation&gt;rotación 45&lt;/rotation&gt;</v>
       </c>
       <c r="R9" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets a &lt;rotation&gt;rotation 45&lt;/rotation&gt;</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T9" s="14" t="str">
-        <f>SUBSTITUTE(C9, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U9" s="14" t="str">
-        <f>SUBSTITUTE(D9, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V9" s="14" t="str">
-        <f>SUBSTITUTE(F9, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Box.Rotado</v>
       </c>
       <c r="W9" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X9" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A9)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-9</v>
       </c>
       <c r="Y9" s="14" t="s">
@@ -3484,7 +3546,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -3519,52 +3581,52 @@
         <v>2</v>
       </c>
       <c r="L10" s="13" t="str">
-        <f>CONCATENATE("", C10)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M10" s="13" t="str">
-        <f>CONCATENATE("", D10)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N10" s="13" t="str">
-        <f>CONCATENATE("", E10)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O10" s="13" t="str">
-        <f>CONCATENATE("", F10)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Camara</v>
       </c>
       <c r="P10" s="37" t="s">
         <v>103</v>
       </c>
       <c r="Q10" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P10,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento de visualización en KML. Establece la posición y orientación exactas de la propia cámara en el espacio tridimensional (latitud, longitud, altitud, rotación e inclinación).</v>
       </c>
       <c r="R10" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P10,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Visualization element in KML. Sets the exact position and orientation of the camera itself in three-dimensional space (latitude, longitude, altitude, rotation, and tilt).</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T10" s="14" t="str">
-        <f>SUBSTITUTE(C10, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U10" s="14" t="str">
-        <f>SUBSTITUTE(D10, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V10" s="14" t="str">
-        <f>SUBSTITUTE(F10, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Camara</v>
       </c>
       <c r="W10" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X10" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A10)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-10</v>
       </c>
       <c r="Y10" s="14" t="s">
@@ -3586,7 +3648,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -3621,52 +3683,52 @@
         <v>2</v>
       </c>
       <c r="L11" s="13" t="str">
-        <f>CONCATENATE("", C11)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M11" s="13" t="str">
-        <f>CONCATENATE("", D11)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N11" s="13" t="str">
-        <f>CONCATENATE("", E11)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O11" s="13" t="str">
-        <f>CONCATENATE("", F11)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Camara.Alcance</v>
       </c>
       <c r="P11" s="37" t="s">
         <v>326</v>
       </c>
       <c r="Q11" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P11,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Especifica la distancia focal de la cámara hasta el punto de interés en metros. &lt;range&gt;1000&lt;/range&gt;</v>
       </c>
       <c r="R11" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P11,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Specifies the focal length of the camera to the point of interest in meters. &lt;range&gt;1000&lt;/range&gt;</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T11" s="14" t="str">
-        <f>SUBSTITUTE(C11, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U11" s="14" t="str">
-        <f>SUBSTITUTE(D11, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V11" s="14" t="str">
-        <f>SUBSTITUTE(F11, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Camara.Alcance</v>
       </c>
       <c r="W11" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X11" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A11)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-11</v>
       </c>
       <c r="Y11" s="14" t="s">
@@ -3688,7 +3750,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -3723,52 +3785,52 @@
         <v>2</v>
       </c>
       <c r="L12" s="13" t="str">
-        <f>CONCATENATE("", C12)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M12" s="13" t="str">
-        <f>CONCATENATE("", D12)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N12" s="13" t="str">
-        <f>CONCATENATE("", E12)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O12" s="13" t="str">
-        <f>CONCATENATE("", F12)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Camara.Alvo</v>
       </c>
       <c r="P12" s="37" t="s">
         <v>104</v>
       </c>
       <c r="Q12" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P12,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento de visualización en KML. Establece la vista posicionando la cámara respecto a un punto geográfico objetivo (incluyendo distancia, inclinación y rumbo).</v>
       </c>
       <c r="R12" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P12,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Visualization element in KML. Sets the view by positioning the camera relative to a target geographic point (including distance, tilt, and heading).</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T12" s="14" t="str">
-        <f>SUBSTITUTE(C12, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U12" s="14" t="str">
-        <f>SUBSTITUTE(D12, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V12" s="14" t="str">
-        <f>SUBSTITUTE(F12, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Camara.Alvo</v>
       </c>
       <c r="W12" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X12" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A12)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-12</v>
       </c>
       <c r="Y12" s="14" t="s">
@@ -3790,7 +3852,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -3825,52 +3887,52 @@
         <v>2</v>
       </c>
       <c r="L13" s="13" t="str">
-        <f>CONCATENATE("", C13)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M13" s="13" t="str">
-        <f>CONCATENATE("", D13)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N13" s="13" t="str">
-        <f>CONCATENATE("", E13)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O13" s="13" t="str">
-        <f>CONCATENATE("", F13)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Camara.Azimut</v>
       </c>
       <c r="P13" s="37" t="s">
         <v>176</v>
       </c>
       <c r="Q13" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P13,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Establece la dirección del acimut en sentido horario y en grados decimales (Norte = 0, Este = 90, Sur = 180, Oeste = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
       </c>
       <c r="R13" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P13,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets the azimuth direction clockwise and in decimal degrees (North = 0, East = 90, South = 180, West = 270). &lt;heading&gt;0&lt;/heading&gt;</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T13" s="14" t="str">
-        <f>SUBSTITUTE(C13, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U13" s="14" t="str">
-        <f>SUBSTITUTE(D13, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V13" s="14" t="str">
-        <f>SUBSTITUTE(F13, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Camara.Azimut</v>
       </c>
       <c r="W13" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X13" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A13)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-13</v>
       </c>
       <c r="Y13" s="14" t="s">
@@ -3892,7 +3954,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -3927,52 +3989,52 @@
         <v>2</v>
       </c>
       <c r="L14" s="13" t="str">
-        <f>CONCATENATE("", C14)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M14" s="13" t="str">
-        <f>CONCATENATE("", D14)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N14" s="13" t="str">
-        <f>CONCATENATE("", E14)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O14" s="13" t="str">
-        <f>CONCATENATE("", F14)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Dado.Estendido</v>
       </c>
       <c r="P14" s="37" t="s">
         <v>214</v>
       </c>
       <c r="Q14" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P14,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define un conjunto de datos extendido (personalizado). &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
       </c>
       <c r="R14" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P14,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Defines an extended (custom) dataset. &lt;ExtendendData&gt; ..... &lt;/ExtendedData&gt;</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T14" s="14" t="str">
-        <f>SUBSTITUTE(C14, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U14" s="14" t="str">
-        <f>SUBSTITUTE(D14, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V14" s="14" t="str">
-        <f>SUBSTITUTE(F14, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Dado.Estendido</v>
       </c>
       <c r="W14" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X14" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A14)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-14</v>
       </c>
       <c r="Y14" s="14" t="s">
@@ -3994,7 +4056,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -4029,52 +4091,52 @@
         <v>2</v>
       </c>
       <c r="L15" s="13" t="str">
-        <f>CONCATENATE("", C15)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M15" s="13" t="str">
-        <f>CONCATENATE("", D15)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N15" s="13" t="str">
-        <f>CONCATENATE("", E15)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O15" s="13" t="str">
-        <f>CONCATENATE("", F15)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="P15" s="37" t="s">
         <v>218</v>
       </c>
       <c r="Q15" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define un dato personalizado dentro de ExtendenData &lt;Nombre de datos='doname'&lt;value&gt;&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
       </c>
       <c r="R15" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P15,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Define a custom data within ExtendenData &lt;Data name='doname'&gt;&lt;value&gt;1&lt;/value&gt;&lt;/Data&gt;</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T15" s="14" t="str">
-        <f>SUBSTITUTE(C15, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U15" s="14" t="str">
-        <f>SUBSTITUTE(D15, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V15" s="14" t="str">
-        <f>SUBSTITUTE(F15, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Dado.Estendido.Dado</v>
       </c>
       <c r="W15" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X15" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A15)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-15</v>
       </c>
       <c r="Y15" s="14" t="s">
@@ -4096,7 +4158,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -4131,52 +4193,52 @@
         <v>2</v>
       </c>
       <c r="L16" s="13" t="str">
-        <f>CONCATENATE("", C16)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M16" s="13" t="str">
-        <f>CONCATENATE("", D16)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N16" s="13" t="str">
-        <f>CONCATENATE("", E16)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O16" s="13" t="str">
-        <f>CONCATENATE("", F16)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="P16" s="37" t="s">
         <v>220</v>
       </c>
       <c r="Q16" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P16,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define un dato plano personalizado dentro de ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
       </c>
       <c r="R16" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P16,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Define a custom flat data inside ExtendenData &lt;SimpleData name='Elevation'&gt;10000&lt;/SimpleData&gt;</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T16" s="14" t="str">
-        <f>SUBSTITUTE(C16, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U16" s="14" t="str">
-        <f>SUBSTITUTE(D16, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V16" s="14" t="str">
-        <f>SUBSTITUTE(F16, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Dado.Estendido.Dado.Simples</v>
       </c>
       <c r="W16" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X16" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A16)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-16</v>
       </c>
       <c r="Y16" s="14" t="s">
@@ -4198,7 +4260,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -4233,52 +4295,52 @@
         <v>2</v>
       </c>
       <c r="L17" s="13" t="str">
-        <f>CONCATENATE("", C17)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M17" s="13" t="str">
-        <f>CONCATENATE("", D17)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N17" s="13" t="str">
-        <f>CONCATENATE("", E17)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O17" s="13" t="str">
-        <f>CONCATENATE("", F17)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="P17" s="37" t="s">
         <v>224</v>
       </c>
       <c r="Q17" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P17,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define un diseño &lt;Schema&gt; personalizado ..... &lt;/Schema&gt;</v>
       </c>
       <c r="R17" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P17,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Define a custom layout &lt;Schema&gt; ..... &lt;/Schema&gt;</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T17" s="14" t="str">
-        <f>SUBSTITUTE(C17, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U17" s="14" t="str">
-        <f>SUBSTITUTE(D17, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V17" s="14" t="str">
-        <f>SUBSTITUTE(F17, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Dado.Estendido.Esquema</v>
       </c>
       <c r="W17" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X17" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A17)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-17</v>
       </c>
       <c r="Y17" s="14" t="s">
@@ -4300,7 +4362,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="31">
         <v>18</v>
       </c>
@@ -4335,52 +4397,52 @@
         <v>2</v>
       </c>
       <c r="L18" s="13" t="str">
-        <f>CONCATENATE("", C18)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M18" s="13" t="str">
-        <f>CONCATENATE("", D18)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N18" s="13" t="str">
-        <f>CONCATENATE("", E18)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O18" s="13" t="str">
-        <f>CONCATENATE("", F18)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="P18" s="37" t="s">
         <v>223</v>
       </c>
       <c r="Q18" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P18,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>Elemento KML. Define un dato &lt;Schema&gt; asociado a uno para añadir datos personalizados tipados a un elemento KML.</v>
       </c>
       <c r="R18" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P18,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Defines a piece of data associated &lt;Schema&gt; with one to add typed custom data to a KML element.</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T18" s="14" t="str">
-        <f>SUBSTITUTE(C18, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U18" s="14" t="str">
-        <f>SUBSTITUTE(D18, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V18" s="14" t="str">
-        <f>SUBSTITUTE(F18, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Dado.Estendido.Esquema.Dado</v>
       </c>
       <c r="W18" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X18" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A18)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-18</v>
       </c>
       <c r="Y18" s="14" t="s">
@@ -4402,7 +4464,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="31">
         <v>19</v>
       </c>
@@ -4437,52 +4499,52 @@
         <v>2</v>
       </c>
       <c r="L19" s="13" t="str">
-        <f>CONCATENATE("", C19)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M19" s="13" t="str">
-        <f>CONCATENATE("", D19)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N19" s="13" t="str">
-        <f>CONCATENATE("", E19)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O19" s="13" t="str">
-        <f>CONCATENATE("", F19)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Documento</v>
       </c>
       <c r="P19" s="37" t="s">
         <v>239</v>
       </c>
       <c r="Q19" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P19,"pt","es")</f>
+        <f t="shared" si="9"/>
         <v>KML que agrupa contenido geográfico, estilos y esquemas asociados. Es fundamental cuando el archivo contiene múltiples objetos o estilos reutilizables.</v>
       </c>
       <c r="R19" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P19,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML bundler of geographic content, styles, and associated schemas. It is critical when the file contains multiple reusable objects or styles.</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T19" s="14" t="str">
-        <f>SUBSTITUTE(C19, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U19" s="14" t="str">
-        <f>SUBSTITUTE(D19, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V19" s="14" t="str">
-        <f>SUBSTITUTE(F19, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Documento</v>
       </c>
       <c r="W19" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X19" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A19)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-19</v>
       </c>
       <c r="Y19" s="14" t="s">
@@ -4504,7 +4566,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="31">
         <v>20</v>
       </c>
@@ -4539,19 +4601,19 @@
         <v>2</v>
       </c>
       <c r="L20" s="13" t="str">
-        <f>CONCATENATE("", C20)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M20" s="13" t="str">
-        <f>CONCATENATE("", D20)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N20" s="13" t="str">
-        <f>CONCATENATE("", E20)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O20" s="13" t="str">
-        <f>CONCATENATE("", F20)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N0</v>
       </c>
       <c r="P20" s="37" t="s">
@@ -4561,29 +4623,29 @@
         <v>146</v>
       </c>
       <c r="R20" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A KML element of level 0 Root (&lt;KML&gt;).</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T20" s="14" t="str">
-        <f>SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U20" s="14" t="str">
-        <f>SUBSTITUTE(D20, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V20" s="14" t="str">
-        <f>SUBSTITUTE(F20, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N0</v>
       </c>
       <c r="W20" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X20" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A20)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-20</v>
       </c>
       <c r="Y20" s="14" t="s">
@@ -4605,7 +4667,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="31">
         <v>21</v>
       </c>
@@ -4640,19 +4702,19 @@
         <v>2</v>
       </c>
       <c r="L21" s="13" t="str">
-        <f>CONCATENATE("", C21)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M21" s="13" t="str">
-        <f>CONCATENATE("", D21)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N21" s="13" t="str">
-        <f>CONCATENATE("", E21)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O21" s="13" t="str">
-        <f>CONCATENATE("", F21)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N1</v>
       </c>
       <c r="P21" s="37" t="s">
@@ -4662,29 +4724,29 @@
         <v>147</v>
       </c>
       <c r="R21" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A level 1 KML element (&lt;Document&gt; and &lt;Folder&gt;).</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T21" s="14" t="str">
-        <f>SUBSTITUTE(C21, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U21" s="14" t="str">
-        <f>SUBSTITUTE(D21, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V21" s="14" t="str">
-        <f>SUBSTITUTE(F21, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N1</v>
       </c>
       <c r="W21" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X21" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A21)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-21</v>
       </c>
       <c r="Y21" s="14" t="s">
@@ -4706,7 +4768,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -4741,19 +4803,19 @@
         <v>2</v>
       </c>
       <c r="L22" s="13" t="str">
-        <f>CONCATENATE("", C22)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M22" s="13" t="str">
-        <f>CONCATENATE("", D22)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N22" s="13" t="str">
-        <f>CONCATENATE("", E22)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O22" s="13" t="str">
-        <f>CONCATENATE("", F22)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N2</v>
       </c>
       <c r="P22" s="37" t="s">
@@ -4763,29 +4825,29 @@
         <v>148</v>
       </c>
       <c r="R22" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P22,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A level 2 KML element (&lt;Placemark&gt;, &lt;GroundOverlay&gt;...).</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T22" s="14" t="str">
-        <f>SUBSTITUTE(C22, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U22" s="14" t="str">
-        <f>SUBSTITUTE(D22, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V22" s="14" t="str">
-        <f>SUBSTITUTE(F22, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N2</v>
       </c>
       <c r="W22" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X22" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A22)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-22</v>
       </c>
       <c r="Y22" s="14" t="s">
@@ -4807,7 +4869,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -4842,19 +4904,19 @@
         <v>2</v>
       </c>
       <c r="L23" s="13" t="str">
-        <f>CONCATENATE("", C23)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M23" s="13" t="str">
-        <f>CONCATENATE("", D23)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N23" s="13" t="str">
-        <f>CONCATENATE("", E23)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O23" s="13" t="str">
-        <f>CONCATENATE("", F23)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N3</v>
       </c>
       <c r="P23" s="37" t="s">
@@ -4864,29 +4926,29 @@
         <v>148</v>
       </c>
       <c r="R23" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P23,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A level 3 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T23" s="14" t="str">
-        <f>SUBSTITUTE(C23, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U23" s="14" t="str">
-        <f>SUBSTITUTE(D23, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V23" s="14" t="str">
-        <f>SUBSTITUTE(F23, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N3</v>
       </c>
       <c r="W23" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X23" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A23)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-23</v>
       </c>
       <c r="Y23" s="14" t="s">
@@ -4908,7 +4970,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -4943,19 +5005,19 @@
         <v>2</v>
       </c>
       <c r="L24" s="13" t="str">
-        <f>CONCATENATE("", C24)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M24" s="13" t="str">
-        <f>CONCATENATE("", D24)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N24" s="13" t="str">
-        <f>CONCATENATE("", E24)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O24" s="13" t="str">
-        <f>CONCATENATE("", F24)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N4</v>
       </c>
       <c r="P24" s="37" t="s">
@@ -4965,29 +5027,29 @@
         <v>148</v>
       </c>
       <c r="R24" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P24,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A level 4 KML element (&lt;Point&gt;, &lt;Polygon&gt;, &lt;Style&gt;).</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T24" s="14" t="str">
-        <f>SUBSTITUTE(C24, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U24" s="14" t="str">
-        <f>SUBSTITUTE(D24, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V24" s="14" t="str">
-        <f>SUBSTITUTE(F24, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N4</v>
       </c>
       <c r="W24" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X24" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A24)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-24</v>
       </c>
       <c r="Y24" s="14" t="s">
@@ -5009,7 +5071,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -5044,19 +5106,19 @@
         <v>2</v>
       </c>
       <c r="L25" s="13" t="str">
-        <f>CONCATENATE("", C25)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M25" s="13" t="str">
-        <f>CONCATENATE("", D25)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N25" s="13" t="str">
-        <f>CONCATENATE("", E25)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O25" s="13" t="str">
-        <f>CONCATENATE("", F25)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Elemento.N5</v>
       </c>
       <c r="P25" s="37" t="s">
@@ -5066,29 +5128,29 @@
         <v>148</v>
       </c>
       <c r="R25" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P25,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>A level 5 KML element (&lt;outerBoundaryIs&gt;, &lt;LinearRing&gt;, &lt;coordinates&gt;).</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T25" s="14" t="str">
-        <f>SUBSTITUTE(C25, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U25" s="14" t="str">
-        <f>SUBSTITUTE(D25, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V25" s="14" t="str">
-        <f>SUBSTITUTE(F25, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Elemento.N5</v>
       </c>
       <c r="W25" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X25" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A25)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-25</v>
       </c>
       <c r="Y25" s="14" t="s">
@@ -5110,7 +5172,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -5145,52 +5207,52 @@
         <v>2</v>
       </c>
       <c r="L26" s="13" t="str">
-        <f>CONCATENATE("", C26)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M26" s="13" t="str">
-        <f>CONCATENATE("", D26)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N26" s="13" t="str">
-        <f>CONCATENATE("", E26)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O26" s="13" t="str">
-        <f>CONCATENATE("", F26)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo</v>
       </c>
       <c r="P26" s="37" t="s">
         <v>97</v>
       </c>
       <c r="Q26" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P26,"pt","es")</f>
+        <f t="shared" ref="Q26:Q62" si="10">_xlfn.TRANSLATE(P26,"pt","es")</f>
         <v>Elemento de estilo en KML. Agrupa propiedades gráficas de personalización como colores, transparencias, tamaños e iconos.</v>
       </c>
       <c r="R26" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P26,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Styling element in KML. Groups graphical customization properties such as colors, transparencies, sizes, and icons.</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T26" s="14" t="str">
-        <f>SUBSTITUTE(C26, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U26" s="14" t="str">
-        <f>SUBSTITUTE(D26, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V26" s="14" t="str">
-        <f>SUBSTITUTE(F26, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo</v>
       </c>
       <c r="W26" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X26" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A26)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-26</v>
       </c>
       <c r="Y26" s="14" t="s">
@@ -5212,7 +5274,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -5247,52 +5309,52 @@
         <v>2</v>
       </c>
       <c r="L27" s="13" t="str">
-        <f>CONCATENATE("", C27)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M27" s="13" t="str">
-        <f>CONCATENATE("", D27)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N27" s="13" t="str">
-        <f>CONCATENATE("", E27)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O27" s="13" t="str">
-        <f>CONCATENATE("", F27)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Balão</v>
       </c>
       <c r="P27" s="37" t="s">
         <v>100</v>
       </c>
       <c r="Q27" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P27,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de estilo en KML. Personaliza la burbuja de información/ventana emergente que se abre al hacer clic en un elemento (soporta etiquetas HTML).</v>
       </c>
       <c r="R27" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P27,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Styling element in KML. Customizes the info/pop-up bubble that opens when you click on an element (supports HTML tags).</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T27" s="14" t="str">
-        <f>SUBSTITUTE(C27, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U27" s="14" t="str">
-        <f>SUBSTITUTE(D27, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V27" s="14" t="str">
-        <f>SUBSTITUTE(F27, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Balão</v>
       </c>
       <c r="W27" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X27" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A27)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-27</v>
       </c>
       <c r="Y27" s="14" t="s">
@@ -5314,7 +5376,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -5349,52 +5411,52 @@
         <v>2</v>
       </c>
       <c r="L28" s="13" t="str">
-        <f>CONCATENATE("", C28)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M28" s="13" t="str">
-        <f>CONCATENATE("", D28)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N28" s="13" t="str">
-        <f>CONCATENATE("", E28)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O28" s="13" t="str">
-        <f>CONCATENATE("", F28)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Cor</v>
       </c>
       <c r="P28" s="37" t="s">
         <v>167</v>
       </c>
       <c r="Q28" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P28,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece un &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
       </c>
       <c r="R28" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P28,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets a &lt;color&gt;color 7f0000ff&lt;/color&gt;</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T28" s="14" t="str">
-        <f>SUBSTITUTE(C28, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U28" s="14" t="str">
-        <f>SUBSTITUTE(D28, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V28" s="14" t="str">
-        <f>SUBSTITUTE(F28, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Cor</v>
       </c>
       <c r="W28" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X28" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A28)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-28</v>
       </c>
       <c r="Y28" s="14" t="s">
@@ -5416,7 +5478,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -5451,52 +5513,52 @@
         <v>2</v>
       </c>
       <c r="L29" s="13" t="str">
-        <f>CONCATENATE("", C29)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M29" s="13" t="str">
-        <f>CONCATENATE("", D29)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N29" s="13" t="str">
-        <f>CONCATENATE("", E29)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O29" s="13" t="str">
-        <f>CONCATENATE("", F29)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="P29" s="37" t="s">
         <v>168</v>
       </c>
       <c r="Q29" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P29,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece un espesor &lt;width&gt;de 1&lt;/width&gt;</v>
       </c>
       <c r="R29" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P29,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets a thickness &lt;width&gt;of 1&lt;/width&gt;</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T29" s="14" t="str">
-        <f>SUBSTITUTE(C29, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U29" s="14" t="str">
-        <f>SUBSTITUTE(D29, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V29" s="14" t="str">
-        <f>SUBSTITUTE(F29, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Espessura</v>
       </c>
       <c r="W29" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X29" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A29)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-29</v>
       </c>
       <c r="Y29" s="14" t="s">
@@ -5518,7 +5580,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -5553,52 +5615,52 @@
         <v>2</v>
       </c>
       <c r="L30" s="13" t="str">
-        <f>CONCATENATE("", C30)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M30" s="13" t="str">
-        <f>CONCATENATE("", D30)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N30" s="13" t="str">
-        <f>CONCATENATE("", E30)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O30" s="13" t="str">
-        <f>CONCATENATE("", F30)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Linha</v>
       </c>
       <c r="P30" s="37" t="s">
         <v>98</v>
       </c>
       <c r="Q30" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P30,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de estilo en KML. Establece el color, la opacidad y el grosor de las líneas.</v>
       </c>
       <c r="R30" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P30,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Styling element in KML. Sets the color, opacity, and thickness of the lines.</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T30" s="14" t="str">
-        <f>SUBSTITUTE(C30, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U30" s="14" t="str">
-        <f>SUBSTITUTE(D30, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V30" s="14" t="str">
-        <f>SUBSTITUTE(F30, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Linha</v>
       </c>
       <c r="W30" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X30" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A30)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-30</v>
       </c>
       <c r="Y30" s="14" t="s">
@@ -5620,7 +5682,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -5655,52 +5717,52 @@
         <v>2</v>
       </c>
       <c r="L31" s="13" t="str">
-        <f>CONCATENATE("", C31)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M31" s="13" t="str">
-        <f>CONCATENATE("", D31)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N31" s="13" t="str">
-        <f>CONCATENATE("", E31)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O31" s="13" t="str">
-        <f>CONCATENATE("", F31)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="P31" s="37" t="s">
         <v>101</v>
       </c>
       <c r="Q31" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P31,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de estilo en KML. Permite cambiar la apariencia de un elemento según la acción del usuario (por ejemplo, cambiar el icono cuando el cursor flota).</v>
       </c>
       <c r="R31" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P31,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Styling element in KML. Allows you to toggle the appearance of an element based on the user's action (e.g., change the icon when the cursor hovers).</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T31" s="14" t="str">
-        <f>SUBSTITUTE(C31, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U31" s="14" t="str">
-        <f>SUBSTITUTE(D31, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V31" s="14" t="str">
-        <f>SUBSTITUTE(F31, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Mapa</v>
       </c>
       <c r="W31" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X31" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A31)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-31</v>
       </c>
       <c r="Y31" s="14" t="s">
@@ -5722,7 +5784,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -5757,52 +5819,52 @@
         <v>2</v>
       </c>
       <c r="L32" s="13" t="str">
-        <f>CONCATENATE("", C32)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M32" s="13" t="str">
-        <f>CONCATENATE("", D32)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N32" s="13" t="str">
-        <f>CONCATENATE("", E32)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O32" s="13" t="str">
-        <f>CONCATENATE("", F32)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Texto</v>
       </c>
       <c r="P32" s="37" t="s">
         <v>99</v>
       </c>
       <c r="Q32" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P32,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de estilo en KML. Establece el color y la escala del texto de la etiqueta en viñetas.</v>
       </c>
       <c r="R32" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P32,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>Styling element in KML. Sets the color and scale of the bullet label text.</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T32" s="14" t="str">
-        <f>SUBSTITUTE(C32, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U32" s="14" t="str">
-        <f>SUBSTITUTE(D32, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V32" s="14" t="str">
-        <f>SUBSTITUTE(F32, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Texto</v>
       </c>
       <c r="W32" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X32" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A32)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-32</v>
       </c>
       <c r="Y32" s="14" t="s">
@@ -5824,7 +5886,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -5859,52 +5921,52 @@
         <v>2</v>
       </c>
       <c r="L33" s="13" t="str">
-        <f>CONCATENATE("", C33)</f>
+        <f t="shared" si="0"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M33" s="13" t="str">
-        <f>CONCATENATE("", D33)</f>
+        <f t="shared" si="1"/>
         <v>Esquemas</v>
       </c>
       <c r="N33" s="13" t="str">
-        <f>CONCATENATE("", E33)</f>
+        <f t="shared" si="2"/>
         <v>KML</v>
       </c>
       <c r="O33" s="13" t="str">
-        <f>CONCATENATE("", F33)</f>
+        <f t="shared" si="3"/>
         <v>Kml.Estilo.Usado</v>
       </c>
       <c r="P33" s="37" t="s">
         <v>165</v>
       </c>
       <c r="Q33" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P33,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece la referencia a un estilo &lt;styleUrl&gt;ya definido #EstilodeLinha&lt;/styleUrl&gt;</v>
       </c>
       <c r="R33" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P33,"pt","en")</f>
+        <f t="shared" si="4"/>
         <v>KML element. Sets the reference to a style already defined &lt;styleUrl&gt;#EstilodeLinha&lt;/styleUrl&gt;</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T33" s="14" t="str">
-        <f>SUBSTITUTE(C33, "_", " ")</f>
+        <f t="shared" si="5"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U33" s="14" t="str">
-        <f>SUBSTITUTE(D33, "_", " ")</f>
+        <f t="shared" si="6"/>
         <v>Esquemas</v>
       </c>
       <c r="V33" s="14" t="str">
-        <f>SUBSTITUTE(F33, "_", " ")</f>
+        <f t="shared" si="7"/>
         <v>Kml.Estilo.Usado</v>
       </c>
       <c r="W33" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X33" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A33)</f>
+        <f t="shared" si="8"/>
         <v>Key-Kml-33</v>
       </c>
       <c r="Y33" s="14" t="s">
@@ -5926,7 +5988,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -5961,52 +6023,52 @@
         <v>2</v>
       </c>
       <c r="L34" s="13" t="str">
-        <f>CONCATENATE("", C34)</f>
+        <f t="shared" ref="L34:L62" si="11">CONCATENATE("", C34)</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="M34" s="13" t="str">
-        <f>CONCATENATE("", D34)</f>
+        <f t="shared" ref="M34:M62" si="12">CONCATENATE("", D34)</f>
         <v>Esquemas</v>
       </c>
       <c r="N34" s="13" t="str">
-        <f>CONCATENATE("", E34)</f>
+        <f t="shared" ref="N34:N62" si="13">CONCATENATE("", E34)</f>
         <v>KML</v>
       </c>
       <c r="O34" s="13" t="str">
-        <f>CONCATENATE("", F34)</f>
+        <f t="shared" ref="O34:O62" si="14">CONCATENATE("", F34)</f>
         <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="P34" s="37" t="s">
         <v>169</v>
       </c>
       <c r="Q34" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P34,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece un modo de visibilidad &lt;gx:etiquetaVisibilidad&gt; &lt;/gx:etiquetaVisibilidad&gt;</v>
       </c>
       <c r="R34" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P34,"pt","en")</f>
+        <f t="shared" ref="R34:R62" si="15">_xlfn.TRANSLATE(P34,"pt","en")</f>
         <v>KML element. Sets a visibility mode &lt;gx:labelVisibility&gt; &lt;/gx:labelVisibility&gt;</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T34" s="14" t="str">
-        <f>SUBSTITUTE(C34, "_", " ")</f>
+        <f t="shared" ref="T34:T62" si="16">SUBSTITUTE(C34, "_", " ")</f>
         <v>Interoperabilidade</v>
       </c>
       <c r="U34" s="14" t="str">
-        <f>SUBSTITUTE(D34, "_", " ")</f>
+        <f t="shared" ref="U34:U62" si="17">SUBSTITUTE(D34, "_", " ")</f>
         <v>Esquemas</v>
       </c>
       <c r="V34" s="14" t="str">
-        <f>SUBSTITUTE(F34, "_", " ")</f>
+        <f t="shared" ref="V34:V62" si="18">SUBSTITUTE(F34, "_", " ")</f>
         <v>Kml.Estilo.Visibilidade</v>
       </c>
       <c r="W34" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X34" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A34)</f>
+        <f t="shared" ref="X34:X63" si="19">CONCATENATE("Key-Kml-",A34)</f>
         <v>Key-Kml-34</v>
       </c>
       <c r="Y34" s="14" t="s">
@@ -6028,7 +6090,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -6063,52 +6125,52 @@
         <v>2</v>
       </c>
       <c r="L35" s="13" t="str">
-        <f>CONCATENATE("", C35)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M35" s="13" t="str">
-        <f>CONCATENATE("", D35)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N35" s="13" t="str">
-        <f>CONCATENATE("", E35)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O35" s="13" t="str">
-        <f>CONCATENATE("", F35)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Extrusão</v>
       </c>
       <c r="P35" s="37" t="s">
         <v>170</v>
       </c>
       <c r="Q35" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P35,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Fija un valor de extrusión &lt;extrude&gt;de 1&lt;/extrude&gt;.</v>
       </c>
       <c r="R35" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P35,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets an extrusion value &lt;extrude&gt;of 1&lt;/extrude&gt;.</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T35" s="14" t="str">
-        <f>SUBSTITUTE(C35, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U35" s="14" t="str">
-        <f>SUBSTITUTE(D35, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V35" s="14" t="str">
-        <f>SUBSTITUTE(F35, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Extrusão</v>
       </c>
       <c r="W35" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X35" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A35)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-35</v>
       </c>
       <c r="Y35" s="14" t="s">
@@ -6130,7 +6192,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -6165,52 +6227,52 @@
         <v>2</v>
       </c>
       <c r="L36" s="13" t="str">
-        <f>CONCATENATE("", C36)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M36" s="13" t="str">
-        <f>CONCATENATE("", D36)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N36" s="13" t="str">
-        <f>CONCATENATE("", E36)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O36" s="13" t="str">
-        <f>CONCATENATE("", F36)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Gira.X</v>
       </c>
       <c r="P36" s="37" t="s">
         <v>185</v>
       </c>
       <c r="Q36" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P36,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Ajusta la inclinación alrededor del eje &lt;tilt&gt;X 10,5&lt;/tilt&gt; Un valor de 0 está hacia abajo hacia la Tierra. Valor 90, la vista es hacia el horizonte. El valor &gt; 90 indica que la opinión sube. Los valores siempre son positivos.</v>
       </c>
       <c r="R36" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P36,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets the tilt about the X-axis &lt;tilt&gt;10.5&lt;/tilt&gt; A value of 0 view is downward toward the Earth. Value 90 the view is to the horizon. Value &gt; 90 indicates the view points up. The values are always positive.</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T36" s="14" t="str">
-        <f>SUBSTITUTE(C36, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U36" s="14" t="str">
-        <f>SUBSTITUTE(D36, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V36" s="14" t="str">
-        <f>SUBSTITUTE(F36, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Gira.X</v>
       </c>
       <c r="W36" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X36" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A36)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-36</v>
       </c>
       <c r="Y36" s="14" t="s">
@@ -6232,7 +6294,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -6267,52 +6329,52 @@
         <v>2</v>
       </c>
       <c r="L37" s="13" t="str">
-        <f>CONCATENATE("", C37)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M37" s="13" t="str">
-        <f>CONCATENATE("", D37)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N37" s="13" t="str">
-        <f>CONCATENATE("", E37)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O37" s="13" t="str">
-        <f>CONCATENATE("", F37)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Gira.Z</v>
       </c>
       <c r="P37" s="37" t="s">
         <v>184</v>
       </c>
       <c r="Q37" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P37,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Define que un giro alrededor del eje &lt;roll&gt;Z 0&lt;/roll&gt; no puede ser valor negativo.</v>
       </c>
       <c r="R37" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P37,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Defines a turn around the Z-axis &lt;roll&gt;0&lt;/roll&gt; cannot be negative value.</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T37" s="14" t="str">
-        <f>SUBSTITUTE(C37, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U37" s="14" t="str">
-        <f>SUBSTITUTE(D37, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V37" s="14" t="str">
-        <f>SUBSTITUTE(F37, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Gira.Z</v>
       </c>
       <c r="W37" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X37" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A37)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-37</v>
       </c>
       <c r="Y37" s="14" t="s">
@@ -6334,7 +6396,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -6369,52 +6431,52 @@
         <v>2</v>
       </c>
       <c r="L38" s="13" t="str">
-        <f>CONCATENATE("", C38)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M38" s="13" t="str">
-        <f>CONCATENATE("", D38)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N38" s="13" t="str">
-        <f>CONCATENATE("", E38)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O38" s="13" t="str">
-        <f>CONCATENATE("", F38)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar</v>
       </c>
       <c r="P38" s="37" t="s">
         <v>115</v>
       </c>
       <c r="Q38" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P38,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Define el elemento más común que representa una característica geográfica individual y puede asociar un nombre, descripción, estilo y geometría.</v>
       </c>
       <c r="R38" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P38,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines the most common element that represents an individual geographic feature and can associate a name, description, style, and geometry.</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T38" s="14" t="str">
-        <f>SUBSTITUTE(C38, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U38" s="14" t="str">
-        <f>SUBSTITUTE(D38, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V38" s="14" t="str">
-        <f>SUBSTITUTE(F38, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar</v>
       </c>
       <c r="W38" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X38" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A38)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-38</v>
       </c>
       <c r="Y38" s="14" t="s">
@@ -6436,7 +6498,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -6471,52 +6533,52 @@
         <v>2</v>
       </c>
       <c r="L39" s="13" t="str">
-        <f>CONCATENATE("", C39)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M39" s="13" t="str">
-        <f>CONCATENATE("", D39)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N39" s="13" t="str">
-        <f>CONCATENATE("", E39)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O39" s="13" t="str">
-        <f>CONCATENATE("", F39)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="P39" s="37" t="s">
         <v>113</v>
       </c>
       <c r="Q39" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P39,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Un contenedor que agrupa varias geometrías bajo un único Placemark (por ejemplo, un país compuesto por varias islas).</v>
       </c>
       <c r="R39" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P39,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. A container that groups several geometries under a single Placemark (for example, a country composed of several islands).</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T39" s="14" t="str">
-        <f>SUBSTITUTE(C39, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U39" s="14" t="str">
-        <f>SUBSTITUTE(D39, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V39" s="14" t="str">
-        <f>SUBSTITUTE(F39, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Geometria</v>
       </c>
       <c r="W39" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X39" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A39)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-39</v>
       </c>
       <c r="Y39" s="14" t="s">
@@ -6538,7 +6600,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="31">
         <v>41</v>
       </c>
@@ -6573,52 +6635,52 @@
         <v>2</v>
       </c>
       <c r="L40" s="13" t="str">
-        <f>CONCATENATE("", C40)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M40" s="13" t="str">
-        <f>CONCATENATE("", D40)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N40" s="13" t="str">
-        <f>CONCATENATE("", E40)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O40" s="13" t="str">
-        <f>CONCATENATE("", F40)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="P40" s="37" t="s">
         <v>109</v>
       </c>
       <c r="Q40" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P40,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Establece una ubicación puntual en el mapa usando longitud, latitud y, opcionalmente, coordenadas de altitud.</v>
       </c>
       <c r="R40" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P40,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Sets a point location on the map using longitude, latitude, and optionally altitude coordinates.</v>
       </c>
       <c r="S40" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T40" s="14" t="str">
-        <f>SUBSTITUTE(C40, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U40" s="14" t="str">
-        <f>SUBSTITUTE(D40, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V40" s="14" t="str">
-        <f>SUBSTITUTE(F40, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto</v>
       </c>
       <c r="W40" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X40" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A40)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-41</v>
       </c>
       <c r="Y40" s="14" t="s">
@@ -6640,7 +6702,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="31">
         <v>42</v>
       </c>
@@ -6675,52 +6737,52 @@
         <v>2</v>
       </c>
       <c r="L41" s="13" t="str">
-        <f>CONCATENATE("", C41)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M41" s="13" t="str">
-        <f>CONCATENATE("", D41)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N41" s="13" t="str">
-        <f>CONCATENATE("", E41)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O41" s="13" t="str">
-        <f>CONCATENATE("", F41)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="P41" s="37" t="s">
         <v>166</v>
       </c>
       <c r="Q41" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P41,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Fija una altitud &lt;altitude&gt;de 10,5&lt;/altitude&gt;</v>
       </c>
       <c r="R41" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P41,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Set an altitude &lt;altitude&gt;of 10.5&lt;/altitude&gt;</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T41" s="14" t="str">
-        <f>SUBSTITUTE(C41, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U41" s="14" t="str">
-        <f>SUBSTITUTE(D41, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V41" s="14" t="str">
-        <f>SUBSTITUTE(F41, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto.Altitude</v>
       </c>
       <c r="W41" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X41" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A41)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-42</v>
       </c>
       <c r="Y41" s="14" t="s">
@@ -6742,7 +6804,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="31">
         <v>43</v>
       </c>
@@ -6777,52 +6839,52 @@
         <v>2</v>
       </c>
       <c r="L42" s="13" t="str">
-        <f>CONCATENATE("", C42)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M42" s="13" t="str">
-        <f>CONCATENATE("", D42)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N42" s="13" t="str">
-        <f>CONCATENATE("", E42)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O42" s="13" t="str">
-        <f>CONCATENATE("", F42)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="P42" s="37" t="s">
         <v>186</v>
       </c>
       <c r="Q42" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P42,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece el modo &lt;altitudeMode&gt;altitud absoluta&lt;/altitudeMode&gt; (Valores posibles: relativeToGround, clampToGround y absoluto)</v>
       </c>
       <c r="R42" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P42,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets &lt;altitudeMode&gt;the absolute altitude&lt;/altitudeMode&gt; mode (Possible values: relativeToGround, clampToGround, and absolute)</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T42" s="14" t="str">
-        <f>SUBSTITUTE(C42, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U42" s="14" t="str">
-        <f>SUBSTITUTE(D42, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V42" s="14" t="str">
-        <f>SUBSTITUTE(F42, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto.AltitudeModo</v>
       </c>
       <c r="W42" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X42" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A42)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-43</v>
       </c>
       <c r="Y42" s="14" t="s">
@@ -6844,7 +6906,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="31">
         <v>44</v>
       </c>
@@ -6879,52 +6941,52 @@
         <v>2</v>
       </c>
       <c r="L43" s="13" t="str">
-        <f>CONCATENATE("", C43)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M43" s="13" t="str">
-        <f>CONCATENATE("", D43)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N43" s="13" t="str">
-        <f>CONCATENATE("", E43)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O43" s="13" t="str">
-        <f>CONCATENATE("", F43)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="P43" s="37" t="s">
         <v>173</v>
       </c>
       <c r="Q43" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P43,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Conjuntos latitud &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
       </c>
       <c r="R43" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P43,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets latitude &lt;latitude&gt;-22.45&lt;/latitude&gt;</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T43" s="14" t="str">
-        <f>SUBSTITUTE(C43, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U43" s="14" t="str">
-        <f>SUBSTITUTE(D43, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V43" s="14" t="str">
-        <f>SUBSTITUTE(F43, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto.Latitude</v>
       </c>
       <c r="W43" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X43" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A43)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-44</v>
       </c>
       <c r="Y43" s="14" t="s">
@@ -6946,7 +7008,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="31">
         <v>45</v>
       </c>
@@ -6981,52 +7043,52 @@
         <v>2</v>
       </c>
       <c r="L44" s="13" t="str">
-        <f>CONCATENATE("", C44)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M44" s="13" t="str">
-        <f>CONCATENATE("", D44)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N44" s="13" t="str">
-        <f>CONCATENATE("", E44)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O44" s="13" t="str">
-        <f>CONCATENATE("", F44)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="P44" s="37" t="s">
         <v>172</v>
       </c>
       <c r="Q44" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P44,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Conjuntos longitud &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
       </c>
       <c r="R44" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P44,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets longitude &lt;longitude&gt;-122.36415&lt;/longitude&gt;</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T44" s="14" t="str">
-        <f>SUBSTITUTE(C44, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U44" s="14" t="str">
-        <f>SUBSTITUTE(D44, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V44" s="14" t="str">
-        <f>SUBSTITUTE(F44, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto.Longitude</v>
       </c>
       <c r="W44" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X44" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A44)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-45</v>
       </c>
       <c r="Y44" s="14" t="s">
@@ -7048,7 +7110,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="31">
         <v>46</v>
       </c>
@@ -7083,52 +7145,52 @@
         <v>2</v>
       </c>
       <c r="L45" s="13" t="str">
-        <f>CONCATENATE("", C45)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M45" s="13" t="str">
-        <f>CONCATENATE("", D45)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N45" s="13" t="str">
-        <f>CONCATENATE("", E45)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O45" s="13" t="str">
-        <f>CONCATENATE("", F45)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="P45" s="37" t="s">
         <v>164</v>
       </c>
       <c r="Q45" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P45,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de coordenadas en KML. Coordenadas. X, Y, Z separados por comas y coordinados por espacios &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
       </c>
       <c r="R45" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P45,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Coordinate element in KML. Coordinates. X, Y, Z separated by commas and coordinated by spaces &lt;coordinates&gt;x1 , y1 , z1 x2 , y2 , z2 x3 , y3 , z3 x4 , y4 , z4&lt;/coordinates&gt;.</v>
       </c>
       <c r="S45" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T45" s="14" t="str">
-        <f>SUBSTITUTE(C45, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U45" s="14" t="str">
-        <f>SUBSTITUTE(D45, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V45" s="14" t="str">
-        <f>SUBSTITUTE(F45, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Ponto.XYZ</v>
       </c>
       <c r="W45" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X45" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A45)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-46</v>
       </c>
       <c r="Y45" s="14" t="s">
@@ -7150,7 +7212,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="31">
         <v>47</v>
       </c>
@@ -7185,52 +7247,52 @@
         <v>2</v>
       </c>
       <c r="L46" s="13" t="str">
-        <f>CONCATENATE("", C46)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M46" s="13" t="str">
-        <f>CONCATENATE("", D46)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N46" s="13" t="str">
-        <f>CONCATENATE("", E46)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O46" s="13" t="str">
-        <f>CONCATENATE("", F46)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="P46" s="37" t="s">
         <v>110</v>
       </c>
       <c r="Q46" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P46,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Define una línea continua a través de una secuencia de coordenadas (útil para caminos, rutas y ríos).</v>
       </c>
       <c r="R46" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P46,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines a continuous line through a sequence of coordinates (useful for paths, routes, and rivers).</v>
       </c>
       <c r="S46" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T46" s="14" t="str">
-        <f>SUBSTITUTE(C46, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U46" s="14" t="str">
-        <f>SUBSTITUTE(D46, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V46" s="14" t="str">
-        <f>SUBSTITUTE(F46, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Segmento</v>
       </c>
       <c r="W46" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X46" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A46)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-47</v>
       </c>
       <c r="Y46" s="14" t="s">
@@ -7252,7 +7314,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="31">
         <v>48</v>
       </c>
@@ -7287,52 +7349,52 @@
         <v>2</v>
       </c>
       <c r="L47" s="13" t="str">
-        <f>CONCATENATE("", C47)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M47" s="13" t="str">
-        <f>CONCATENATE("", D47)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N47" s="13" t="str">
-        <f>CONCATENATE("", E47)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O47" s="13" t="str">
-        <f>CONCATENATE("", F47)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="P47" s="37" t="s">
         <v>111</v>
       </c>
       <c r="Q47" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P47,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Una línea cerrada, no auto-intersectante, usada principalmente para definir los límites de un polígono.</v>
       </c>
       <c r="R47" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P47,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. A closed, non-self-intersecting line, used primarily to define the boundaries of a polygon.</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T47" s="14" t="str">
-        <f>SUBSTITUTE(C47, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U47" s="14" t="str">
-        <f>SUBSTITUTE(D47, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V47" s="14" t="str">
-        <f>SUBSTITUTE(F47, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Segmento.Poligonal</v>
       </c>
       <c r="W47" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X47" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A47)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-48</v>
       </c>
       <c r="Y47" s="14" t="s">
@@ -7354,7 +7416,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="31">
         <v>49</v>
       </c>
@@ -7389,52 +7451,52 @@
         <v>2</v>
       </c>
       <c r="L48" s="13" t="str">
-        <f>CONCATENATE("", C48)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M48" s="13" t="str">
-        <f>CONCATENATE("", D48)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N48" s="13" t="str">
-        <f>CONCATENATE("", E48)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O48" s="13" t="str">
-        <f>CONCATENATE("", F48)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="P48" s="37" t="s">
         <v>112</v>
       </c>
       <c r="Q48" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P48,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Define un área delimitada por un límite exterior (&lt;outerBoundaryIs&gt;) y, opcionalmente, por un límite interior (&lt;innerBoundaryIs&gt;) para crear agujeros.</v>
       </c>
       <c r="R48" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P48,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. Defines an area bounded by an outer boundary (&lt;outerBoundaryIs&gt;) and, optionally, inner boundary (&lt;innerBoundaryIs&gt;) to create holes.</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T48" s="14" t="str">
-        <f>SUBSTITUTE(C48, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U48" s="14" t="str">
-        <f>SUBSTITUTE(D48, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V48" s="14" t="str">
-        <f>SUBSTITUTE(F48, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Segmento.Poligono</v>
       </c>
       <c r="W48" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X48" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A48)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-49</v>
       </c>
       <c r="Y48" s="14" t="s">
@@ -7456,7 +7518,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="31">
         <v>40</v>
       </c>
@@ -7491,52 +7553,52 @@
         <v>2</v>
       </c>
       <c r="L49" s="13" t="str">
-        <f>CONCATENATE("", C49)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M49" s="13" t="str">
-        <f>CONCATENATE("", D49)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N49" s="13" t="str">
-        <f>CONCATENATE("", E49)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O49" s="13" t="str">
-        <f>CONCATENATE("", F49)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="P49" s="37" t="s">
         <v>329</v>
       </c>
       <c r="Q49" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P49,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Determina si una línea o polígono sigue la curvatura de la tierra, los relieves del terreno o si se dibuja como una línea recta en el espacio tridimensional. &lt;tessellate&gt;1&lt;/tessellate&gt; solo funciona si el modo altitud (&lt;altitudeMode&gt;) está configurado en clampToGround (fijado a tierra, que es el valor predeterminado). Si la altitud es absoluta o relativa al suelo, se ignora el efecto del teselado.</v>
       </c>
       <c r="R49" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P49,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Controls whether a line or polygon follows the curvature of the earth, the terrain reliefs, or whether it is drawn as a straight line in three-dimensional space. &lt;tessellate&gt;1&lt;/tessellate&gt; Works only if the altitude mode (&lt;altitudeMode&gt;) is set to clampToGround (secured to ground, which is the default). If the altitude is absolute or relative to the ground, the effect of tessellate is ignored.</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T49" s="14" t="str">
-        <f>SUBSTITUTE(C49, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U49" s="14" t="str">
-        <f>SUBSTITUTE(D49, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V49" s="14" t="str">
-        <f>SUBSTITUTE(F49, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Lugar.Segmento.Projeção</v>
       </c>
       <c r="W49" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X49" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A49)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-40</v>
       </c>
       <c r="Y49" s="14" t="s">
@@ -7558,7 +7620,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -7593,52 +7655,52 @@
         <v>2</v>
       </c>
       <c r="L50" s="13" t="str">
-        <f>CONCATENATE("", C50)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M50" s="13" t="str">
-        <f>CONCATENATE("", D50)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N50" s="13" t="str">
-        <f>CONCATENATE("", E50)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O50" s="13" t="str">
-        <f>CONCATENATE("", F50)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Modelo.3D</v>
       </c>
       <c r="P50" s="37" t="s">
         <v>114</v>
       </c>
       <c r="Q50" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P50,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de características geográficas en KML. Permite insertar modelos 3D complejos (normalmente en formato COLLADA .dae) en el mapa.</v>
       </c>
       <c r="R50" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P50,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Geographic feature element in KML. It allows you to insert complex 3D models (usually in COLLADA .dae format) into the map.</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T50" s="14" t="str">
-        <f>SUBSTITUTE(C50, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U50" s="14" t="str">
-        <f>SUBSTITUTE(D50, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V50" s="14" t="str">
-        <f>SUBSTITUTE(F50, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Modelo.3D</v>
       </c>
       <c r="W50" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X50" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A50)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-50</v>
       </c>
       <c r="Y50" s="14" t="s">
@@ -7660,7 +7722,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -7695,52 +7757,52 @@
         <v>2</v>
       </c>
       <c r="L51" s="13" t="str">
-        <f>CONCATENATE("", C51)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M51" s="13" t="str">
-        <f>CONCATENATE("", D51)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N51" s="13" t="str">
-        <f>CONCATENATE("", E51)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O51" s="13" t="str">
-        <f>CONCATENATE("", F51)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Nome</v>
       </c>
       <c r="P51" s="37" t="s">
         <v>171</v>
       </c>
       <c r="Q51" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P51,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Define un nombre que puede ser archivo, lugar, etc. &lt;name&gt;Nombre del elemento&lt;/name&gt;</v>
       </c>
       <c r="R51" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P51,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Defines a name that can be file, place, etc. &lt;name&gt;Element Name&lt;/name&gt;</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T51" s="14" t="str">
-        <f>SUBSTITUTE(C51, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U51" s="14" t="str">
-        <f>SUBSTITUTE(D51, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V51" s="14" t="str">
-        <f>SUBSTITUTE(F51, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Nome</v>
       </c>
       <c r="W51" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X51" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A51)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-51</v>
       </c>
       <c r="Y51" s="14" t="s">
@@ -7762,7 +7824,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -7797,52 +7859,52 @@
         <v>2</v>
       </c>
       <c r="L52" s="13" t="str">
-        <f>CONCATENATE("", C52)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M52" s="13" t="str">
-        <f>CONCATENATE("", D52)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N52" s="13" t="str">
-        <f>CONCATENATE("", E52)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O52" s="13" t="str">
-        <f>CONCATENATE("", F52)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Pasta</v>
       </c>
       <c r="P52" s="37" t="s">
         <v>236</v>
       </c>
       <c r="Q52" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P52,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>KML folder grouper element que ordena elementos en la jerarquía de carpetas (como la barra lateral de Google Earth), permite habilitar o desactivar la visibilidad de bloques.</v>
       </c>
       <c r="R52" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P52,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML folder grouper element that sorts elements in folder hierarchy (such as the Google Earth sidebar), allows you to enable or disable block visibility.</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T52" s="14" t="str">
-        <f>SUBSTITUTE(C52, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U52" s="14" t="str">
-        <f>SUBSTITUTE(D52, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V52" s="14" t="str">
-        <f>SUBSTITUTE(F52, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Pasta</v>
       </c>
       <c r="W52" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X52" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A52)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-52</v>
       </c>
       <c r="Y52" s="14" t="s">
@@ -7864,7 +7926,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -7899,52 +7961,52 @@
         <v>2</v>
       </c>
       <c r="L53" s="13" t="str">
-        <f>CONCATENATE("", C53)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M53" s="13" t="str">
-        <f>CONCATENATE("", D53)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N53" s="13" t="str">
-        <f>CONCATENATE("", E53)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O53" s="13" t="str">
-        <f>CONCATENATE("", F53)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="P53" s="37" t="s">
         <v>325</v>
       </c>
       <c r="Q53" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P53,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Especifica si un elemento en el árbol de lugares en Google Earth o Google Maps se muestra abierto o cerrado por &lt;open&gt;defecto 1&lt;/open&gt;</v>
       </c>
       <c r="R53" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P53,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Specifies whether an item in the place tree in Google Earth or Google Maps is displayed open or closed by default &lt;open&gt;1&lt;/open&gt;</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T53" s="14" t="str">
-        <f>SUBSTITUTE(C53, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U53" s="14" t="str">
-        <f>SUBSTITUTE(D53, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V53" s="14" t="str">
-        <f>SUBSTITUTE(F53, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Pasta.Aberta</v>
       </c>
       <c r="W53" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X53" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A53)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-53</v>
       </c>
       <c r="Y53" s="14" t="s">
@@ -7966,7 +8028,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -8001,52 +8063,52 @@
         <v>2</v>
       </c>
       <c r="L54" s="13" t="str">
-        <f>CONCATENATE("", C54)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M54" s="13" t="str">
-        <f>CONCATENATE("", D54)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N54" s="13" t="str">
-        <f>CONCATENATE("", E54)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O54" s="13" t="str">
-        <f>CONCATENATE("", F54)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Region</v>
       </c>
       <c r="P54" s="37" t="s">
         <v>215</v>
       </c>
       <c r="Q54" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P54,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Define una región. &lt;Region&gt; ..... &lt;/Region&gt;</v>
       </c>
       <c r="R54" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P54,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Defines a region. &lt;Region&gt; ..... &lt;/Region&gt;</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T54" s="14" t="str">
-        <f>SUBSTITUTE(C54, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U54" s="14" t="str">
-        <f>SUBSTITUTE(D54, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V54" s="14" t="str">
-        <f>SUBSTITUTE(F54, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Region</v>
       </c>
       <c r="W54" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X54" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A54)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-54</v>
       </c>
       <c r="Y54" s="14" t="s">
@@ -8068,7 +8130,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -8103,52 +8165,52 @@
         <v>2</v>
       </c>
       <c r="L55" s="13" t="str">
-        <f>CONCATENATE("", C55)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M55" s="13" t="str">
-        <f>CONCATENATE("", D55)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N55" s="13" t="str">
-        <f>CONCATENATE("", E55)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O55" s="13" t="str">
-        <f>CONCATENATE("", F55)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Sobrepor</v>
       </c>
       <c r="P55" s="37" t="s">
         <v>106</v>
       </c>
       <c r="Q55" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P55,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento superpuesto en KML. Muestra una imagen fija en la pantalla de la aplicación (como logotipos, leyendas o brújulas) independientemente de la navegación por el mapa.</v>
       </c>
       <c r="R55" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P55,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Overlay element in KML. Displays a fixed image on the app screen (such as logos, legends, or compasses) independent of the map navigation.</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T55" s="14" t="str">
-        <f>SUBSTITUTE(C55, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U55" s="14" t="str">
-        <f>SUBSTITUTE(D55, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V55" s="14" t="str">
-        <f>SUBSTITUTE(F55, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Sobrepor</v>
       </c>
       <c r="W55" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X55" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A55)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-55</v>
       </c>
       <c r="Y55" s="14" t="s">
@@ -8170,7 +8232,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -8205,52 +8267,52 @@
         <v>2</v>
       </c>
       <c r="L56" s="13" t="str">
-        <f>CONCATENATE("", C56)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M56" s="13" t="str">
-        <f>CONCATENATE("", D56)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N56" s="13" t="str">
-        <f>CONCATENATE("", E56)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O56" s="13" t="str">
-        <f>CONCATENATE("", F56)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="P56" s="37" t="s">
         <v>107</v>
       </c>
       <c r="Q56" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P56,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento superpuesto en KML. Asocia una foto con una ubicación geográfica específica, permitiendo navegación en gigapíxeles o vista panorámica.</v>
       </c>
       <c r="R56" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P56,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Overlay element in KML. Associates a photo with a specific geographic location, allowing gigapixel navigation or panoramic view.</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T56" s="14" t="str">
-        <f>SUBSTITUTE(C56, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U56" s="14" t="str">
-        <f>SUBSTITUTE(D56, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V56" s="14" t="str">
-        <f>SUBSTITUTE(F56, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Sobrepor.Foto</v>
       </c>
       <c r="W56" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X56" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A56)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-56</v>
       </c>
       <c r="Y56" s="14" t="s">
@@ -8272,7 +8334,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -8307,52 +8369,52 @@
         <v>2</v>
       </c>
       <c r="L57" s="13" t="str">
-        <f>CONCATENATE("", C57)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M57" s="13" t="str">
-        <f>CONCATENATE("", D57)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N57" s="13" t="str">
-        <f>CONCATENATE("", E57)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O57" s="13" t="str">
-        <f>CONCATENATE("", F57)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="P57" s="37" t="s">
         <v>108</v>
       </c>
       <c r="Q57" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P57,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento superpuesto en KML. Proyecta una imagen bidimensional directamente sobre la superficie terrestre, alineada por coordenadas geográficas de frontera.</v>
       </c>
       <c r="R57" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P57,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Overlay element in KML. It projects a two-dimensional image directly onto the Earth's surface, aligned by geographic boundary coordinates.</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T57" s="14" t="str">
-        <f>SUBSTITUTE(C57, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U57" s="14" t="str">
-        <f>SUBSTITUTE(D57, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V57" s="14" t="str">
-        <f>SUBSTITUTE(F57, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Sobrepor.Piso</v>
       </c>
       <c r="W57" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X57" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A57)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-57</v>
       </c>
       <c r="Y57" s="14" t="s">
@@ -8374,7 +8436,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -8409,52 +8471,52 @@
         <v>2</v>
       </c>
       <c r="L58" s="13" t="str">
-        <f>CONCATENATE("", C58)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M58" s="13" t="str">
-        <f>CONCATENATE("", D58)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N58" s="13" t="str">
-        <f>CONCATENATE("", E58)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O58" s="13" t="str">
-        <f>CONCATENATE("", F58)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="P58" s="37" t="s">
         <v>105</v>
       </c>
       <c r="Q58" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P58,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de animación en KML. Establece un rango de tiempo con &lt;begin&gt;la fecha/hora de inicio () y fin &lt;end&gt;().</v>
       </c>
       <c r="R58" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P58,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Animation element in KML. Sets a time range with start (&lt;begin&gt;) and end () date/time&lt;end&gt;.</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T58" s="14" t="str">
-        <f>SUBSTITUTE(C58, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U58" s="14" t="str">
-        <f>SUBSTITUTE(D58, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V58" s="14" t="str">
-        <f>SUBSTITUTE(F58, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Tempo.Intervalo</v>
       </c>
       <c r="W58" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X58" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A58)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-58</v>
       </c>
       <c r="Y58" s="14" t="s">
@@ -8476,7 +8538,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -8511,52 +8573,52 @@
         <v>2</v>
       </c>
       <c r="L59" s="13" t="str">
-        <f>CONCATENATE("", C59)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M59" s="13" t="str">
-        <f>CONCATENATE("", D59)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N59" s="13" t="str">
-        <f>CONCATENATE("", E59)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O59" s="13" t="str">
-        <f>CONCATENATE("", F59)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="P59" s="37" t="s">
         <v>177</v>
       </c>
       <c r="Q59" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P59,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Define un momento que puede ser un año, una fecha o una hora. &lt;when&gt;01-08-2024&lt;/when&gt;</v>
       </c>
       <c r="R59" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P59,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Defines a moment that can be a year, date, or time. &lt;when&gt;2024-08-01&lt;/when&gt;</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T59" s="14" t="str">
-        <f>SUBSTITUTE(C59, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U59" s="14" t="str">
-        <f>SUBSTITUTE(D59, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V59" s="14" t="str">
-        <f>SUBSTITUTE(F59, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Tempo.Momento</v>
       </c>
       <c r="W59" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X59" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A59)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-59</v>
       </c>
       <c r="Y59" s="14" t="s">
@@ -8578,7 +8640,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -8613,52 +8675,52 @@
         <v>2</v>
       </c>
       <c r="L60" s="13" t="str">
-        <f>CONCATENATE("", C60)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M60" s="13" t="str">
-        <f>CONCATENATE("", D60)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N60" s="13" t="str">
-        <f>CONCATENATE("", E60)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O60" s="13" t="str">
-        <f>CONCATENATE("", F60)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="P60" s="37" t="s">
         <v>225</v>
       </c>
       <c r="Q60" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P60,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece un momento final en &lt;TimeSpan&gt;un . &lt;end&gt;01-08-2024&lt;/end&gt;</v>
       </c>
       <c r="R60" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P60,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets an end moment in a &lt;TimeSpan&gt;. &lt;end&gt;2024-08-01&lt;/end&gt;</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T60" s="14" t="str">
-        <f>SUBSTITUTE(C60, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U60" s="14" t="str">
-        <f>SUBSTITUTE(D60, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V60" s="14" t="str">
-        <f>SUBSTITUTE(F60, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Tempo.Momento.Final</v>
       </c>
       <c r="W60" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X60" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A60)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-60</v>
       </c>
       <c r="Y60" s="14" t="s">
@@ -8680,7 +8742,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -8715,52 +8777,52 @@
         <v>2</v>
       </c>
       <c r="L61" s="13" t="str">
-        <f>CONCATENATE("", C61)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M61" s="13" t="str">
-        <f>CONCATENATE("", D61)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N61" s="13" t="str">
-        <f>CONCATENATE("", E61)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O61" s="13" t="str">
-        <f>CONCATENATE("", F61)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="P61" s="37" t="s">
         <v>226</v>
       </c>
       <c r="Q61" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P61,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento KML. Establece un momento inicial en &lt;TimeSpan&gt;un . &lt;begin&gt;01-01-2024&lt;/begin&gt;</v>
       </c>
       <c r="R61" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P61,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>KML element. Sets a starting moment in a &lt;TimeSpan&gt;. &lt;begin&gt;2024-01-01&lt;/begin&gt;</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T61" s="14" t="str">
-        <f>SUBSTITUTE(C61, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U61" s="14" t="str">
-        <f>SUBSTITUTE(D61, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V61" s="14" t="str">
-        <f>SUBSTITUTE(F61, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Tempo.Momento.Inicial</v>
       </c>
       <c r="W61" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X61" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A61)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-61</v>
       </c>
       <c r="Y61" s="14" t="s">
@@ -8782,7 +8844,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -8817,52 +8879,52 @@
         <v>2</v>
       </c>
       <c r="L62" s="13" t="str">
-        <f>CONCATENATE("", C62)</f>
+        <f t="shared" si="11"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="M62" s="13" t="str">
-        <f>CONCATENATE("", D62)</f>
+        <f t="shared" si="12"/>
         <v>Esquemas</v>
       </c>
       <c r="N62" s="13" t="str">
-        <f>CONCATENATE("", E62)</f>
+        <f t="shared" si="13"/>
         <v>KML</v>
       </c>
       <c r="O62" s="13" t="str">
-        <f>CONCATENATE("", F62)</f>
+        <f t="shared" si="14"/>
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="P62" s="37" t="s">
         <v>102</v>
       </c>
       <c r="Q62" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P62,"pt","es")</f>
+        <f t="shared" si="10"/>
         <v>Elemento de animación en KML. Asocia un elemento con un punto específico en el tiempo (por ejemplo, un evento puntual).</v>
       </c>
       <c r="R62" s="14" t="str">
-        <f>_xlfn.TRANSLATE(P62,"pt","en")</f>
+        <f t="shared" si="15"/>
         <v>Animation element in KML. Associates an element with a specific point in time (e.g., point event).</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>2</v>
       </c>
       <c r="T62" s="14" t="str">
-        <f>SUBSTITUTE(C62, "_", " ")</f>
+        <f t="shared" si="16"/>
         <v>Interoperabilidade</v>
       </c>
       <c r="U62" s="14" t="str">
-        <f>SUBSTITUTE(D62, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Esquemas</v>
       </c>
       <c r="V62" s="14" t="str">
-        <f>SUBSTITUTE(F62, "_", " ")</f>
+        <f t="shared" si="18"/>
         <v>Kml.Tempo.Registra</v>
       </c>
       <c r="W62" s="14" t="s">
         <v>64</v>
       </c>
       <c r="X62" s="30" t="str">
-        <f>CONCATENATE("Key-Kml-",A62)</f>
+        <f t="shared" si="19"/>
         <v>Key-Kml-62</v>
       </c>
       <c r="Y62" s="14" t="s">
@@ -8882,27 +8944,140 @@
       </c>
       <c r="AD62" s="37" t="s">
         <v>134</v>
+      </c>
+    </row>
+    <row r="63" spans="1:30" s="63" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="31">
+        <v>63</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C63" s="60" t="s">
+        <v>333</v>
+      </c>
+      <c r="D63" s="60" t="s">
+        <v>334</v>
+      </c>
+      <c r="E63" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="F63" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="G63" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="H63" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="I63" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="J63" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="K63" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="L63" s="13" t="str">
+        <f t="shared" ref="L63:O63" si="20">SUBSTITUTE(CONCATENATE("", C63), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M63" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N63" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>Macros</v>
+      </c>
+      <c r="O63" s="13" t="str">
+        <f t="shared" si="20"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P63" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="Q63" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="R63" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="S63" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="T63" s="14" t="str">
+        <f t="shared" ref="T63:V63" si="21">SUBSTITUTE(C63, ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="U63" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V63" s="61" t="str">
+        <f t="shared" si="21"/>
+        <v>Macros</v>
+      </c>
+      <c r="W63" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="X63" s="30" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-Kml-63</v>
+      </c>
+      <c r="Y63" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z63" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA63" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="AB63" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC63" s="62" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD63" s="62" t="s">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD62">
     <sortCondition ref="F30:F62"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B62">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B62 A63">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F62">
-    <cfRule type="duplicateValues" dxfId="32" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F63">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R63">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9054,7 +9229,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9125,22 +9300,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="27" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="23" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10810,54 +10985,54 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B10:B1048576 B1:B8">
-    <cfRule type="duplicateValues" dxfId="22" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="19" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3">
+    <cfRule type="duplicateValues" dxfId="20" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E4">
+    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 B1">
-    <cfRule type="duplicateValues" dxfId="18" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="17" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="duplicateValues" dxfId="16" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="15" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="duplicateValues" dxfId="14" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="13" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="duplicateValues" dxfId="12" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="duplicateValues" dxfId="11" priority="66"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="66"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/BIM/Ontologia_Kml_2x2.xlsx
+++ b/Versão5/BIM/Ontologia_Kml_2x2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\BIM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4785289B-A6E6-4186-8404-DDC52FEBD042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2BC3C16-3035-46EF-ADE1-B754261AC1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="681" activeTab="1" xr2:uid="{EADD6BF3-7ABC-4ACF-B5B1-0F5DE0265229}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="16" r:id="rId1"/>
@@ -1625,49 +1625,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="35">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="33">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1950,6 +1908,14 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1957,6 +1923,24 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2324,14 +2308,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{643CFCF6-0637-46A8-9CC0-1BF6FB3A6D15}">
   <sheetPr codeName="Planilha14"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="6.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="65.33203125" style="29" customWidth="1"/>
-    <col min="3" max="3" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="65.36328125" style="29" customWidth="1"/>
+    <col min="3" max="3" width="4.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -2342,7 +2326,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
@@ -2353,7 +2337,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -2364,7 +2348,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
@@ -2375,7 +2359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -2387,7 +2371,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -2399,7 +2383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>17</v>
       </c>
@@ -2410,7 +2394,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
@@ -2421,7 +2405,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>0</v>
       </c>
@@ -2432,7 +2416,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>22</v>
       </c>
@@ -2443,7 +2427,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2454,7 +2438,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>25</v>
       </c>
@@ -2465,7 +2449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>26</v>
       </c>
@@ -2476,7 +2460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
         <v>27</v>
       </c>
@@ -2487,7 +2471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
         <v>28</v>
       </c>
@@ -2498,7 +2482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
         <v>90</v>
       </c>
@@ -2509,7 +2493,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -2520,19 +2504,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="7">
         <f ca="1">NOW()</f>
-        <v>46258.594610069442</v>
+        <v>46264.564807060182</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
         <v>31</v>
       </c>
@@ -2543,7 +2527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
@@ -2554,7 +2538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="6.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
         <v>34</v>
       </c>
@@ -2565,7 +2549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
         <v>35</v>
       </c>
@@ -2576,7 +2560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
@@ -2588,7 +2572,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
@@ -2611,35 +2595,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B21B10B-C8BF-4318-B9A8-B9240E89A4C8}">
   <dimension ref="A1:AD63"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" customWidth="1"/>
-    <col min="3" max="3" width="10.6640625" customWidth="1"/>
-    <col min="4" max="4" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.453125" customWidth="1"/>
+    <col min="3" max="3" width="10.6328125" customWidth="1"/>
+    <col min="4" max="4" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="155.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="144.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="134.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="11" width="7.81640625" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="155.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="144.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="134.6328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.6328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.36328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.6328125" bestFit="1" customWidth="1"/>
     <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.1640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.36328125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="58">
         <v>1</v>
       </c>
@@ -2731,7 +2715,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="31">
         <v>2</v>
       </c>
@@ -2833,7 +2817,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="31">
         <v>3</v>
       </c>
@@ -2934,7 +2918,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="31">
         <v>4</v>
       </c>
@@ -3036,7 +3020,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="31">
         <v>5</v>
       </c>
@@ -3138,7 +3122,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="31">
         <v>6</v>
       </c>
@@ -3240,7 +3224,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="31">
         <v>7</v>
       </c>
@@ -3342,7 +3326,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="31">
         <v>8</v>
       </c>
@@ -3444,7 +3428,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="31">
         <v>9</v>
       </c>
@@ -3546,7 +3530,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="31">
         <v>10</v>
       </c>
@@ -3648,7 +3632,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="31">
         <v>11</v>
       </c>
@@ -3750,7 +3734,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="31">
         <v>12</v>
       </c>
@@ -3852,7 +3836,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="31">
         <v>13</v>
       </c>
@@ -3954,7 +3938,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="31">
         <v>14</v>
       </c>
@@ -4056,7 +4040,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="31">
         <v>15</v>
       </c>
@@ -4158,7 +4142,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="31">
         <v>16</v>
       </c>
@@ -4260,7 +4244,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="31">
         <v>17</v>
       </c>
@@ -4362,7 +4346,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="31">
         <v>18</v>
       </c>
@@ -4464,7 +4448,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="31">
         <v>19</v>
       </c>
@@ -4566,7 +4550,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="31">
         <v>20</v>
       </c>
@@ -4667,7 +4651,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="31">
         <v>21</v>
       </c>
@@ -4768,7 +4752,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="31">
         <v>22</v>
       </c>
@@ -4869,7 +4853,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="31">
         <v>23</v>
       </c>
@@ -4970,7 +4954,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="31">
         <v>24</v>
       </c>
@@ -5071,7 +5055,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="31">
         <v>25</v>
       </c>
@@ -5172,7 +5156,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="31">
         <v>26</v>
       </c>
@@ -5274,7 +5258,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="31">
         <v>27</v>
       </c>
@@ -5376,7 +5360,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="31">
         <v>28</v>
       </c>
@@ -5478,7 +5462,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="31">
         <v>29</v>
       </c>
@@ -5580,7 +5564,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="31">
         <v>30</v>
       </c>
@@ -5682,7 +5666,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="31">
         <v>31</v>
       </c>
@@ -5784,7 +5768,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="31">
         <v>32</v>
       </c>
@@ -5886,7 +5870,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="31">
         <v>33</v>
       </c>
@@ -5988,7 +5972,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="31">
         <v>34</v>
       </c>
@@ -6090,7 +6074,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="31">
         <v>35</v>
       </c>
@@ -6192,7 +6176,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="31">
         <v>36</v>
       </c>
@@ -6294,7 +6278,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="31">
         <v>37</v>
       </c>
@@ -6396,7 +6380,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="31">
         <v>38</v>
       </c>
@@ -6498,7 +6482,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="31">
         <v>39</v>
       </c>
@@ -6600,7 +6584,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="31">
         <v>41</v>
       </c>
@@ -6702,7 +6686,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="31">
         <v>42</v>
       </c>
@@ -6804,7 +6788,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="31">
         <v>43</v>
       </c>
@@ -6906,7 +6890,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="31">
         <v>44</v>
       </c>
@@ -7008,7 +6992,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="31">
         <v>45</v>
       </c>
@@ -7110,7 +7094,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="31">
         <v>46</v>
       </c>
@@ -7212,7 +7196,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="31">
         <v>47</v>
       </c>
@@ -7314,7 +7298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="31">
         <v>48</v>
       </c>
@@ -7416,7 +7400,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="31">
         <v>49</v>
       </c>
@@ -7518,7 +7502,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="31">
         <v>40</v>
       </c>
@@ -7620,7 +7604,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="31">
         <v>50</v>
       </c>
@@ -7722,7 +7706,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="31">
         <v>51</v>
       </c>
@@ -7824,7 +7808,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="31">
         <v>52</v>
       </c>
@@ -7926,7 +7910,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="31">
         <v>53</v>
       </c>
@@ -8028,7 +8012,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="31">
         <v>54</v>
       </c>
@@ -8130,7 +8114,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="31">
         <v>55</v>
       </c>
@@ -8232,7 +8216,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="31">
         <v>56</v>
       </c>
@@ -8334,7 +8318,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="31">
         <v>57</v>
       </c>
@@ -8436,7 +8420,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="31">
         <v>58</v>
       </c>
@@ -8538,7 +8522,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="31">
         <v>59</v>
       </c>
@@ -8640,7 +8624,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="31">
         <v>60</v>
       </c>
@@ -8742,7 +8726,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="31">
         <v>61</v>
       </c>
@@ -8844,7 +8828,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:30" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="31">
         <v>62</v>
       </c>
@@ -8946,7 +8930,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="63" spans="1:30" s="63" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:30" s="63" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="31">
         <v>63</v>
       </c>
@@ -8957,10 +8941,10 @@
         <v>333</v>
       </c>
       <c r="D63" s="60" t="s">
+        <v>335</v>
+      </c>
+      <c r="E63" s="60" t="s">
         <v>334</v>
-      </c>
-      <c r="E63" s="60" t="s">
-        <v>335</v>
       </c>
       <c r="F63" s="60" t="s">
         <v>336</v>
@@ -8986,11 +8970,11 @@
       </c>
       <c r="M63" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N63" s="13" t="str">
         <f t="shared" si="20"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O63" s="13" t="str">
         <f t="shared" si="20"/>
@@ -9014,11 +8998,11 @@
       </c>
       <c r="U63" s="14" t="str">
         <f t="shared" si="21"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V63" s="61" t="str">
         <f t="shared" si="21"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W63" s="14" t="s">
         <v>64</v>
@@ -9050,34 +9034,29 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD62">
     <sortCondition ref="F30:F62"/>
   </sortState>
-  <conditionalFormatting sqref="A2:B62 A63">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B63">
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F62">
-    <cfRule type="duplicateValues" dxfId="34" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F63">
+    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="33" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R63">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC1:AD1">
-    <cfRule type="cellIs" dxfId="32" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F63">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R63">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9089,15 +9068,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE389E0-AD15-4DC4-98AC-F14614FE99CB}">
   <sheetPr codeName="Planilha16"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="13.1640625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="13.1796875" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" style="22" customWidth="1"/>
-    <col min="2" max="10" width="7.6640625" style="23" customWidth="1"/>
-    <col min="11" max="21" width="7.6640625" style="21" customWidth="1"/>
-    <col min="22" max="16384" width="13.1640625" style="21"/>
+    <col min="1" max="1" width="3.36328125" style="22" customWidth="1"/>
+    <col min="2" max="10" width="7.6328125" style="23" customWidth="1"/>
+    <col min="11" max="21" width="7.6328125" style="21" customWidth="1"/>
+    <col min="22" max="16384" width="13.1796875" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="18" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="18" customFormat="1" ht="15.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>66</v>
       </c>
@@ -9162,7 +9141,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19">
         <v>2</v>
       </c>
@@ -9229,7 +9208,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9244,15 +9223,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{303D1F58-E12C-4CFF-B0CB-74B96F67AF9C}">
   <sheetPr codeName="Planilha17"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.36328125" style="27" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="12.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.81640625" style="28" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24">
         <v>0</v>
       </c>
@@ -9275,7 +9254,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="10">
         <v>2</v>
       </c>
@@ -9300,22 +9279,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:G1 B3:G1048576">
-    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2">
-    <cfRule type="duplicateValues" dxfId="29" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 A1:B1">
-    <cfRule type="duplicateValues" dxfId="27" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576 B1">
-    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:G2">
-    <cfRule type="containsText" dxfId="25" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="20" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9326,30 +9305,30 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5F366C-5F74-4E71-97A7-7194C8A394D8}">
   <dimension ref="A1:W23"/>
-  <sheetFormatPr defaultColWidth="6.1640625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="6.1796875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" style="55" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.6640625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="11.83203125" style="52" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="52" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" style="55" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6328125" style="38" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="52" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" style="52" customWidth="1"/>
     <col min="5" max="5" width="8" style="52" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" style="52" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="52" customWidth="1"/>
-    <col min="8" max="8" width="5.6640625" style="52" customWidth="1"/>
-    <col min="9" max="9" width="5.33203125" style="52" customWidth="1"/>
-    <col min="10" max="10" width="8.5" style="52" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" style="52" customWidth="1"/>
-    <col min="12" max="12" width="8.5" style="52" customWidth="1"/>
-    <col min="13" max="13" width="8.33203125" style="52" customWidth="1"/>
-    <col min="14" max="14" width="5.83203125" style="52" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.1640625" style="52" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="52" customWidth="1"/>
+    <col min="7" max="7" width="8.6328125" style="52" customWidth="1"/>
+    <col min="8" max="8" width="5.6328125" style="52" customWidth="1"/>
+    <col min="9" max="9" width="5.36328125" style="52" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" style="52" customWidth="1"/>
+    <col min="11" max="11" width="7.81640625" style="52" customWidth="1"/>
+    <col min="12" max="12" width="8.453125" style="52" customWidth="1"/>
+    <col min="13" max="13" width="8.36328125" style="52" customWidth="1"/>
+    <col min="14" max="14" width="5.81640625" style="52" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.1796875" style="52" customWidth="1"/>
     <col min="16" max="16" width="8" style="52" customWidth="1"/>
-    <col min="17" max="17" width="19.83203125" style="52" customWidth="1"/>
-    <col min="18" max="23" width="5.6640625" style="52" customWidth="1"/>
-    <col min="24" max="16384" width="6.1640625" style="52"/>
+    <col min="17" max="17" width="19.81640625" style="52" customWidth="1"/>
+    <col min="18" max="23" width="5.6328125" style="52" customWidth="1"/>
+    <col min="24" max="16384" width="6.1796875" style="52"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="44" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="40">
         <v>1</v>
       </c>
@@ -9420,7 +9399,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="45">
         <v>2</v>
       </c>
@@ -9491,7 +9470,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="45">
         <v>3</v>
       </c>
@@ -9562,7 +9541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="45">
         <v>4</v>
       </c>
@@ -9633,7 +9612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="45">
         <v>5</v>
       </c>
@@ -9704,7 +9683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="45">
         <v>6</v>
       </c>
@@ -9775,7 +9754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="45">
         <v>7</v>
       </c>
@@ -9846,7 +9825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="45">
         <v>8</v>
       </c>
@@ -9917,7 +9896,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="45">
         <v>9</v>
       </c>
@@ -9988,7 +9967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="45">
         <v>10</v>
       </c>
@@ -10059,7 +10038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="45">
         <v>11</v>
       </c>
@@ -10130,7 +10109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="45">
         <v>12</v>
       </c>
@@ -10201,7 +10180,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="45">
         <v>13</v>
       </c>
@@ -10272,7 +10251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="45">
         <v>14</v>
       </c>
@@ -10343,7 +10322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="45">
         <v>15</v>
       </c>
@@ -10414,7 +10393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="45">
         <v>16</v>
       </c>
@@ -10485,7 +10464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="45">
         <v>17</v>
       </c>
@@ -10556,7 +10535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="45">
         <v>18</v>
       </c>
@@ -10627,7 +10606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="45">
         <v>19</v>
       </c>
@@ -10698,7 +10677,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="45">
         <v>20</v>
       </c>
@@ -10769,7 +10748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="45">
         <v>21</v>
       </c>
@@ -10840,7 +10819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="45">
         <v>22</v>
       </c>
@@ -10911,7 +10890,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="45">
         <v>23</v>
       </c>
@@ -10985,54 +10964,54 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B10:B1048576 B1:B8">
-    <cfRule type="duplicateValues" dxfId="24" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="21" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3">
-    <cfRule type="duplicateValues" dxfId="20" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E4">
-    <cfRule type="duplicateValues" dxfId="18" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5">
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E6">
-    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1 B1">
-    <cfRule type="duplicateValues" dxfId="12" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="71"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="11" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="duplicateValues" dxfId="10" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="9" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="duplicateValues" dxfId="8" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="69"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="duplicateValues" dxfId="7" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="68"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="duplicateValues" dxfId="6" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="67"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="duplicateValues" dxfId="5" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
